--- a/reports/QommonsAI利用集計_2026-07.xlsx
+++ b/reports/QommonsAI利用集計_2026-07.xlsx
@@ -59809,7 +59809,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.109</v>
+        <v>4.104</v>
       </c>
       <c r="C29">
         <f>ROUND(C28/B29,0)</f>
@@ -59866,7 +59866,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>【前提】入出力文字数はログ集計値（プレフィックス除く）。質問数Cは会話スレッドIDが生ログに無いため自動再計算していません。実測し直す場合はこの値を編集してください。</t>
+          <t>【前提】入出力文字数はログ集計値（プレフィックス除く）。質問数C=総プロンプト数÷セッション数(ユーザーごとに発言間隔が60分を超えたら新セッション、として自動算出。今回のセッション数=3834)</t>
         </is>
       </c>
     </row>

--- a/reports/QommonsAI利用集計_2026-07.xlsx
+++ b/reports/QommonsAI利用集計_2026-07.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>集計期間: 2026-07-01 〜 2026-07-19  ／ 利用回数=プロンプト(質問)数  ／ 使用文字数=入力+出力(プレフィックス除く)</t>
+          <t>集計期間: 2026-07-01 〜 2026-07-21  ／ 利用回数=プロンプト(質問)数  ／ 使用文字数=入力+出力(プレフィックス除く)</t>
         </is>
       </c>
     </row>
@@ -605,16 +605,16 @@
         <v>0.75</v>
       </c>
       <c r="E7" t="n">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F7" t="n">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G7" t="n">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="H7" t="n">
-        <v>1232068</v>
+        <v>1234438</v>
       </c>
       <c r="I7" t="n">
         <v>130</v>
@@ -747,63 +747,63 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>保健福祉部地域福祉課</t>
+          <t>生涯学習部管理課</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.5</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="E12" t="n">
         <v>416</v>
       </c>
       <c r="F12" t="n">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="G12" t="n">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="H12" t="n">
-        <v>563572</v>
+        <v>644554</v>
       </c>
       <c r="I12" t="n">
-        <v>139</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>生涯学習部管理課</t>
+          <t>保健福祉部地域福祉課</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.5</v>
       </c>
       <c r="E13" t="n">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="F13" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="G13" t="n">
-        <v>811</v>
+        <v>823</v>
       </c>
       <c r="H13" t="n">
-        <v>625198</v>
+        <v>563572</v>
       </c>
       <c r="I13" t="n">
-        <v>37</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -822,19 +822,19 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="E14" t="n">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="F14" t="n">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="G14" t="n">
-        <v>769</v>
+        <v>781</v>
       </c>
       <c r="H14" t="n">
-        <v>681964</v>
+        <v>692557</v>
       </c>
       <c r="I14" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15">
@@ -915,19 +915,19 @@
         <v>0.8888888888888888</v>
       </c>
       <c r="E17" t="n">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="F17" t="n">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="G17" t="n">
-        <v>641</v>
+        <v>661</v>
       </c>
       <c r="H17" t="n">
-        <v>510037</v>
+        <v>525196</v>
       </c>
       <c r="I17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18">
@@ -1194,16 +1194,16 @@
         <v>0.8</v>
       </c>
       <c r="E26" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F26" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G26" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="H26" t="n">
-        <v>303289</v>
+        <v>307643</v>
       </c>
       <c r="I26" t="n">
         <v>57</v>
@@ -1318,19 +1318,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="E30" t="n">
+        <v>185</v>
+      </c>
+      <c r="F30" t="n">
         <v>181</v>
       </c>
-      <c r="F30" t="n">
-        <v>177</v>
-      </c>
       <c r="G30" t="n">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="H30" t="n">
-        <v>332467</v>
+        <v>341325</v>
       </c>
       <c r="I30" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31">
@@ -3289,60 +3289,60 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>生涯学習部文化財課</t>
+          <t>環境部環境総務課</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>6</v>
       </c>
       <c r="C94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E94" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F94" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G94" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H94" t="n">
-        <v>44999</v>
+        <v>55802</v>
       </c>
       <c r="I94" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>市民部交通安全課</t>
+          <t>生涯学習部文化財課</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C95" t="n">
         <v>3</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E95" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F95" t="n">
         <v>29</v>
       </c>
       <c r="G95" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H95" t="n">
-        <v>45435</v>
+        <v>44999</v>
       </c>
       <c r="I95" t="n">
         <v>10</v>
@@ -3351,17 +3351,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>環境部環境総務課</t>
+          <t>市民部交通安全課</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="E96" t="n">
         <v>29</v>
@@ -3373,10 +3373,10 @@
         <v>58</v>
       </c>
       <c r="H96" t="n">
-        <v>51623</v>
+        <v>45435</v>
       </c>
       <c r="I96" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97">
@@ -3550,16 +3550,16 @@
         <v>0.3636363636363636</v>
       </c>
       <c r="E102" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F102" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G102" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H102" t="n">
-        <v>32042</v>
+        <v>35052</v>
       </c>
       <c r="I102" t="n">
         <v>6</v>
@@ -4776,10 +4776,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1177.012366666668</v>
+        <v>1179.811833333335</v>
       </c>
       <c r="Q5" t="n">
-        <v>151.8725634408599</v>
+        <v>152.2337849462363</v>
       </c>
     </row>
     <row r="6">
@@ -6035,251 +6035,251 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>腰山　恭平</t>
+          <t>佐川　篤</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>市民部国保年金課</t>
+          <t>財務部財政課</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>koshiyama@city.hakodate.hokkaido.jp</t>
+          <t>sagawa.atsushi@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E31" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F31" t="n">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="G31" t="n">
-        <v>13571</v>
+        <v>10142</v>
       </c>
       <c r="H31" t="n">
-        <v>121177</v>
+        <v>163490</v>
       </c>
       <c r="I31" t="n">
-        <v>134748</v>
+        <v>173632</v>
       </c>
       <c r="J31" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>46204.61715277778</v>
+        <v>46206.57855324074</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>46220.87768518519</v>
+        <v>46223.71409722222</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>6.753433333333334</v>
+        <v>7.478066666666667</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.871410752688172</v>
+        <v>0.9649118279569893</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>松尾　晃太</t>
+          <t>腰山　恭平</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>総務部人事課</t>
+          <t>市民部国保年金課</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>matsuo.k@city.hakodate.hokkaido.jp</t>
+          <t>koshiyama@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E32" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="F32" t="n">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="G32" t="n">
-        <v>13661</v>
+        <v>13571</v>
       </c>
       <c r="H32" t="n">
-        <v>157709</v>
+        <v>121177</v>
       </c>
       <c r="I32" t="n">
-        <v>171370</v>
+        <v>134748</v>
       </c>
       <c r="J32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>46204.60045138889</v>
+        <v>46204.61715277778</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>46218.41377314815</v>
+        <v>46220.87768518519</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>7.989166666666667</v>
+        <v>6.753433333333334</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>1.030860215053763</v>
+        <v>0.871410752688172</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>伊東　篤</t>
+          <t>松尾　晃太</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>福祉事務所生活支援総務課</t>
+          <t>総務部人事課</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ito@city.hakodate.hokkaido.jp</t>
+          <t>matsuo.k@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E33" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F33" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G33" t="n">
-        <v>18609</v>
+        <v>13661</v>
       </c>
       <c r="H33" t="n">
-        <v>116527</v>
+        <v>157709</v>
       </c>
       <c r="I33" t="n">
-        <v>135136</v>
+        <v>171370</v>
       </c>
       <c r="J33" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>46204.49625</v>
+        <v>46204.60045138889</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>46220.563125</v>
+        <v>46218.41377314815</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>7.606033333333333</v>
+        <v>7.989166666666667</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.9814236559139784</v>
+        <v>1.030860215053763</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>渡邊　雄人</t>
+          <t>伊東　篤</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>総務部人事課</t>
+          <t>福祉事務所生活支援総務課</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>watanabe.yuto@city.hakodate.hokkaido.jp</t>
+          <t>ito@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D34" t="n">
+        <v>105</v>
+      </c>
+      <c r="E34" t="n">
         <v>104</v>
       </c>
-      <c r="E34" t="n">
-        <v>103</v>
-      </c>
       <c r="F34" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G34" t="n">
-        <v>5689</v>
+        <v>18609</v>
       </c>
       <c r="H34" t="n">
-        <v>130696</v>
+        <v>116527</v>
       </c>
       <c r="I34" t="n">
-        <v>136385</v>
+        <v>135136</v>
       </c>
       <c r="J34" t="n">
         <v>12</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>46204.36684027778</v>
+        <v>46204.49625</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>46220.62813657407</v>
+        <v>46220.563125</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>5.494333333333333</v>
+        <v>7.606033333333333</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.7089462365591397</v>
+        <v>0.9814236559139784</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>佐川　篤</t>
+          <t>渡邊　雄人</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>財務部財政課</t>
+          <t>総務部人事課</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>sagawa.atsushi@city.hakodate.hokkaido.jp</t>
+          <t>watanabe.yuto@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E35" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F35" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="G35" t="n">
-        <v>9792</v>
+        <v>5689</v>
       </c>
       <c r="H35" t="n">
-        <v>148681</v>
+        <v>130696</v>
       </c>
       <c r="I35" t="n">
-        <v>158473</v>
+        <v>136385</v>
       </c>
       <c r="J35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>46206.57855324074</v>
+        <v>46204.36684027778</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>46222.9393287037</v>
+        <v>46220.62813657407</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>6.914433333333334</v>
+        <v>5.494333333333333</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.8921849462365592</v>
+        <v>0.7089462365591397</v>
       </c>
     </row>
     <row r="36">
@@ -6935,101 +6935,101 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>三上　弥生</t>
+          <t>木村　翔平</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>市民部市民・男女共同参画課</t>
+          <t>監査事務局監査課</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>mikami@city.hakodate.hokkaido.jp</t>
+          <t>kimura.shohei@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D49" t="n">
         <v>78</v>
       </c>
       <c r="E49" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F49" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G49" t="n">
-        <v>8265</v>
+        <v>4835</v>
       </c>
       <c r="H49" t="n">
-        <v>105883</v>
+        <v>123533</v>
       </c>
       <c r="I49" t="n">
-        <v>114148</v>
+        <v>128368</v>
       </c>
       <c r="J49" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>46205.3634837963</v>
+        <v>46204.37707175926</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>46213.72163194444</v>
+        <v>46223.37800925926</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>5.182433333333334</v>
+        <v>5.084766666666667</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0.6687010752688173</v>
+        <v>0.6560989247311828</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>木村　翔平</t>
+          <t>三上　弥生</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>監査事務局監査課</t>
+          <t>市民部市民・男女共同参画課</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>kimura.shohei@city.hakodate.hokkaido.jp</t>
+          <t>mikami@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E50" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F50" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G50" t="n">
-        <v>4501</v>
+        <v>8265</v>
       </c>
       <c r="H50" t="n">
-        <v>121497</v>
+        <v>105883</v>
       </c>
       <c r="I50" t="n">
-        <v>125998</v>
+        <v>114148</v>
       </c>
       <c r="J50" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>46204.37707175926</v>
+        <v>46205.3634837963</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>46219.49931712963</v>
+        <v>46213.72163194444</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>4.9501</v>
+        <v>5.182433333333334</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>0.6387225806451613</v>
+        <v>0.6687010752688173</v>
       </c>
     </row>
     <row r="51">
@@ -7085,367 +7085,367 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>阿部　良枝</t>
+          <t>大久保　勇佑</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>生涯学習部生涯学習文化課</t>
+          <t>生涯学習部管理課</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>abe.yoshie@city.hakodate.hokkaido.jp</t>
+          <t>ohkubo.y@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E52" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F52" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G52" t="n">
-        <v>4177</v>
+        <v>1927</v>
       </c>
       <c r="H52" t="n">
-        <v>106923</v>
+        <v>125324</v>
       </c>
       <c r="I52" t="n">
-        <v>111100</v>
+        <v>127251</v>
       </c>
       <c r="J52" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>46204.43336805556</v>
+        <v>46212.85341435186</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>46220.73082175926</v>
+        <v>46223.57847222222</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>4.399500000000001</v>
+        <v>4.562866666666666</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>0.5676774193548388</v>
+        <v>0.5887569892473118</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>村上　貴洋</t>
+          <t>阿部　良枝</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>企画部企画管理課</t>
+          <t>生涯学習部生涯学習文化課</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>murakami.t@city.hakodate.hokkaido.jp</t>
+          <t>abe.yoshie@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E53" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F53" t="n">
         <v>148</v>
       </c>
       <c r="G53" t="n">
-        <v>4030</v>
+        <v>4177</v>
       </c>
       <c r="H53" t="n">
-        <v>123080</v>
+        <v>106923</v>
       </c>
       <c r="I53" t="n">
-        <v>127110</v>
+        <v>111100</v>
       </c>
       <c r="J53" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>46204.43607638889</v>
+        <v>46204.43336805556</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>46217.36251157407</v>
+        <v>46220.73082175926</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>4.908666666666666</v>
+        <v>4.399500000000001</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.6333763440860214</v>
+        <v>0.5676774193548388</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>松木　あゆみ</t>
+          <t>村上　貴洋</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>会計部会計課</t>
+          <t>企画部企画管理課</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>matsuki.a@city.hakodate.hokkaido.jp</t>
+          <t>murakami.t@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E54" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F54" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G54" t="n">
-        <v>7836</v>
+        <v>4030</v>
       </c>
       <c r="H54" t="n">
-        <v>111563</v>
+        <v>123080</v>
       </c>
       <c r="I54" t="n">
-        <v>119399</v>
+        <v>127110</v>
       </c>
       <c r="J54" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>46204.43329861111</v>
+        <v>46204.43607638889</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>46220.70045138889</v>
+        <v>46217.36251157407</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>5.285966666666667</v>
+        <v>4.908666666666666</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>0.6820602150537635</v>
+        <v>0.6333763440860214</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>高橋　大智</t>
+          <t>松木　あゆみ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>企業局上下水道部浄水課</t>
+          <t>会計部会計課</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>takahashi.daichi@city.hakodate.hokkaido.jp</t>
+          <t>matsuki.a@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D55" t="n">
         <v>73</v>
       </c>
       <c r="E55" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F55" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G55" t="n">
-        <v>4745</v>
+        <v>7836</v>
       </c>
       <c r="H55" t="n">
-        <v>115921</v>
+        <v>111563</v>
       </c>
       <c r="I55" t="n">
-        <v>120666</v>
+        <v>119399</v>
       </c>
       <c r="J55" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>46204.54836805556</v>
+        <v>46204.43329861111</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>46220.62081018519</v>
+        <v>46220.70045138889</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>4.813033333333334</v>
+        <v>5.285966666666667</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.6210365591397851</v>
+        <v>0.6820602150537635</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>上田　智子</t>
+          <t>高橋　大智</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>総務部行政改革課</t>
+          <t>企業局上下水道部浄水課</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ueda.tomoko@city.hakodate.hokkaido.jp</t>
+          <t>takahashi.daichi@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E56" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F56" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G56" t="n">
-        <v>3450</v>
+        <v>4745</v>
       </c>
       <c r="H56" t="n">
-        <v>113281</v>
+        <v>115921</v>
       </c>
       <c r="I56" t="n">
-        <v>116731</v>
+        <v>120666</v>
       </c>
       <c r="J56" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>46204.4175462963</v>
+        <v>46204.54836805556</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>46220.48436342592</v>
+        <v>46220.62081018519</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>4.466033333333333</v>
+        <v>4.813033333333334</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>0.5762623655913978</v>
+        <v>0.6210365591397851</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>佐藤　優香</t>
+          <t>上田　智子</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>はこだて療育・自立支援センター</t>
+          <t>総務部行政改革課</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>sato.yuka@city.hakodate.hokkaido.jp</t>
+          <t>ueda.tomoko@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E57" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F57" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G57" t="n">
-        <v>7967</v>
+        <v>3450</v>
       </c>
       <c r="H57" t="n">
-        <v>64244</v>
+        <v>113281</v>
       </c>
       <c r="I57" t="n">
-        <v>72211</v>
+        <v>116731</v>
       </c>
       <c r="J57" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>46204.6734375</v>
+        <v>46204.4175462963</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>46220.70237268518</v>
+        <v>46220.48436342592</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>3.734866666666667</v>
+        <v>4.466033333333333</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>0.4819182795698925</v>
+        <v>0.5762623655913978</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>米澤　和希</t>
+          <t>佐藤　優香</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>保健福祉部指導監査課</t>
+          <t>はこだて療育・自立支援センター</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>yonezawa.k@city.hakodate.hokkaido.jp</t>
+          <t>sato.yuka@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E58" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F58" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G58" t="n">
-        <v>4173</v>
+        <v>7967</v>
       </c>
       <c r="H58" t="n">
-        <v>84741</v>
+        <v>64244</v>
       </c>
       <c r="I58" t="n">
-        <v>88914</v>
+        <v>72211</v>
       </c>
       <c r="J58" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>46204.43335648148</v>
+        <v>46204.6734375</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>46219.46643518518</v>
+        <v>46220.70237268518</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>3.6593</v>
+        <v>3.734866666666667</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>0.4721677419354839</v>
+        <v>0.4819182795698925</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>丑澤　拓巳</t>
+          <t>米澤　和希</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>農林水産部農林整備課</t>
+          <t>保健福祉部指導監査課</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ushizawa@city.hakodate.hokkaido.jp</t>
+          <t>yonezawa.k@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -7458,94 +7458,94 @@
         <v>135</v>
       </c>
       <c r="G59" t="n">
-        <v>10551</v>
+        <v>4173</v>
       </c>
       <c r="H59" t="n">
-        <v>75517</v>
+        <v>84741</v>
       </c>
       <c r="I59" t="n">
-        <v>86068</v>
+        <v>88914</v>
       </c>
       <c r="J59" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>46205.36403935185</v>
+        <v>46204.43335648148</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>46220.60672453704</v>
+        <v>46219.46643518518</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>4.627433333333333</v>
+        <v>3.6593</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>0.5970881720430108</v>
+        <v>0.4721677419354839</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>今野　史章</t>
+          <t>丑澤　拓巳</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>総務部総務課</t>
+          <t>農林水産部農林整備課</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>konno.fumiaki@city.hakodate.hokkaido.jp</t>
+          <t>ushizawa@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E60" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F60" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G60" t="n">
-        <v>17389</v>
+        <v>10551</v>
       </c>
       <c r="H60" t="n">
-        <v>103541</v>
+        <v>75517</v>
       </c>
       <c r="I60" t="n">
-        <v>120930</v>
+        <v>86068</v>
       </c>
       <c r="J60" t="n">
         <v>12</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>46204.55697916666</v>
+        <v>46205.36403935185</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>46220.55394675926</v>
+        <v>46220.60672453704</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>6.929166666666666</v>
+        <v>4.627433333333333</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>0.8940860215053763</v>
+        <v>0.5970881720430108</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>大久保　勇佑</t>
+          <t>今野　史章</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>生涯学習部管理課</t>
+          <t>総務部総務課</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ohkubo.y@city.hakodate.hokkaido.jp</t>
+          <t>konno.fumiaki@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -7558,28 +7558,28 @@
         <v>132</v>
       </c>
       <c r="G61" t="n">
-        <v>1812</v>
+        <v>17389</v>
       </c>
       <c r="H61" t="n">
-        <v>106083</v>
+        <v>103541</v>
       </c>
       <c r="I61" t="n">
-        <v>107895</v>
+        <v>120930</v>
       </c>
       <c r="J61" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>46212.85341435186</v>
+        <v>46204.55697916666</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>46216.92079861111</v>
+        <v>46220.55394675926</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>3.8985</v>
+        <v>6.929166666666666</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>0.5030322580645161</v>
+        <v>0.8940860215053763</v>
       </c>
     </row>
     <row r="62">
@@ -7985,57 +7985,57 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>藤島　真央</t>
+          <t>天満　真吾</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>総務部情報システム課</t>
+          <t>福祉事務所生活支援総務課</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>fujishima@city.hakodate.hokkaido.jp</t>
+          <t>tenma@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E70" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F70" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G70" t="n">
-        <v>1851</v>
+        <v>9881</v>
       </c>
       <c r="H70" t="n">
-        <v>63394</v>
+        <v>82936</v>
       </c>
       <c r="I70" t="n">
-        <v>65245</v>
+        <v>92817</v>
       </c>
       <c r="J70" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>46204.48256944444</v>
+        <v>46204.36869212963</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>46220.49844907408</v>
+        <v>46223.64053240741</v>
       </c>
       <c r="M70" s="6" t="n">
-        <v>2.483333333333333</v>
+        <v>4.740733333333334</v>
       </c>
       <c r="N70" s="6" t="n">
-        <v>0.3204301075268817</v>
+        <v>0.6117075268817205</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>(システムアカウント)</t>
+          <t>藤島　真央</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8045,141 +8045,141 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>system@city.hakodate.hokkaido.jp</t>
+          <t>fujishima@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D71" t="n">
         <v>59</v>
       </c>
       <c r="E71" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F71" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G71" t="n">
-        <v>63670</v>
+        <v>1851</v>
       </c>
       <c r="H71" t="n">
-        <v>75610</v>
+        <v>63394</v>
       </c>
       <c r="I71" t="n">
-        <v>139280</v>
+        <v>65245</v>
       </c>
       <c r="J71" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>46204.49123842592</v>
+        <v>46204.48256944444</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>46219.44039351852</v>
+        <v>46220.49844907408</v>
       </c>
       <c r="M71" s="6" t="n">
-        <v>15.25433333333333</v>
+        <v>2.483333333333333</v>
       </c>
       <c r="N71" s="6" t="n">
-        <v>1.968301075268817</v>
+        <v>0.3204301075268817</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>中貝　円香</t>
+          <t>(システムアカウント)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>生涯学習部管理課</t>
+          <t>総務部情報システム課</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>nakagai.madoka@city.hakodate.hokkaido.jp</t>
+          <t>system@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D72" t="n">
         <v>59</v>
       </c>
       <c r="E72" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F72" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G72" t="n">
-        <v>8031</v>
+        <v>63670</v>
       </c>
       <c r="H72" t="n">
-        <v>72184</v>
+        <v>75610</v>
       </c>
       <c r="I72" t="n">
-        <v>80215</v>
+        <v>139280</v>
       </c>
       <c r="J72" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>46205.68140046296</v>
+        <v>46204.49123842592</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>46220.66303240741</v>
+        <v>46219.44039351852</v>
       </c>
       <c r="M72" s="6" t="n">
-        <v>4.012333333333333</v>
+        <v>15.25433333333333</v>
       </c>
       <c r="N72" s="6" t="n">
-        <v>0.5177204301075269</v>
+        <v>1.968301075268817</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>天満　真吾</t>
+          <t>中貝　円香</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>福祉事務所生活支援総務課</t>
+          <t>生涯学習部管理課</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>tenma@city.hakodate.hokkaido.jp</t>
+          <t>nakagai.madoka@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E73" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F73" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="G73" t="n">
-        <v>9599</v>
+        <v>8031</v>
       </c>
       <c r="H73" t="n">
-        <v>78864</v>
+        <v>72184</v>
       </c>
       <c r="I73" t="n">
-        <v>88463</v>
+        <v>80215</v>
       </c>
       <c r="J73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>46204.36869212963</v>
+        <v>46205.68140046296</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>46217.78318287037</v>
+        <v>46220.66303240741</v>
       </c>
       <c r="M73" s="6" t="n">
-        <v>4.5486</v>
+        <v>4.012333333333333</v>
       </c>
       <c r="N73" s="6" t="n">
-        <v>0.586916129032258</v>
+        <v>0.5177204301075269</v>
       </c>
     </row>
     <row r="74">
@@ -8485,67 +8485,67 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>佐々木　梨那</t>
+          <t>石岡　大宗</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>市民部市民・男女共同参画課</t>
+          <t>保健福祉部介護保険課</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>sasaki.rina@city.hakodate.hokkaido.jp</t>
+          <t>ishioka.hironori@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E80" t="n">
         <v>55</v>
       </c>
       <c r="F80" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G80" t="n">
-        <v>3772</v>
+        <v>47192</v>
       </c>
       <c r="H80" t="n">
-        <v>82982</v>
+        <v>83335</v>
       </c>
       <c r="I80" t="n">
-        <v>86754</v>
+        <v>130527</v>
       </c>
       <c r="J80" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>46204.46628472222</v>
+        <v>46205.78462962963</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>46219.68502314815</v>
+        <v>46223.61363425926</v>
       </c>
       <c r="M80" s="6" t="n">
-        <v>3.520466666666667</v>
+        <v>12.21623333333333</v>
       </c>
       <c r="N80" s="6" t="n">
-        <v>0.4542537634408602</v>
+        <v>1.57628817204301</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>伊藤　善人</t>
+          <t>佐々木　梨那</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>経済部ＧＸ産業創出推進室ＧＸ産業創出推進課</t>
+          <t>市民部市民・男女共同参画課</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ito.yoshihito@city.hakodate.hokkaido.jp</t>
+          <t>sasaki.rina@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -8558,294 +8558,294 @@
         <v>110</v>
       </c>
       <c r="G81" t="n">
-        <v>5878</v>
+        <v>3772</v>
       </c>
       <c r="H81" t="n">
-        <v>100052</v>
+        <v>82982</v>
       </c>
       <c r="I81" t="n">
-        <v>105930</v>
+        <v>86754</v>
       </c>
       <c r="J81" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>46206.50047453704</v>
+        <v>46204.46628472222</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>46219.54077546296</v>
+        <v>46219.68502314815</v>
       </c>
       <c r="M81" s="6" t="n">
-        <v>4.510666666666666</v>
+        <v>3.520466666666667</v>
       </c>
       <c r="N81" s="6" t="n">
-        <v>0.582021505376344</v>
+        <v>0.4542537634408602</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>引地　俊貴</t>
+          <t>伊藤　善人</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>企画部企画管理課</t>
+          <t>経済部ＧＸ産業創出推進室ＧＸ産業創出推進課</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>hikichi.t@city.hakodate.hokkaido.jp</t>
+          <t>ito.yoshihito@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D82" t="n">
         <v>55</v>
       </c>
       <c r="E82" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F82" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G82" t="n">
-        <v>735</v>
+        <v>5878</v>
       </c>
       <c r="H82" t="n">
-        <v>58399</v>
+        <v>100052</v>
       </c>
       <c r="I82" t="n">
-        <v>59134</v>
+        <v>105930</v>
       </c>
       <c r="J82" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>46206.54832175926</v>
+        <v>46206.50047453704</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>46220.54733796296</v>
+        <v>46219.54077546296</v>
       </c>
       <c r="M82" s="6" t="n">
-        <v>2.093633333333333</v>
+        <v>4.510666666666666</v>
       </c>
       <c r="N82" s="6" t="n">
-        <v>0.2701462365591398</v>
+        <v>0.582021505376344</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>辻　祥也</t>
+          <t>引地　俊貴</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>消防本部消防本部予防課</t>
+          <t>企画部企画管理課</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>tsuji.s@city.hakodate.hokkaido.jp</t>
+          <t>hikichi.t@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E83" t="n">
         <v>54</v>
       </c>
       <c r="F83" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G83" t="n">
-        <v>4098</v>
+        <v>735</v>
       </c>
       <c r="H83" t="n">
-        <v>80244</v>
+        <v>58399</v>
       </c>
       <c r="I83" t="n">
-        <v>84342</v>
+        <v>59134</v>
       </c>
       <c r="J83" t="n">
         <v>6</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>46204.44900462963</v>
+        <v>46206.54832175926</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>46218.49505787037</v>
+        <v>46220.54733796296</v>
       </c>
       <c r="M83" s="6" t="n">
-        <v>3.4944</v>
+        <v>2.093633333333333</v>
       </c>
       <c r="N83" s="6" t="n">
-        <v>0.4508903225806452</v>
+        <v>0.2701462365591398</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>須川　大地</t>
+          <t>辻　祥也</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>監査事務局監査課</t>
+          <t>消防本部消防本部予防課</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>sugawa.d@city.hakodate.hokkaido.jp</t>
+          <t>tsuji.s@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D84" t="n">
         <v>54</v>
       </c>
       <c r="E84" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F84" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G84" t="n">
-        <v>7550</v>
+        <v>4098</v>
       </c>
       <c r="H84" t="n">
-        <v>79973</v>
+        <v>80244</v>
       </c>
       <c r="I84" t="n">
-        <v>87523</v>
+        <v>84342</v>
       </c>
       <c r="J84" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>46204.5630787037</v>
+        <v>46204.44900462963</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>46220.41780092593</v>
+        <v>46218.49505787037</v>
       </c>
       <c r="M84" s="6" t="n">
-        <v>4.175766666666666</v>
+        <v>3.4944</v>
       </c>
       <c r="N84" s="6" t="n">
-        <v>0.5388086021505376</v>
+        <v>0.4508903225806452</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>山本　瑞</t>
+          <t>須川　大地</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>消防本部消防本部指導課</t>
+          <t>監査事務局監査課</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>yamamoto.mitsushi@city.hakodate.hokkaido.jp</t>
+          <t>sugawa.d@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D85" t="n">
         <v>54</v>
       </c>
       <c r="E85" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F85" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G85" t="n">
-        <v>2444</v>
+        <v>7550</v>
       </c>
       <c r="H85" t="n">
-        <v>72940</v>
+        <v>79973</v>
       </c>
       <c r="I85" t="n">
-        <v>75384</v>
+        <v>87523</v>
       </c>
       <c r="J85" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>46205.55505787037</v>
+        <v>46204.5630787037</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>46220.70048611111</v>
+        <v>46220.41780092593</v>
       </c>
       <c r="M85" s="6" t="n">
-        <v>2.920133333333333</v>
+        <v>4.175766666666666</v>
       </c>
       <c r="N85" s="6" t="n">
-        <v>0.3767913978494624</v>
+        <v>0.5388086021505376</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>村山　卓也</t>
+          <t>山本　瑞</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>経済部雇用労政課</t>
+          <t>消防本部消防本部指導課</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>murayama.takuya@city.hakodate.hokkaido.jp</t>
+          <t>yamamoto.mitsushi@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D86" t="n">
         <v>54</v>
       </c>
       <c r="E86" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F86" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G86" t="n">
-        <v>13344</v>
+        <v>2444</v>
       </c>
       <c r="H86" t="n">
-        <v>77687</v>
+        <v>72940</v>
       </c>
       <c r="I86" t="n">
-        <v>91031</v>
+        <v>75384</v>
       </c>
       <c r="J86" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>46205.68289351852</v>
+        <v>46205.55505787037</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>46217.59480324074</v>
+        <v>46220.70048611111</v>
       </c>
       <c r="M86" s="6" t="n">
-        <v>5.258366666666666</v>
+        <v>2.920133333333333</v>
       </c>
       <c r="N86" s="6" t="n">
-        <v>0.6784989247311828</v>
+        <v>0.3767913978494624</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>池田　恵一</t>
+          <t>村山　卓也</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>企画部企画管理課</t>
+          <t>経済部雇用労政課</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ikeda.keiichi@city.hakodate.hokkaido.jp</t>
+          <t>murayama.takuya@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -8858,228 +8858,228 @@
         <v>108</v>
       </c>
       <c r="G87" t="n">
-        <v>3748</v>
+        <v>13344</v>
       </c>
       <c r="H87" t="n">
-        <v>75459</v>
+        <v>77687</v>
       </c>
       <c r="I87" t="n">
-        <v>79207</v>
+        <v>91031</v>
       </c>
       <c r="J87" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>46218.38143518518</v>
+        <v>46205.68289351852</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>46220.69466435185</v>
+        <v>46217.59480324074</v>
       </c>
       <c r="M87" s="6" t="n">
-        <v>3.2649</v>
+        <v>5.258366666666666</v>
       </c>
       <c r="N87" s="6" t="n">
-        <v>0.4212774193548387</v>
+        <v>0.6784989247311828</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>高橋　順子</t>
+          <t>池田　恵一</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>子ども未来部母子保健課</t>
+          <t>企画部企画管理課</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>takahashi.junko@city.hakodate.hokkaido.jp</t>
+          <t>ikeda.keiichi@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E88" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F88" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G88" t="n">
-        <v>9545</v>
+        <v>3748</v>
       </c>
       <c r="H88" t="n">
-        <v>68826</v>
+        <v>75459</v>
       </c>
       <c r="I88" t="n">
-        <v>78371</v>
+        <v>79207</v>
       </c>
       <c r="J88" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K88" s="5" t="n">
-        <v>46205.71129629629</v>
+        <v>46218.38143518518</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>46219.58623842592</v>
+        <v>46220.69466435185</v>
       </c>
       <c r="M88" s="6" t="n">
-        <v>4.2032</v>
+        <v>3.2649</v>
       </c>
       <c r="N88" s="6" t="n">
-        <v>0.5423483870967741</v>
+        <v>0.4212774193548387</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>直江　望</t>
+          <t>高橋　順子</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>財務部財政課</t>
+          <t>子ども未来部母子保健課</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>naoe@city.hakodate.hokkaido.jp</t>
+          <t>takahashi.junko@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E89" t="n">
         <v>51</v>
       </c>
       <c r="F89" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G89" t="n">
-        <v>2278</v>
+        <v>9545</v>
       </c>
       <c r="H89" t="n">
-        <v>80395</v>
+        <v>68826</v>
       </c>
       <c r="I89" t="n">
-        <v>82673</v>
+        <v>78371</v>
       </c>
       <c r="J89" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>46204.56894675926</v>
+        <v>46205.71129629629</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>46220.57133101852</v>
+        <v>46219.58623842592</v>
       </c>
       <c r="M89" s="6" t="n">
-        <v>3.135433333333333</v>
+        <v>4.2032</v>
       </c>
       <c r="N89" s="6" t="n">
-        <v>0.4045720430107527</v>
+        <v>0.5423483870967741</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>川上　亮太</t>
+          <t>直江　望</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>観光部観光総務課</t>
+          <t>財務部財政課</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>kawakami.r@city.hakodate.hokkaido.jp</t>
+          <t>naoe@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E90" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F90" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G90" t="n">
-        <v>1645</v>
+        <v>2278</v>
       </c>
       <c r="H90" t="n">
-        <v>58483</v>
+        <v>80395</v>
       </c>
       <c r="I90" t="n">
-        <v>60128</v>
+        <v>82673</v>
       </c>
       <c r="J90" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K90" s="5" t="n">
-        <v>46204.48583333333</v>
+        <v>46204.56894675926</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>46219.5775</v>
+        <v>46220.57133101852</v>
       </c>
       <c r="M90" s="6" t="n">
-        <v>2.278433333333334</v>
+        <v>3.135433333333333</v>
       </c>
       <c r="N90" s="6" t="n">
-        <v>0.2939913978494624</v>
+        <v>0.4045720430107527</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>石岡　大宗</t>
+          <t>川上　亮太</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>保健福祉部介護保険課</t>
+          <t>観光部観光総務課</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ishioka.hironori@city.hakodate.hokkaido.jp</t>
+          <t>kawakami.r@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D91" t="n">
         <v>50</v>
       </c>
       <c r="E91" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F91" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G91" t="n">
-        <v>47037</v>
+        <v>1645</v>
       </c>
       <c r="H91" t="n">
-        <v>72897</v>
+        <v>58483</v>
       </c>
       <c r="I91" t="n">
-        <v>119934</v>
+        <v>60128</v>
       </c>
       <c r="J91" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K91" s="5" t="n">
-        <v>46205.78462962963</v>
+        <v>46204.48583333333</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>46222.51329861111</v>
+        <v>46219.5775</v>
       </c>
       <c r="M91" s="6" t="n">
-        <v>11.8373</v>
+        <v>2.278433333333334</v>
       </c>
       <c r="N91" s="6" t="n">
-        <v>1.527393548387097</v>
+        <v>0.2939913978494624</v>
       </c>
     </row>
     <row r="92">
@@ -9585,117 +9585,117 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>辰間　羚央</t>
+          <t>近藤　正律</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>財務部管理課</t>
+          <t>総務部行政改革課</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>tatsuma@city.hakodate.hokkaido.jp</t>
+          <t>kondo@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D102" t="n">
         <v>46</v>
       </c>
       <c r="E102" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F102" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G102" t="n">
-        <v>1048</v>
+        <v>8914</v>
       </c>
       <c r="H102" t="n">
-        <v>66217</v>
+        <v>87305</v>
       </c>
       <c r="I102" t="n">
-        <v>67265</v>
+        <v>96219</v>
       </c>
       <c r="J102" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="K102" s="5" t="n">
-        <v>46211.57831018518</v>
+        <v>46204.4658449074</v>
       </c>
       <c r="L102" s="5" t="n">
-        <v>46220.69944444444</v>
+        <v>46223.52303240741</v>
       </c>
       <c r="M102" s="6" t="n">
-        <v>2.416833333333333</v>
+        <v>4.692966666666667</v>
       </c>
       <c r="N102" s="6" t="n">
-        <v>0.3118494623655914</v>
+        <v>0.6055440860215054</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>岡田　絵美</t>
+          <t>辰間　羚央</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>選挙管理委員会事務局選挙課</t>
+          <t>財務部管理課</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>okada.emi@city.hakodate.hokkaido.jp</t>
+          <t>tatsuma@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E103" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F103" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G103" t="n">
-        <v>4713</v>
+        <v>1048</v>
       </c>
       <c r="H103" t="n">
-        <v>68182</v>
+        <v>66217</v>
       </c>
       <c r="I103" t="n">
-        <v>72895</v>
+        <v>67265</v>
       </c>
       <c r="J103" t="n">
         <v>7</v>
       </c>
       <c r="K103" s="5" t="n">
-        <v>46204.42819444444</v>
+        <v>46211.57831018518</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>46219.61452546297</v>
+        <v>46220.69944444444</v>
       </c>
       <c r="M103" s="6" t="n">
-        <v>3.215333333333334</v>
+        <v>2.416833333333333</v>
       </c>
       <c r="N103" s="6" t="n">
-        <v>0.4148817204301076</v>
+        <v>0.3118494623655914</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>本田　和樹</t>
+          <t>岡田　絵美</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>企業局上下水道部管路整備室</t>
+          <t>選挙管理委員会事務局選挙課</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>honda.kazuki@city.hakodate.hokkaido.jp</t>
+          <t>okada.emi@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -9708,44 +9708,44 @@
         <v>89</v>
       </c>
       <c r="G104" t="n">
-        <v>2296</v>
+        <v>4713</v>
       </c>
       <c r="H104" t="n">
-        <v>53833</v>
+        <v>68182</v>
       </c>
       <c r="I104" t="n">
-        <v>56129</v>
+        <v>72895</v>
       </c>
       <c r="J104" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K104" s="5" t="n">
-        <v>46204.43325231481</v>
+        <v>46204.42819444444</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>46220.5661574074</v>
+        <v>46219.61452546297</v>
       </c>
       <c r="M104" s="6" t="n">
-        <v>2.253633333333333</v>
+        <v>3.215333333333334</v>
       </c>
       <c r="N104" s="6" t="n">
-        <v>0.2907913978494623</v>
+        <v>0.4148817204301076</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>及川　奈緒子</t>
+          <t>本田　和樹</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>財務部税務室</t>
+          <t>企業局上下水道部管路整備室</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>oikawa.naoko@city.hakodate.hokkaido.jp</t>
+          <t>honda.kazuki@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -9758,44 +9758,44 @@
         <v>89</v>
       </c>
       <c r="G105" t="n">
-        <v>4624</v>
+        <v>2296</v>
       </c>
       <c r="H105" t="n">
-        <v>59854</v>
+        <v>53833</v>
       </c>
       <c r="I105" t="n">
-        <v>64478</v>
+        <v>56129</v>
       </c>
       <c r="J105" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K105" s="5" t="n">
-        <v>46204.43329861111</v>
+        <v>46204.43325231481</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>46220.47017361111</v>
+        <v>46220.5661574074</v>
       </c>
       <c r="M105" s="6" t="n">
-        <v>2.919933333333333</v>
+        <v>2.253633333333333</v>
       </c>
       <c r="N105" s="6" t="n">
-        <v>0.3767655913978494</v>
+        <v>0.2907913978494623</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>両角　忠之</t>
+          <t>及川　奈緒子</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>企業局上下水道部管路整備室</t>
+          <t>財務部税務室</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>morozumi@city.hakodate.hokkaido.jp</t>
+          <t>oikawa.naoko@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -9808,144 +9808,144 @@
         <v>89</v>
       </c>
       <c r="G106" t="n">
-        <v>1818</v>
+        <v>4624</v>
       </c>
       <c r="H106" t="n">
-        <v>69024</v>
+        <v>59854</v>
       </c>
       <c r="I106" t="n">
-        <v>70842</v>
+        <v>64478</v>
       </c>
       <c r="J106" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K106" s="5" t="n">
-        <v>46204.55600694445</v>
+        <v>46204.43329861111</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>46218.59541666666</v>
+        <v>46220.47017361111</v>
       </c>
       <c r="M106" s="6" t="n">
-        <v>2.6644</v>
+        <v>2.919933333333333</v>
       </c>
       <c r="N106" s="6" t="n">
-        <v>0.3437935483870968</v>
+        <v>0.3767655913978494</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>山下　雅史</t>
+          <t>両角　忠之</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>消防本部消防本部警防課</t>
+          <t>企業局上下水道部管路整備室</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>yamashita.m@city.hakodate.hokkaido.jp</t>
+          <t>morozumi@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D107" t="n">
         <v>45</v>
       </c>
       <c r="E107" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F107" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G107" t="n">
-        <v>5058</v>
+        <v>1818</v>
       </c>
       <c r="H107" t="n">
-        <v>55650</v>
+        <v>69024</v>
       </c>
       <c r="I107" t="n">
-        <v>60708</v>
+        <v>70842</v>
       </c>
       <c r="J107" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K107" s="5" t="n">
-        <v>46204.62579861111</v>
+        <v>46204.55600694445</v>
       </c>
       <c r="L107" s="5" t="n">
-        <v>46219.80175925926</v>
+        <v>46218.59541666666</v>
       </c>
       <c r="M107" s="6" t="n">
-        <v>2.8666</v>
+        <v>2.6644</v>
       </c>
       <c r="N107" s="6" t="n">
-        <v>0.3698838709677419</v>
+        <v>0.3437935483870968</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>西川　太一</t>
+          <t>山下　雅史</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>企画部地域デジタル課</t>
+          <t>消防本部消防本部警防課</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>nishikawa.taichi@city.hakodate.hokkaido.jp</t>
+          <t>yamashita.m@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E108" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F108" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G108" t="n">
-        <v>5006</v>
+        <v>5058</v>
       </c>
       <c r="H108" t="n">
-        <v>71478</v>
+        <v>55650</v>
       </c>
       <c r="I108" t="n">
-        <v>76484</v>
+        <v>60708</v>
       </c>
       <c r="J108" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K108" s="5" t="n">
-        <v>46204.36356481481</v>
+        <v>46204.62579861111</v>
       </c>
       <c r="L108" s="5" t="n">
-        <v>46220.72502314814</v>
+        <v>46219.80175925926</v>
       </c>
       <c r="M108" s="6" t="n">
-        <v>3.3838</v>
+        <v>2.8666</v>
       </c>
       <c r="N108" s="6" t="n">
-        <v>0.4366193548387097</v>
+        <v>0.3698838709677419</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>半田　陽祐</t>
+          <t>西川　太一</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>企業局交通部施設課</t>
+          <t>企画部地域デジタル課</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>handa@city.hakodate.hokkaido.jp</t>
+          <t>nishikawa.taichi@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -9958,244 +9958,244 @@
         <v>87</v>
       </c>
       <c r="G109" t="n">
-        <v>4714</v>
+        <v>5006</v>
       </c>
       <c r="H109" t="n">
-        <v>55983</v>
+        <v>71478</v>
       </c>
       <c r="I109" t="n">
-        <v>60697</v>
+        <v>76484</v>
       </c>
       <c r="J109" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K109" s="5" t="n">
-        <v>46204.42826388889</v>
+        <v>46204.36356481481</v>
       </c>
       <c r="L109" s="5" t="n">
-        <v>46220.4480787037</v>
+        <v>46220.72502314814</v>
       </c>
       <c r="M109" s="6" t="n">
-        <v>2.8089</v>
+        <v>3.3838</v>
       </c>
       <c r="N109" s="6" t="n">
-        <v>0.3624387096774194</v>
+        <v>0.4366193548387097</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>菊地　正明</t>
+          <t>半田　陽祐</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>湯川支所</t>
+          <t>企業局交通部施設課</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>kikuchi.masa@city.hakodate.hokkaido.jp</t>
+          <t>handa@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D110" t="n">
         <v>44</v>
       </c>
       <c r="E110" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F110" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G110" t="n">
-        <v>10821</v>
+        <v>4714</v>
       </c>
       <c r="H110" t="n">
-        <v>50627</v>
+        <v>55983</v>
       </c>
       <c r="I110" t="n">
-        <v>61448</v>
+        <v>60697</v>
       </c>
       <c r="J110" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K110" s="5" t="n">
-        <v>46204.47886574074</v>
+        <v>46204.42826388889</v>
       </c>
       <c r="L110" s="5" t="n">
-        <v>46220.50607638889</v>
+        <v>46220.4480787037</v>
       </c>
       <c r="M110" s="6" t="n">
-        <v>3.851766666666667</v>
+        <v>2.8089</v>
       </c>
       <c r="N110" s="6" t="n">
-        <v>0.4970021505376344</v>
+        <v>0.3624387096774194</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>塚田　花野</t>
+          <t>菊地　正明</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>財務部税務室</t>
+          <t>湯川支所</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>tsukada.hanano@city.hakodate.hokkaido.jp</t>
+          <t>kikuchi.masa@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D111" t="n">
         <v>44</v>
       </c>
       <c r="E111" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F111" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G111" t="n">
-        <v>1714</v>
+        <v>10821</v>
       </c>
       <c r="H111" t="n">
-        <v>61323</v>
+        <v>50627</v>
       </c>
       <c r="I111" t="n">
-        <v>63037</v>
+        <v>61448</v>
       </c>
       <c r="J111" t="n">
         <v>9</v>
       </c>
       <c r="K111" s="5" t="n">
-        <v>46205.47797453704</v>
+        <v>46204.47886574074</v>
       </c>
       <c r="L111" s="5" t="n">
-        <v>46220.50118055556</v>
+        <v>46220.50607638889</v>
       </c>
       <c r="M111" s="6" t="n">
-        <v>2.3869</v>
+        <v>3.851766666666667</v>
       </c>
       <c r="N111" s="6" t="n">
-        <v>0.3079870967741935</v>
+        <v>0.4970021505376344</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>吉田　知世</t>
+          <t>塚田　花野</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>会計部会計課</t>
+          <t>財務部税務室</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>yoshida.tomoyo@city.hakodate.hokkaido.jp</t>
+          <t>tsukada.hanano@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E112" t="n">
         <v>43</v>
       </c>
       <c r="F112" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G112" t="n">
-        <v>2911</v>
+        <v>1714</v>
       </c>
       <c r="H112" t="n">
-        <v>65398</v>
+        <v>61323</v>
       </c>
       <c r="I112" t="n">
-        <v>68309</v>
+        <v>63037</v>
       </c>
       <c r="J112" t="n">
         <v>9</v>
       </c>
       <c r="K112" s="5" t="n">
-        <v>46204.43342592593</v>
+        <v>46205.47797453704</v>
       </c>
       <c r="L112" s="5" t="n">
-        <v>46220.72418981481</v>
+        <v>46220.50118055556</v>
       </c>
       <c r="M112" s="6" t="n">
-        <v>2.762133333333333</v>
+        <v>2.3869</v>
       </c>
       <c r="N112" s="6" t="n">
-        <v>0.3564043010752688</v>
+        <v>0.3079870967741935</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>小林　文京</t>
+          <t>吉田　知世</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>市民部市民・男女共同参画課</t>
+          <t>会計部会計課</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>kobayashi.fumitaka@city.hakodate.hokkaido.jp</t>
+          <t>yoshida.tomoyo@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D113" t="n">
         <v>43</v>
       </c>
       <c r="E113" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F113" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G113" t="n">
-        <v>4135</v>
+        <v>2911</v>
       </c>
       <c r="H113" t="n">
-        <v>55395</v>
+        <v>65398</v>
       </c>
       <c r="I113" t="n">
-        <v>59530</v>
+        <v>68309</v>
       </c>
       <c r="J113" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K113" s="5" t="n">
-        <v>46206.53248842592</v>
+        <v>46204.43342592593</v>
       </c>
       <c r="L113" s="5" t="n">
-        <v>46218.65644675926</v>
+        <v>46220.72418981481</v>
       </c>
       <c r="M113" s="6" t="n">
-        <v>2.6735</v>
+        <v>2.762133333333333</v>
       </c>
       <c r="N113" s="6" t="n">
-        <v>0.3449677419354839</v>
+        <v>0.3564043010752688</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>岩城　崇太</t>
+          <t>小林　文京</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>財務部財政課</t>
+          <t>市民部市民・男女共同参画課</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>iwaki@city.hakodate.hokkaido.jp</t>
+          <t>kobayashi.fumitaka@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -10208,78 +10208,78 @@
         <v>85</v>
       </c>
       <c r="G114" t="n">
-        <v>966</v>
+        <v>4135</v>
       </c>
       <c r="H114" t="n">
-        <v>58857</v>
+        <v>55395</v>
       </c>
       <c r="I114" t="n">
-        <v>59823</v>
+        <v>59530</v>
       </c>
       <c r="J114" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K114" s="5" t="n">
-        <v>46209.43712962963</v>
+        <v>46206.53248842592</v>
       </c>
       <c r="L114" s="5" t="n">
-        <v>46219.36576388889</v>
+        <v>46218.65644675926</v>
       </c>
       <c r="M114" s="6" t="n">
-        <v>2.1551</v>
+        <v>2.6735</v>
       </c>
       <c r="N114" s="6" t="n">
-        <v>0.2780774193548387</v>
+        <v>0.3449677419354839</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>近藤　正律</t>
+          <t>岩城　崇太</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>総務部行政改革課</t>
+          <t>財務部財政課</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>kondo@city.hakodate.hokkaido.jp</t>
+          <t>iwaki@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D115" t="n">
+        <v>43</v>
+      </c>
+      <c r="E115" t="n">
         <v>42</v>
       </c>
-      <c r="E115" t="n">
-        <v>40</v>
-      </c>
       <c r="F115" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G115" t="n">
-        <v>8010</v>
+        <v>966</v>
       </c>
       <c r="H115" t="n">
-        <v>79351</v>
+        <v>58857</v>
       </c>
       <c r="I115" t="n">
-        <v>87361</v>
+        <v>59823</v>
       </c>
       <c r="J115" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K115" s="5" t="n">
-        <v>46204.4658449074</v>
+        <v>46209.43712962963</v>
       </c>
       <c r="L115" s="5" t="n">
-        <v>46220.77868055556</v>
+        <v>46219.36576388889</v>
       </c>
       <c r="M115" s="6" t="n">
-        <v>4.247033333333333</v>
+        <v>2.1551</v>
       </c>
       <c r="N115" s="6" t="n">
-        <v>0.5480043010752689</v>
+        <v>0.2780774193548387</v>
       </c>
     </row>
     <row r="116">
@@ -15585,167 +15585,167 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>福田　誠</t>
+          <t>荒木　彰浩</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>監査事務局監査課</t>
+          <t>消防本部北消防署</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>fukuda.m@city.hakodate.hokkaido.jp</t>
+          <t>araki.a@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D222" t="n">
         <v>18</v>
       </c>
       <c r="E222" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F222" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G222" t="n">
-        <v>6266</v>
+        <v>1439</v>
       </c>
       <c r="H222" t="n">
-        <v>30857</v>
+        <v>23701</v>
       </c>
       <c r="I222" t="n">
-        <v>37123</v>
+        <v>25140</v>
       </c>
       <c r="J222" t="n">
         <v>6</v>
       </c>
       <c r="K222" s="5" t="n">
-        <v>46204.3941087963</v>
+        <v>46204.29359953704</v>
       </c>
       <c r="L222" s="5" t="n">
-        <v>46212.61950231482</v>
+        <v>46224.26418981481</v>
       </c>
       <c r="M222" s="6" t="n">
-        <v>2.281766666666667</v>
+        <v>1.077833333333333</v>
       </c>
       <c r="N222" s="6" t="n">
-        <v>0.2944215053763441</v>
+        <v>0.1390752688172043</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>山田　恭平</t>
+          <t>福田　誠</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>市民部国保年金課</t>
+          <t>監査事務局監査課</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>yamada.kyohei@city.hakodate.hokkaido.jp</t>
+          <t>fukuda.m@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D223" t="n">
         <v>18</v>
       </c>
       <c r="E223" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F223" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G223" t="n">
-        <v>3691</v>
+        <v>6266</v>
       </c>
       <c r="H223" t="n">
-        <v>16291</v>
+        <v>30857</v>
       </c>
       <c r="I223" t="n">
-        <v>19982</v>
+        <v>37123</v>
       </c>
       <c r="J223" t="n">
         <v>6</v>
       </c>
       <c r="K223" s="5" t="n">
-        <v>46204.41961805556</v>
+        <v>46204.3941087963</v>
       </c>
       <c r="L223" s="5" t="n">
-        <v>46213.62094907407</v>
+        <v>46212.61950231482</v>
       </c>
       <c r="M223" s="6" t="n">
-        <v>1.281233333333333</v>
+        <v>2.281766666666667</v>
       </c>
       <c r="N223" s="6" t="n">
-        <v>0.1653204301075269</v>
+        <v>0.2944215053763441</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>吉田　光治</t>
+          <t>山田　恭平</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>恵山支所産業建設課</t>
+          <t>市民部国保年金課</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>yoshida.kouji@city.hakodate.hokkaido.jp</t>
+          <t>yamada.kyohei@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D224" t="n">
         <v>18</v>
       </c>
       <c r="E224" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F224" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G224" t="n">
-        <v>2016</v>
+        <v>3691</v>
       </c>
       <c r="H224" t="n">
-        <v>25588</v>
+        <v>16291</v>
       </c>
       <c r="I224" t="n">
-        <v>27604</v>
+        <v>19982</v>
       </c>
       <c r="J224" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K224" s="5" t="n">
-        <v>46204.47773148148</v>
+        <v>46204.41961805556</v>
       </c>
       <c r="L224" s="5" t="n">
-        <v>46210.63547453703</v>
+        <v>46213.62094907407</v>
       </c>
       <c r="M224" s="6" t="n">
-        <v>1.256133333333333</v>
+        <v>1.281233333333333</v>
       </c>
       <c r="N224" s="6" t="n">
-        <v>0.1620817204301075</v>
+        <v>0.1653204301075269</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>米倉　航平</t>
+          <t>吉田　光治</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>総務部総務課</t>
+          <t>恵山支所産業建設課</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>yonekura.kohei@city.hakodate.hokkaido.jp</t>
+          <t>yoshida.kouji@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -15758,44 +15758,44 @@
         <v>36</v>
       </c>
       <c r="G225" t="n">
-        <v>3678</v>
+        <v>2016</v>
       </c>
       <c r="H225" t="n">
-        <v>18934</v>
+        <v>25588</v>
       </c>
       <c r="I225" t="n">
-        <v>22612</v>
+        <v>27604</v>
       </c>
       <c r="J225" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K225" s="5" t="n">
-        <v>46204.49260416667</v>
+        <v>46204.47773148148</v>
       </c>
       <c r="L225" s="5" t="n">
-        <v>46217.41085648148</v>
+        <v>46210.63547453703</v>
       </c>
       <c r="M225" s="6" t="n">
-        <v>1.366733333333333</v>
+        <v>1.256133333333333</v>
       </c>
       <c r="N225" s="6" t="n">
-        <v>0.176352688172043</v>
+        <v>0.1620817204301075</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>土田　ゆりあ</t>
+          <t>米倉　航平</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>農林水産部企画調整課</t>
+          <t>総務部総務課</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>tsuchida.y@city.hakodate.hokkaido.jp</t>
+          <t>yonekura.kohei@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -15808,44 +15808,44 @@
         <v>36</v>
       </c>
       <c r="G226" t="n">
-        <v>629</v>
+        <v>3678</v>
       </c>
       <c r="H226" t="n">
-        <v>25045</v>
+        <v>18934</v>
       </c>
       <c r="I226" t="n">
-        <v>25674</v>
+        <v>22612</v>
       </c>
       <c r="J226" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K226" s="5" t="n">
-        <v>46204.59165509259</v>
+        <v>46204.49260416667</v>
       </c>
       <c r="L226" s="5" t="n">
-        <v>46211.67664351852</v>
+        <v>46217.41085648148</v>
       </c>
       <c r="M226" s="6" t="n">
-        <v>0.9606333333333335</v>
+        <v>1.366733333333333</v>
       </c>
       <c r="N226" s="6" t="n">
-        <v>0.123952688172043</v>
+        <v>0.176352688172043</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>佐藤　史絵</t>
+          <t>土田　ゆりあ</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>銭亀沢支所</t>
+          <t>農林水産部企画調整課</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>sato.shie@city.hakodate.hokkaido.jp</t>
+          <t>tsuchida.y@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -15858,178 +15858,178 @@
         <v>36</v>
       </c>
       <c r="G227" t="n">
-        <v>1501</v>
+        <v>629</v>
       </c>
       <c r="H227" t="n">
-        <v>24470</v>
+        <v>25045</v>
       </c>
       <c r="I227" t="n">
-        <v>25971</v>
+        <v>25674</v>
       </c>
       <c r="J227" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K227" s="5" t="n">
-        <v>46205.68292824074</v>
+        <v>46204.59165509259</v>
       </c>
       <c r="L227" s="5" t="n">
-        <v>46217.60002314814</v>
+        <v>46211.67664351852</v>
       </c>
       <c r="M227" s="6" t="n">
-        <v>1.115866666666667</v>
+        <v>0.9606333333333335</v>
       </c>
       <c r="N227" s="6" t="n">
-        <v>0.1439827956989247</v>
+        <v>0.123952688172043</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>嵐　奈津恵</t>
+          <t>佐藤　史絵</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>企業局管理部料金課</t>
+          <t>銭亀沢支所</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>arashi@city.hakodate.hokkaido.jp</t>
+          <t>sato.shie@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D228" t="n">
         <v>18</v>
       </c>
       <c r="E228" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F228" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G228" t="n">
-        <v>2700</v>
+        <v>1501</v>
       </c>
       <c r="H228" t="n">
-        <v>25329</v>
+        <v>24470</v>
       </c>
       <c r="I228" t="n">
-        <v>28029</v>
+        <v>25971</v>
       </c>
       <c r="J228" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K228" s="5" t="n">
-        <v>46205.68296296296</v>
+        <v>46205.68292824074</v>
       </c>
       <c r="L228" s="5" t="n">
-        <v>46211.57109953704</v>
+        <v>46217.60002314814</v>
       </c>
       <c r="M228" s="6" t="n">
-        <v>1.3843</v>
+        <v>1.115866666666667</v>
       </c>
       <c r="N228" s="6" t="n">
-        <v>0.1786193548387097</v>
+        <v>0.1439827956989247</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>一戸　千尋</t>
+          <t>嵐　奈津恵</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>保健所保健予防課</t>
+          <t>企業局管理部料金課</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>ichinohe.chihiro@city.hakodate.hokkaido.jp</t>
+          <t>arashi@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D229" t="n">
         <v>18</v>
       </c>
       <c r="E229" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F229" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G229" t="n">
-        <v>1000</v>
+        <v>2700</v>
       </c>
       <c r="H229" t="n">
-        <v>26361</v>
+        <v>25329</v>
       </c>
       <c r="I229" t="n">
-        <v>27361</v>
+        <v>28029</v>
       </c>
       <c r="J229" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K229" s="5" t="n">
-        <v>46205.69747685185</v>
+        <v>46205.68296296296</v>
       </c>
       <c r="L229" s="5" t="n">
-        <v>46218.46958333333</v>
+        <v>46211.57109953704</v>
       </c>
       <c r="M229" s="6" t="n">
-        <v>1.0787</v>
+        <v>1.3843</v>
       </c>
       <c r="N229" s="6" t="n">
-        <v>0.1391870967741936</v>
+        <v>0.1786193548387097</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>荒木　彰浩</t>
+          <t>一戸　千尋</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>消防本部北消防署</t>
+          <t>保健所保健予防課</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>araki.a@city.hakodate.hokkaido.jp</t>
+          <t>ichinohe.chihiro@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E230" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F230" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G230" t="n">
-        <v>465</v>
+        <v>1000</v>
       </c>
       <c r="H230" t="n">
-        <v>21665</v>
+        <v>26361</v>
       </c>
       <c r="I230" t="n">
-        <v>22130</v>
+        <v>27361</v>
       </c>
       <c r="J230" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K230" s="5" t="n">
-        <v>46204.29359953704</v>
+        <v>46205.69747685185</v>
       </c>
       <c r="L230" s="5" t="n">
-        <v>46221.96550925926</v>
+        <v>46218.46958333333</v>
       </c>
       <c r="M230" s="6" t="n">
-        <v>0.8151666666666666</v>
+        <v>1.0787</v>
       </c>
       <c r="N230" s="6" t="n">
-        <v>0.1051827956989247</v>
+        <v>0.1391870967741936</v>
       </c>
     </row>
     <row r="231">
@@ -16985,17 +16985,17 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>水野　博</t>
+          <t>駒込　雄作</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>保健福祉部地域福祉課</t>
+          <t>環境部環境総務課</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>mizuno.hiroshi@city.hakodate.hokkaido.jp</t>
+          <t>komagome.y@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -17008,144 +17008,144 @@
         <v>32</v>
       </c>
       <c r="G250" t="n">
-        <v>537</v>
+        <v>8036</v>
       </c>
       <c r="H250" t="n">
-        <v>22730</v>
+        <v>22732</v>
       </c>
       <c r="I250" t="n">
-        <v>23267</v>
+        <v>30768</v>
       </c>
       <c r="J250" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K250" s="5" t="n">
-        <v>46212.58765046296</v>
+        <v>46212.4965162037</v>
       </c>
       <c r="L250" s="5" t="n">
-        <v>46220.66484953704</v>
+        <v>46223.98996527777</v>
       </c>
       <c r="M250" s="6" t="n">
-        <v>0.8650666666666668</v>
+        <v>2.364933333333334</v>
       </c>
       <c r="N250" s="6" t="n">
-        <v>0.1116215053763441</v>
+        <v>0.3051526881720431</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>木村　元子</t>
+          <t>水野　博</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>生涯学習部文化財課</t>
+          <t>保健福祉部地域福祉課</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>kimura.motoko@city.hakodate.hokkaido.jp</t>
+          <t>mizuno.hiroshi@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E251" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F251" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G251" t="n">
-        <v>1553</v>
+        <v>537</v>
       </c>
       <c r="H251" t="n">
-        <v>20776</v>
+        <v>22730</v>
       </c>
       <c r="I251" t="n">
-        <v>22329</v>
+        <v>23267</v>
       </c>
       <c r="J251" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K251" s="5" t="n">
-        <v>46204.43342592593</v>
+        <v>46212.58765046296</v>
       </c>
       <c r="L251" s="5" t="n">
-        <v>46209.45797453704</v>
+        <v>46220.66484953704</v>
       </c>
       <c r="M251" s="6" t="n">
-        <v>1.003133333333333</v>
+        <v>0.8650666666666668</v>
       </c>
       <c r="N251" s="6" t="n">
-        <v>0.129436559139785</v>
+        <v>0.1116215053763441</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>今野　慎太郎</t>
+          <t>木村　元子</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>企業局管理部経理課</t>
+          <t>生涯学習部文化財課</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>konno.shin@city.hakodate.hokkaido.jp</t>
+          <t>kimura.motoko@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D252" t="n">
         <v>15</v>
       </c>
       <c r="E252" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F252" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G252" t="n">
-        <v>369</v>
+        <v>1553</v>
       </c>
       <c r="H252" t="n">
-        <v>19898</v>
+        <v>20776</v>
       </c>
       <c r="I252" t="n">
-        <v>20267</v>
+        <v>22329</v>
       </c>
       <c r="J252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K252" s="5" t="n">
-        <v>46204.44755787037</v>
+        <v>46204.43342592593</v>
       </c>
       <c r="L252" s="5" t="n">
-        <v>46206.58331018518</v>
+        <v>46209.45797453704</v>
       </c>
       <c r="M252" s="6" t="n">
-        <v>0.7370666666666666</v>
+        <v>1.003133333333333</v>
       </c>
       <c r="N252" s="6" t="n">
-        <v>0.09510537634408602</v>
+        <v>0.129436559139785</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>伊藤　幹太</t>
+          <t>今野　慎太郎</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>市民部国保年金課</t>
+          <t>企業局管理部経理課</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>ito.kanta@city.hakodate.hokkaido.jp</t>
+          <t>konno.shin@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D253" t="n">
@@ -17158,144 +17158,144 @@
         <v>30</v>
       </c>
       <c r="G253" t="n">
-        <v>1290</v>
+        <v>369</v>
       </c>
       <c r="H253" t="n">
-        <v>15307</v>
+        <v>19898</v>
       </c>
       <c r="I253" t="n">
-        <v>16597</v>
+        <v>20267</v>
       </c>
       <c r="J253" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K253" s="5" t="n">
-        <v>46204.54387731481</v>
+        <v>46204.44755787037</v>
       </c>
       <c r="L253" s="5" t="n">
-        <v>46217.65040509259</v>
+        <v>46206.58331018518</v>
       </c>
       <c r="M253" s="6" t="n">
-        <v>0.7682333333333333</v>
+        <v>0.7370666666666666</v>
       </c>
       <c r="N253" s="6" t="n">
-        <v>0.0991268817204301</v>
+        <v>0.09510537634408602</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>清水　みなみ</t>
+          <t>伊藤　幹太</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>福祉事務所障がい保健福祉課</t>
+          <t>市民部国保年金課</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>shimizu.mi@city.hakodate.hokkaido.jp</t>
+          <t>ito.kanta@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D254" t="n">
         <v>15</v>
       </c>
       <c r="E254" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F254" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G254" t="n">
-        <v>2813</v>
+        <v>1290</v>
       </c>
       <c r="H254" t="n">
-        <v>18098</v>
+        <v>15307</v>
       </c>
       <c r="I254" t="n">
-        <v>20911</v>
+        <v>16597</v>
       </c>
       <c r="J254" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K254" s="5" t="n">
-        <v>46205.68289351852</v>
+        <v>46204.54387731481</v>
       </c>
       <c r="L254" s="5" t="n">
-        <v>46212.47804398148</v>
+        <v>46217.65040509259</v>
       </c>
       <c r="M254" s="6" t="n">
-        <v>1.165866666666667</v>
+        <v>0.7682333333333333</v>
       </c>
       <c r="N254" s="6" t="n">
-        <v>0.1504344086021505</v>
+        <v>0.0991268817204301</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>石川　怜</t>
+          <t>清水　みなみ</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>南茅部支所産業建設課</t>
+          <t>福祉事務所障がい保健福祉課</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>ishikawa.r@city.hakodate.hokkaido.jp</t>
+          <t>shimizu.mi@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D255" t="n">
         <v>15</v>
       </c>
       <c r="E255" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F255" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G255" t="n">
-        <v>1432</v>
+        <v>2813</v>
       </c>
       <c r="H255" t="n">
-        <v>21902</v>
+        <v>18098</v>
       </c>
       <c r="I255" t="n">
-        <v>23334</v>
+        <v>20911</v>
       </c>
       <c r="J255" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K255" s="5" t="n">
-        <v>46205.68299768519</v>
+        <v>46205.68289351852</v>
       </c>
       <c r="L255" s="5" t="n">
-        <v>46220.64998842592</v>
+        <v>46212.47804398148</v>
       </c>
       <c r="M255" s="6" t="n">
-        <v>1.016466666666667</v>
+        <v>1.165866666666667</v>
       </c>
       <c r="N255" s="6" t="n">
-        <v>0.1311569892473118</v>
+        <v>0.1504344086021505</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>廣島　菜菜子</t>
+          <t>石川　怜</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>環境部環境推進課</t>
+          <t>南茅部支所産業建設課</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>hiroshima.nanako@city.hakodate.hokkaido.jp</t>
+          <t>ishikawa.r@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D256" t="n">
@@ -17308,144 +17308,144 @@
         <v>30</v>
       </c>
       <c r="G256" t="n">
-        <v>481</v>
+        <v>1432</v>
       </c>
       <c r="H256" t="n">
-        <v>16402</v>
+        <v>21902</v>
       </c>
       <c r="I256" t="n">
-        <v>16883</v>
+        <v>23334</v>
       </c>
       <c r="J256" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K256" s="5" t="n">
-        <v>46206.44105324074</v>
+        <v>46205.68299768519</v>
       </c>
       <c r="L256" s="5" t="n">
-        <v>46219.70211805555</v>
+        <v>46220.64998842592</v>
       </c>
       <c r="M256" s="6" t="n">
-        <v>0.6429333333333334</v>
+        <v>1.016466666666667</v>
       </c>
       <c r="N256" s="6" t="n">
-        <v>0.08295913978494623</v>
+        <v>0.1311569892473118</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>532738@北海道_函館市</t>
+          <t>廣島　菜菜子</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>(未登録)</t>
+          <t>環境部環境推進課</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>532738@北海道_函館市</t>
+          <t>hiroshima.nanako@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D257" t="n">
         <v>15</v>
       </c>
       <c r="E257" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F257" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G257" t="n">
-        <v>8911</v>
+        <v>481</v>
       </c>
       <c r="H257" t="n">
-        <v>24442</v>
+        <v>16402</v>
       </c>
       <c r="I257" t="n">
-        <v>33353</v>
+        <v>16883</v>
       </c>
       <c r="J257" t="n">
         <v>3</v>
       </c>
       <c r="K257" s="5" t="n">
-        <v>46206.46689814814</v>
+        <v>46206.44105324074</v>
       </c>
       <c r="L257" s="5" t="n">
-        <v>46217.70395833333</v>
+        <v>46219.70211805555</v>
       </c>
       <c r="M257" s="6" t="n">
-        <v>2.596933333333333</v>
+        <v>0.6429333333333334</v>
       </c>
       <c r="N257" s="6" t="n">
-        <v>0.3350881720430107</v>
+        <v>0.08295913978494623</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>澤村　美紅</t>
+          <t>532738@北海道_函館市</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>港湾空港部管理課</t>
+          <t>(未登録)</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>sawamura.m@city.hakodate.hokkaido.jp</t>
+          <t>532738@北海道_函館市</t>
         </is>
       </c>
       <c r="D258" t="n">
         <v>15</v>
       </c>
       <c r="E258" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F258" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G258" t="n">
-        <v>468</v>
+        <v>8911</v>
       </c>
       <c r="H258" t="n">
-        <v>17969</v>
+        <v>24442</v>
       </c>
       <c r="I258" t="n">
-        <v>18437</v>
+        <v>33353</v>
       </c>
       <c r="J258" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K258" s="5" t="n">
-        <v>46206.48925925926</v>
+        <v>46206.46689814814</v>
       </c>
       <c r="L258" s="5" t="n">
-        <v>46206.72747685185</v>
+        <v>46217.70395833333</v>
       </c>
       <c r="M258" s="6" t="n">
-        <v>0.6925666666666667</v>
+        <v>2.596933333333333</v>
       </c>
       <c r="N258" s="6" t="n">
-        <v>0.08936344086021505</v>
+        <v>0.3350881720430107</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>田畑　裕康</t>
+          <t>澤村　美紅</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>子ども未来部子ども健やか育成課</t>
+          <t>港湾空港部管理課</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>tabata.hiroyasu@city.hakodate.hokkaido.jp</t>
+          <t>sawamura.m@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D259" t="n">
@@ -17458,44 +17458,44 @@
         <v>30</v>
       </c>
       <c r="G259" t="n">
-        <v>318</v>
+        <v>468</v>
       </c>
       <c r="H259" t="n">
-        <v>19790</v>
+        <v>17969</v>
       </c>
       <c r="I259" t="n">
-        <v>20108</v>
+        <v>18437</v>
       </c>
       <c r="J259" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K259" s="5" t="n">
-        <v>46209.41025462963</v>
+        <v>46206.48925925926</v>
       </c>
       <c r="L259" s="5" t="n">
-        <v>46216.49697916667</v>
+        <v>46206.72747685185</v>
       </c>
       <c r="M259" s="6" t="n">
-        <v>0.7232666666666667</v>
+        <v>0.6925666666666667</v>
       </c>
       <c r="N259" s="6" t="n">
-        <v>0.0933247311827957</v>
+        <v>0.08936344086021505</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>山上　優樹</t>
+          <t>田畑　裕康</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>企画部計画推進室計画調整課</t>
+          <t>子ども未来部子ども健やか育成課</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>yamakami.y@city.hakodate.hokkaido.jp</t>
+          <t>tabata.hiroyasu@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D260" t="n">
@@ -17508,194 +17508,194 @@
         <v>30</v>
       </c>
       <c r="G260" t="n">
-        <v>1241</v>
+        <v>318</v>
       </c>
       <c r="H260" t="n">
-        <v>17444</v>
+        <v>19790</v>
       </c>
       <c r="I260" t="n">
-        <v>18685</v>
+        <v>20108</v>
       </c>
       <c r="J260" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K260" s="5" t="n">
-        <v>46209.63861111111</v>
+        <v>46209.41025462963</v>
       </c>
       <c r="L260" s="5" t="n">
-        <v>46219.3640625</v>
+        <v>46216.49697916667</v>
       </c>
       <c r="M260" s="6" t="n">
-        <v>0.8296666666666667</v>
+        <v>0.7232666666666667</v>
       </c>
       <c r="N260" s="6" t="n">
-        <v>0.1070537634408602</v>
+        <v>0.0933247311827957</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>麻生　礼子</t>
+          <t>山上　優樹</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>はこだて療育・自立支援センター</t>
+          <t>企画部計画推進室計画調整課</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>aso@city.hakodate.hokkaido.jp</t>
+          <t>yamakami.y@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D261" t="n">
         <v>15</v>
       </c>
       <c r="E261" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F261" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G261" t="n">
-        <v>1110</v>
+        <v>1241</v>
       </c>
       <c r="H261" t="n">
-        <v>21333</v>
+        <v>17444</v>
       </c>
       <c r="I261" t="n">
-        <v>22443</v>
+        <v>18685</v>
       </c>
       <c r="J261" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K261" s="5" t="n">
-        <v>46210.55670138889</v>
+        <v>46209.63861111111</v>
       </c>
       <c r="L261" s="5" t="n">
-        <v>46216.76023148148</v>
+        <v>46219.3640625</v>
       </c>
       <c r="M261" s="6" t="n">
-        <v>0.9331</v>
+        <v>0.8296666666666667</v>
       </c>
       <c r="N261" s="6" t="n">
-        <v>0.1204</v>
+        <v>0.1070537634408602</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>木村　凱哉</t>
+          <t>麻生　礼子</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>環境部環境総務課</t>
+          <t>はこだて療育・自立支援センター</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>kimura.yoshiya@city.hakodate.hokkaido.jp</t>
+          <t>aso@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D262" t="n">
         <v>15</v>
       </c>
       <c r="E262" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F262" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G262" t="n">
-        <v>3515</v>
+        <v>1110</v>
       </c>
       <c r="H262" t="n">
-        <v>21519</v>
+        <v>21333</v>
       </c>
       <c r="I262" t="n">
-        <v>25034</v>
+        <v>22443</v>
       </c>
       <c r="J262" t="n">
         <v>4</v>
       </c>
       <c r="K262" s="5" t="n">
-        <v>46212.49480324074</v>
+        <v>46210.55670138889</v>
       </c>
       <c r="L262" s="5" t="n">
-        <v>46220.62030092593</v>
+        <v>46216.76023148148</v>
       </c>
       <c r="M262" s="6" t="n">
-        <v>1.4203</v>
+        <v>0.9331</v>
       </c>
       <c r="N262" s="6" t="n">
-        <v>0.1832645161290323</v>
+        <v>0.1204</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>外岡　佳代子</t>
+          <t>木村　凱哉</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>生涯学習部管理課</t>
+          <t>環境部環境総務課</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>tonooka@city.hakodate.hokkaido.jp</t>
+          <t>kimura.yoshiya@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E263" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F263" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G263" t="n">
-        <v>998</v>
+        <v>3515</v>
       </c>
       <c r="H263" t="n">
-        <v>17487</v>
+        <v>21519</v>
       </c>
       <c r="I263" t="n">
-        <v>18485</v>
+        <v>25034</v>
       </c>
       <c r="J263" t="n">
         <v>4</v>
       </c>
       <c r="K263" s="5" t="n">
-        <v>46204.43319444444</v>
+        <v>46212.49480324074</v>
       </c>
       <c r="L263" s="5" t="n">
-        <v>46213.4459375</v>
+        <v>46220.62030092593</v>
       </c>
       <c r="M263" s="6" t="n">
-        <v>0.7825000000000001</v>
+        <v>1.4203</v>
       </c>
       <c r="N263" s="6" t="n">
-        <v>0.1009677419354839</v>
+        <v>0.1832645161290323</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>円山　牧子</t>
+          <t>外岡　佳代子</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>市民部戸籍住民課</t>
+          <t>生涯学習部管理課</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>maruyama.makiko@city.hakodate.hokkaido.jp</t>
+          <t>tonooka@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D264" t="n">
@@ -17708,44 +17708,44 @@
         <v>28</v>
       </c>
       <c r="G264" t="n">
-        <v>2765</v>
+        <v>998</v>
       </c>
       <c r="H264" t="n">
-        <v>14730</v>
+        <v>17487</v>
       </c>
       <c r="I264" t="n">
-        <v>17495</v>
+        <v>18485</v>
       </c>
       <c r="J264" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K264" s="5" t="n">
-        <v>46204.4334375</v>
+        <v>46204.43319444444</v>
       </c>
       <c r="L264" s="5" t="n">
-        <v>46204.63504629629</v>
+        <v>46213.4459375</v>
       </c>
       <c r="M264" s="6" t="n">
-        <v>1.044</v>
+        <v>0.7825000000000001</v>
       </c>
       <c r="N264" s="6" t="n">
-        <v>0.1347096774193549</v>
+        <v>0.1009677419354839</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>野呂　健尚</t>
+          <t>円山　牧子</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>環境部環境推進課</t>
+          <t>市民部戸籍住民課</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>noro.katsuhisa@city.hakodate.hokkaido.jp</t>
+          <t>maruyama.makiko@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D265" t="n">
@@ -17758,44 +17758,44 @@
         <v>28</v>
       </c>
       <c r="G265" t="n">
-        <v>1494</v>
+        <v>2765</v>
       </c>
       <c r="H265" t="n">
-        <v>18833</v>
+        <v>14730</v>
       </c>
       <c r="I265" t="n">
-        <v>20327</v>
+        <v>17495</v>
       </c>
       <c r="J265" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K265" s="5" t="n">
-        <v>46204.43362268519</v>
+        <v>46204.4334375</v>
       </c>
       <c r="L265" s="5" t="n">
-        <v>46212.70216435185</v>
+        <v>46204.63504629629</v>
       </c>
       <c r="M265" s="6" t="n">
-        <v>0.9265666666666668</v>
+        <v>1.044</v>
       </c>
       <c r="N265" s="6" t="n">
-        <v>0.1195569892473118</v>
+        <v>0.1347096774193549</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>三好　仁子</t>
+          <t>野呂　健尚</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>子ども未来部子どもサービス課</t>
+          <t>環境部環境推進課</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>miyoshi.h@city.hakodate.hokkaido.jp</t>
+          <t>noro.katsuhisa@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D266" t="n">
@@ -17808,144 +17808,144 @@
         <v>28</v>
       </c>
       <c r="G266" t="n">
-        <v>917</v>
+        <v>1494</v>
       </c>
       <c r="H266" t="n">
-        <v>17964</v>
+        <v>18833</v>
       </c>
       <c r="I266" t="n">
-        <v>18881</v>
+        <v>20327</v>
       </c>
       <c r="J266" t="n">
         <v>3</v>
       </c>
       <c r="K266" s="5" t="n">
-        <v>46204.43621527778</v>
+        <v>46204.43362268519</v>
       </c>
       <c r="L266" s="5" t="n">
-        <v>46212.96515046297</v>
+        <v>46212.70216435185</v>
       </c>
       <c r="M266" s="6" t="n">
-        <v>0.7821999999999999</v>
+        <v>0.9265666666666668</v>
       </c>
       <c r="N266" s="6" t="n">
-        <v>0.1009290322580645</v>
+        <v>0.1195569892473118</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>泉　秀典</t>
+          <t>三好　仁子</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>消防本部消防本部庶務課</t>
+          <t>子ども未来部子どもサービス課</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>izumi.h@city.hakodate.hokkaido.jp</t>
+          <t>miyoshi.h@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D267" t="n">
         <v>14</v>
       </c>
       <c r="E267" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F267" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G267" t="n">
-        <v>2152</v>
+        <v>917</v>
       </c>
       <c r="H267" t="n">
-        <v>18899</v>
+        <v>17964</v>
       </c>
       <c r="I267" t="n">
-        <v>21051</v>
+        <v>18881</v>
       </c>
       <c r="J267" t="n">
         <v>3</v>
       </c>
       <c r="K267" s="5" t="n">
-        <v>46204.43623842593</v>
+        <v>46204.43621527778</v>
       </c>
       <c r="L267" s="5" t="n">
-        <v>46210.35274305556</v>
+        <v>46212.96515046297</v>
       </c>
       <c r="M267" s="6" t="n">
-        <v>1.060366666666667</v>
+        <v>0.7821999999999999</v>
       </c>
       <c r="N267" s="6" t="n">
-        <v>0.1368215053763441</v>
+        <v>0.1009290322580645</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>佐々木　柊人</t>
+          <t>泉　秀典</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>衛生試験所</t>
+          <t>消防本部消防本部庶務課</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>syuto.s@city.hakodate.hokkaido.jp</t>
+          <t>izumi.h@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D268" t="n">
         <v>14</v>
       </c>
       <c r="E268" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F268" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G268" t="n">
-        <v>1014</v>
+        <v>2152</v>
       </c>
       <c r="H268" t="n">
-        <v>13806</v>
+        <v>18899</v>
       </c>
       <c r="I268" t="n">
-        <v>14820</v>
+        <v>21051</v>
       </c>
       <c r="J268" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K268" s="5" t="n">
-        <v>46204.43627314815</v>
+        <v>46204.43623842593</v>
       </c>
       <c r="L268" s="5" t="n">
-        <v>46219.593125</v>
+        <v>46210.35274305556</v>
       </c>
       <c r="M268" s="6" t="n">
-        <v>0.663</v>
+        <v>1.060366666666667</v>
       </c>
       <c r="N268" s="6" t="n">
-        <v>0.0855483870967742</v>
+        <v>0.1368215053763441</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>西村　茉莉絵</t>
+          <t>佐々木　柊人</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>会計部会計課</t>
+          <t>衛生試験所</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>nishimura.marie@city.hakodate.hokkaido.jp</t>
+          <t>syuto.s@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D269" t="n">
@@ -17958,144 +17958,144 @@
         <v>28</v>
       </c>
       <c r="G269" t="n">
-        <v>700</v>
+        <v>1014</v>
       </c>
       <c r="H269" t="n">
-        <v>21345</v>
+        <v>13806</v>
       </c>
       <c r="I269" t="n">
-        <v>22045</v>
+        <v>14820</v>
       </c>
       <c r="J269" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K269" s="5" t="n">
-        <v>46204.48357638889</v>
+        <v>46204.43627314815</v>
       </c>
       <c r="L269" s="5" t="n">
-        <v>46220.6920949074</v>
+        <v>46219.593125</v>
       </c>
       <c r="M269" s="6" t="n">
-        <v>0.8514999999999999</v>
+        <v>0.663</v>
       </c>
       <c r="N269" s="6" t="n">
-        <v>0.1098709677419355</v>
+        <v>0.0855483870967742</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>安藤　敏浩</t>
+          <t>西村　茉莉絵</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>土木部公園河川整備課</t>
+          <t>会計部会計課</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>ando.toshihiro@city.hakodate.hokkaido.jp</t>
+          <t>nishimura.marie@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D270" t="n">
         <v>14</v>
       </c>
       <c r="E270" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F270" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G270" t="n">
-        <v>681</v>
+        <v>700</v>
       </c>
       <c r="H270" t="n">
-        <v>16845</v>
+        <v>21345</v>
       </c>
       <c r="I270" t="n">
-        <v>17526</v>
+        <v>22045</v>
       </c>
       <c r="J270" t="n">
         <v>5</v>
       </c>
       <c r="K270" s="5" t="n">
-        <v>46204.60246527778</v>
+        <v>46204.48357638889</v>
       </c>
       <c r="L270" s="5" t="n">
-        <v>46217.63797453704</v>
+        <v>46220.6920949074</v>
       </c>
       <c r="M270" s="6" t="n">
-        <v>0.6976999999999999</v>
+        <v>0.8514999999999999</v>
       </c>
       <c r="N270" s="6" t="n">
-        <v>0.09002580645161289</v>
+        <v>0.1098709677419355</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>久留島　麻央</t>
+          <t>安藤　敏浩</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>保健福祉部高齢福祉課</t>
+          <t>土木部公園河川整備課</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>kurushima@city.hakodate.hokkaido.jp</t>
+          <t>ando.toshihiro@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D271" t="n">
         <v>14</v>
       </c>
       <c r="E271" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F271" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G271" t="n">
-        <v>817</v>
+        <v>681</v>
       </c>
       <c r="H271" t="n">
-        <v>16313</v>
+        <v>16845</v>
       </c>
       <c r="I271" t="n">
-        <v>17130</v>
+        <v>17526</v>
       </c>
       <c r="J271" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K271" s="5" t="n">
-        <v>46205.68296296296</v>
+        <v>46204.60246527778</v>
       </c>
       <c r="L271" s="5" t="n">
-        <v>46216.625</v>
+        <v>46217.63797453704</v>
       </c>
       <c r="M271" s="6" t="n">
-        <v>0.7071666666666666</v>
+        <v>0.6976999999999999</v>
       </c>
       <c r="N271" s="6" t="n">
-        <v>0.09124731182795698</v>
+        <v>0.09002580645161289</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>阿部　駿也</t>
+          <t>久留島　麻央</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>市民部市民・男女共同参画課</t>
+          <t>保健福祉部高齢福祉課</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>abe.shunya@city.hakodate.hokkaido.jp</t>
+          <t>kurushima@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D272" t="n">
@@ -18108,44 +18108,44 @@
         <v>28</v>
       </c>
       <c r="G272" t="n">
-        <v>212</v>
+        <v>817</v>
       </c>
       <c r="H272" t="n">
-        <v>16097</v>
+        <v>16313</v>
       </c>
       <c r="I272" t="n">
-        <v>16309</v>
+        <v>17130</v>
       </c>
       <c r="J272" t="n">
         <v>4</v>
       </c>
       <c r="K272" s="5" t="n">
-        <v>46206.54016203704</v>
+        <v>46205.68296296296</v>
       </c>
       <c r="L272" s="5" t="n">
-        <v>46220.71525462963</v>
+        <v>46216.625</v>
       </c>
       <c r="M272" s="6" t="n">
-        <v>0.5789666666666666</v>
+        <v>0.7071666666666666</v>
       </c>
       <c r="N272" s="6" t="n">
-        <v>0.07470537634408601</v>
+        <v>0.09124731182795698</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>高木　則文</t>
+          <t>阿部　駿也</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>総務部災害対策課</t>
+          <t>市民部市民・男女共同参画課</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>takagi.norifumi@city.hakodate.hokkaido.jp</t>
+          <t>abe.shunya@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D273" t="n">
@@ -18158,44 +18158,44 @@
         <v>28</v>
       </c>
       <c r="G273" t="n">
-        <v>5959</v>
+        <v>212</v>
       </c>
       <c r="H273" t="n">
-        <v>17357</v>
+        <v>16097</v>
       </c>
       <c r="I273" t="n">
-        <v>23316</v>
+        <v>16309</v>
       </c>
       <c r="J273" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K273" s="5" t="n">
-        <v>46206.7419212963</v>
+        <v>46206.54016203704</v>
       </c>
       <c r="L273" s="5" t="n">
-        <v>46220.83063657407</v>
+        <v>46220.71525462963</v>
       </c>
       <c r="M273" s="6" t="n">
-        <v>1.770366666666667</v>
+        <v>0.5789666666666666</v>
       </c>
       <c r="N273" s="6" t="n">
-        <v>0.2284344086021505</v>
+        <v>0.07470537634408601</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>内田　政継</t>
+          <t>高木　則文</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>福祉事務所障がい保健福祉課</t>
+          <t>総務部災害対策課</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>uchida.m@city.hakodate.hokkaido.jp</t>
+          <t>takagi.norifumi@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D274" t="n">
@@ -18208,44 +18208,44 @@
         <v>28</v>
       </c>
       <c r="G274" t="n">
-        <v>1053</v>
+        <v>5959</v>
       </c>
       <c r="H274" t="n">
-        <v>20372</v>
+        <v>17357</v>
       </c>
       <c r="I274" t="n">
-        <v>21425</v>
+        <v>23316</v>
       </c>
       <c r="J274" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K274" s="5" t="n">
-        <v>46209.42143518518</v>
+        <v>46206.7419212963</v>
       </c>
       <c r="L274" s="5" t="n">
-        <v>46220.42631944444</v>
+        <v>46220.83063657407</v>
       </c>
       <c r="M274" s="6" t="n">
-        <v>0.8896666666666667</v>
+        <v>1.770366666666667</v>
       </c>
       <c r="N274" s="6" t="n">
-        <v>0.1147956989247312</v>
+        <v>0.2284344086021505</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>駒込　雄作</t>
+          <t>内田　政継</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>環境部環境総務課</t>
+          <t>福祉事務所障がい保健福祉課</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>komagome.y@city.hakodate.hokkaido.jp</t>
+          <t>uchida.m@city.hakodate.hokkaido.jp</t>
         </is>
       </c>
       <c r="D275" t="n">
@@ -18258,28 +18258,28 @@
         <v>28</v>
       </c>
       <c r="G275" t="n">
-        <v>7929</v>
+        <v>1053</v>
       </c>
       <c r="H275" t="n">
-        <v>18660</v>
+        <v>20372</v>
       </c>
       <c r="I275" t="n">
-        <v>26589</v>
+        <v>21425</v>
       </c>
       <c r="J275" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K275" s="5" t="n">
-        <v>46212.4965162037</v>
+        <v>46209.42143518518</v>
       </c>
       <c r="L275" s="5" t="n">
-        <v>46219.67839120371</v>
+        <v>46220.42631944444</v>
       </c>
       <c r="M275" s="6" t="n">
-        <v>2.2078</v>
+        <v>0.8896666666666667</v>
       </c>
       <c r="N275" s="6" t="n">
-        <v>0.2848774193548387</v>
+        <v>0.1147956989247312</v>
       </c>
     </row>
     <row r="276">
@@ -29465,7 +29465,7 @@
         <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>1232068</v>
+        <v>1234438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -29687,7 +29687,7 @@
         <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>681964</v>
+        <v>692557</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>119934</v>
+        <v>130527</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>625198</v>
+        <v>644554</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -29740,7 +29740,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>107895</v>
+        <v>127251</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -29791,75 +29791,75 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>総務部人事課</t>
+          <t>財務部財政課</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>516173</v>
+        <v>525196</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>松尾　晃太</t>
+          <t>佐川　篤</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>171370</v>
+        <v>173632</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>渡邊　雄人</t>
+          <t>川井　大知</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>136385</v>
+        <v>86621</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>長谷川　康介</t>
+          <t>直江　望</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>55098</v>
+        <v>82673</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>財務部財政課</t>
+          <t>総務部人事課</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>510037</v>
+        <v>516173</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>佐川　篤</t>
+          <t>松尾　晃太</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>158473</v>
+        <v>171370</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>川井　大知</t>
+          <t>渡邊　雄人</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>86621</v>
+        <v>136385</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>直江　望</t>
+          <t>長谷川　康介</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>82673</v>
+        <v>55098</v>
       </c>
     </row>
     <row r="17">
@@ -30108,75 +30108,75 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>土木部公園河川整備課</t>
+          <t>総務部行政改革課</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>334187</v>
+        <v>341325</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>佐藤　靖</t>
+          <t>上田　智子</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>289018</v>
+        <v>116731</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>安藤　敏浩</t>
+          <t>近藤　正律</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>17526</v>
+        <v>96219</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>稲垣　尚志</t>
+          <t>村越　一輝</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>14037</v>
+        <v>93549</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>総務部行政改革課</t>
+          <t>土木部公園河川整備課</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>332467</v>
+        <v>334187</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>上田　智子</t>
+          <t>佐藤　靖</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>116731</v>
+        <v>289018</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>村越　一輝</t>
+          <t>安藤　敏浩</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>93549</v>
+        <v>17526</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>近藤　正律</t>
+          <t>稲垣　尚志</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>87361</v>
+        <v>14037</v>
       </c>
     </row>
     <row r="26">
@@ -30189,7 +30189,7 @@
         <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>303289</v>
+        <v>307643</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>88463</v>
+        <v>92817</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -32083,178 +32083,178 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>議会事務局庶務課</t>
+          <t>環境部環境総務課</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C83" t="n">
-        <v>54875</v>
+        <v>55802</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>三橋　竜二</t>
+          <t>駒込　雄作</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>37425</v>
+        <v>30768</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>古川　峻梧</t>
+          <t>木村　凱哉</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>14777</v>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>三尾　慎吾</t>
-        </is>
-      </c>
-      <c r="I83" t="n">
-        <v>2673</v>
+        <v>25034</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>戸井支所地域振興課</t>
+          <t>議会事務局庶務課</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>3</v>
       </c>
       <c r="C84" t="n">
-        <v>54824</v>
+        <v>54875</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>磯見　通代</t>
+          <t>三橋　竜二</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>28192</v>
+        <v>37425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>稲船　純也</t>
+          <t>古川　峻梧</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>25538</v>
+        <v>14777</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>松野　雄大</t>
+          <t>三尾　慎吾</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1094</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>都市建設部まちづくり景観課</t>
+          <t>戸井支所地域振興課</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C85" t="n">
-        <v>54378</v>
+        <v>54824</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>三橋　由葵乃</t>
+          <t>磯見　通代</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>14004</v>
+        <v>28192</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>清水　歩</t>
+          <t>稲船　純也</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>9627</v>
+        <v>25538</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>小坂　未希子</t>
+          <t>松野　雄大</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>7361</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>子ども未来部子ども見守り・相談課</t>
+          <t>都市建設部まちづくり景観課</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C86" t="n">
-        <v>51998</v>
+        <v>54378</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>坂下　浩</t>
+          <t>三橋　由葵乃</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>41408</v>
+        <v>14004</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>村瀬　美奈子</t>
+          <t>清水　歩</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>4145</v>
+        <v>9627</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>佐藤　悠一朗</t>
+          <t>小坂　未希子</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4093</v>
+        <v>7361</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>環境部環境総務課</t>
+          <t>子ども未来部子ども見守り・相談課</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C87" t="n">
-        <v>51623</v>
+        <v>51998</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>駒込　雄作</t>
+          <t>坂下　浩</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>26589</v>
+        <v>41408</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>木村　凱哉</t>
+          <t>村瀬　美奈子</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>25034</v>
+        <v>4145</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>佐藤　悠一朗</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>4093</v>
       </c>
     </row>
     <row r="88">
@@ -32666,75 +32666,75 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>学校教育部学校教育課</t>
+          <t>消防本部北消防署</t>
         </is>
       </c>
       <c r="B102" t="n">
         <v>4</v>
       </c>
       <c r="C102" t="n">
-        <v>32734</v>
+        <v>35052</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>廣瀬　貴久</t>
+          <t>荒木　彰浩</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>15625</v>
+        <v>25140</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>二本柳　舜</t>
+          <t>羽二生　大祐</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>13687</v>
+        <v>6314</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>冨田　好美</t>
+          <t>鈴木　早姫</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2081</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>消防本部北消防署</t>
+          <t>学校教育部学校教育課</t>
         </is>
       </c>
       <c r="B103" t="n">
         <v>4</v>
       </c>
       <c r="C103" t="n">
-        <v>32042</v>
+        <v>32734</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>荒木　彰浩</t>
+          <t>廣瀬　貴久</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>22130</v>
+        <v>15625</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>羽二生　大祐</t>
+          <t>二本柳　舜</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>6314</v>
+        <v>13687</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>鈴木　早姫</t>
+          <t>冨田　好美</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2140</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="104">
@@ -56814,7 +56814,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>集計期間: 2026-07-01 〜 2026-07-19</t>
+          <t>集計期間: 2026-07-01 〜 2026-07-21</t>
         </is>
       </c>
     </row>
@@ -56875,7 +56875,7 @@
         <v>2815</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>0.1788891713268937</v>
+        <v>0.1784808521430383</v>
       </c>
       <c r="D7" t="n">
         <v>2791</v>
@@ -56896,13 +56896,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2730</v>
+        <v>2736</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>0.1734875444839858</v>
+        <v>0.1734719756530561</v>
       </c>
       <c r="D8" t="n">
-        <v>2691</v>
+        <v>2697</v>
       </c>
       <c r="E8" t="n">
         <v>204</v>
@@ -56920,13 +56920,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2619</v>
+        <v>2642</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>0.1664336553126589</v>
+        <v>0.1675120466649759</v>
       </c>
       <c r="D9" t="n">
-        <v>2590</v>
+        <v>2613</v>
       </c>
       <c r="E9" t="n">
         <v>277</v>
@@ -56944,13 +56944,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2543</v>
+        <v>2548</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>0.1616039654295882</v>
+        <v>0.1615521176768958</v>
       </c>
       <c r="D10" t="n">
-        <v>2512</v>
+        <v>2517</v>
       </c>
       <c r="E10" t="n">
         <v>166</v>
@@ -56971,7 +56971,7 @@
         <v>1628</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>0.1034570411794611</v>
+        <v>0.1032208977935582</v>
       </c>
       <c r="D11" t="n">
         <v>1610</v>
@@ -56992,13 +56992,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>0.08674377224199288</v>
+        <v>0.08667258432665483</v>
       </c>
       <c r="D12" t="n">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="E12" t="n">
         <v>212</v>
@@ -57019,7 +57019,7 @@
         <v>1133</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>0.07200050838840874</v>
+        <v>0.07183616535632767</v>
       </c>
       <c r="D13" t="n">
         <v>1117</v>
@@ -57043,7 +57043,7 @@
         <v>480</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>0.03050330452465684</v>
+        <v>0.03043367993913264</v>
       </c>
       <c r="D14" t="n">
         <v>476</v>
@@ -57067,7 +57067,7 @@
         <v>303</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>0.01925521098118963</v>
+        <v>0.01921126046157748</v>
       </c>
       <c r="D15" t="n">
         <v>298</v>
@@ -57091,7 +57091,7 @@
         <v>120</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>0.007625826131164209</v>
+        <v>0.00760841998478316</v>
       </c>
       <c r="D16" t="n">
         <v>120</v>
@@ -57112,13 +57112,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15736</v>
+        <v>15772</v>
       </c>
       <c r="C17" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>15557</v>
+        <v>15593</v>
       </c>
       <c r="E17" t="n">
         <v>491</v>
@@ -57169,10 +57169,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10830</v>
+        <v>10857</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>0.6882308083375699</v>
+        <v>0.6883717981232564</v>
       </c>
       <c r="D21" t="n">
         <v>432</v>
@@ -57190,10 +57190,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2489</v>
+        <v>2496</v>
       </c>
       <c r="C22" s="8" t="n">
-        <v>0.1581723436705643</v>
+        <v>0.1582551356834897</v>
       </c>
       <c r="D22" t="n">
         <v>266</v>
@@ -57214,7 +57214,7 @@
         <v>1167</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>0.07416115912557193</v>
+        <v>0.07399188435201623</v>
       </c>
       <c r="D23" t="n">
         <v>197</v>
@@ -57235,7 +57235,7 @@
         <v>881</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>0.0559862735129639</v>
+        <v>0.05585848338828303</v>
       </c>
       <c r="D24" t="n">
         <v>185</v>
@@ -57256,7 +57256,7 @@
         <v>175</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>0.01112099644128114</v>
+        <v>0.01109561247780877</v>
       </c>
       <c r="D25" t="n">
         <v>48</v>
@@ -57274,10 +57274,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C26" s="8" t="n">
-        <v>0.006164209456024403</v>
+        <v>0.006276946487446107</v>
       </c>
       <c r="D26" t="n">
         <v>15</v>
@@ -57298,7 +57298,7 @@
         <v>97</v>
       </c>
       <c r="C27" s="8" t="n">
-        <v>0.006164209456024403</v>
+        <v>0.006150139487699721</v>
       </c>
       <c r="D27" t="n">
         <v>37</v>
@@ -57320,7 +57320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -57339,7 +57339,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>集計期間: 2026-07-01 〜 2026-07-19</t>
+          <t>集計期間: 2026-07-01 〜 2026-07-21</t>
         </is>
       </c>
     </row>
@@ -57388,7 +57388,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>0.0003177427554651754</v>
+        <v>0.000317017499365965</v>
       </c>
     </row>
     <row r="8">
@@ -57401,7 +57401,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>0.0002541942043721403</v>
+        <v>0.000253613999492772</v>
       </c>
     </row>
     <row r="9">
@@ -57414,141 +57414,136 @@
         <v>5</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>0.0003177427554651754</v>
+        <v>0.000317017499365965</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07:00〜07:59</t>
+          <t>06:00〜06:59</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>0.001334519572953737</v>
+        <v>6.3403499873193e-05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08:00〜08:59</t>
+          <t>07:00〜07:59</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>343</v>
+        <v>21</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>0.02179715302491103</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>始業前</t>
-        </is>
+        <v>0.001331473497337053</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09:00〜09:59</t>
+          <t>08:00〜08:59</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1450</v>
+        <v>343</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>0.09214539908490087</v>
+        <v>0.0217474004565052</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>午前</t>
+          <t>始業前</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10:00〜10:59</t>
+          <t>09:00〜09:59</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2349</v>
+        <v>1454</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>0.1492755465175394</v>
+        <v>0.09218868881562262</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>午前（ピーク）</t>
+          <t>午前</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>11:00〜11:59</t>
+          <t>10:00〜10:59</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1876</v>
+        <v>2350</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>0.1192170818505338</v>
+        <v>0.1489982247020036</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>午前</t>
+          <t>午前（ピーク）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>12:00〜12:59</t>
+          <t>11:00〜11:59</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>564</v>
+        <v>1881</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>0.03584138281647178</v>
+        <v>0.119261983261476</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>昼休み</t>
+          <t>午前</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>13:00〜13:59</t>
+          <t>12:00〜12:59</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1603</v>
+        <v>574</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>0.1018683274021352</v>
+        <v>0.03639360892721278</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>午後</t>
+          <t>昼休み</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>14:00〜14:59</t>
+          <t>13:00〜13:59</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1789</v>
+        <v>1611</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>0.1136883579054398</v>
+        <v>0.1021430382957139</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -57559,14 +57554,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>15:00〜15:59</t>
+          <t>14:00〜14:59</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1737</v>
+        <v>1790</v>
       </c>
       <c r="C18" s="8" t="n">
-        <v>0.1103838332486019</v>
+        <v>0.1134922647730155</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -57577,68 +57572,68 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16:00〜16:59</t>
+          <t>15:00〜15:59</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1991</v>
+        <v>1738</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>0.1265251652262328</v>
+        <v>0.1101952827796094</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>午後（ピーク）</t>
+          <t>午後</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>17:00〜17:59</t>
+          <t>16:00〜16:59</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1188</v>
+        <v>1992</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>0.07549567869852568</v>
+        <v>0.1262997717474005</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>午後</t>
+          <t>午後（ピーク）</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>18:00〜18:59</t>
+          <t>17:00〜17:59</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>308</v>
+        <v>1190</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>0.0195729537366548</v>
+        <v>0.07545016484909967</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>時間外</t>
+          <t>午後</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>19:00〜19:59</t>
+          <t>18:00〜18:59</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>188</v>
+        <v>308</v>
       </c>
       <c r="C22" s="8" t="n">
-        <v>0.0119471276054906</v>
+        <v>0.01952827796094344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -57649,14 +57644,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20:00〜20:59</t>
+          <t>19:00〜19:59</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>119</v>
+        <v>188</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>0.007562277580071174</v>
+        <v>0.01191985797616028</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -57667,14 +57662,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>21:00〜21:59</t>
+          <t>20:00〜20:59</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>0.006481952211489578</v>
+        <v>0.007545016484909967</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -57685,32 +57680,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>22:00〜22:59</t>
+          <t>21:00〜21:59</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>0.004829689883070666</v>
+        <v>0.006467156987065686</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>深夜</t>
+          <t>時間外</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>23:00〜23:59</t>
+          <t>22:00〜22:59</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="C26" s="8" t="n">
-        <v>0.001143873919674631</v>
+        <v>0.004818665990362668</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -57721,75 +57716,75 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>23:00〜23:59</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>20</v>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>0.00126806999746386</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>深夜</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>15736</v>
-      </c>
-      <c r="C27" t="n">
+      <c r="B28" t="n">
+        <v>15772</v>
+      </c>
+      <c r="C28" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>▼ 曜日別プロンプト数</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>曜日</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>プロンプト数</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>構成比</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>月曜</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>2135</v>
-      </c>
-      <c r="C31" s="8" t="n">
-        <v>0.1356761565836299</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>平日</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>火曜</t>
+          <t>月曜</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2286</v>
+        <v>2170</v>
       </c>
       <c r="C32" s="8" t="n">
-        <v>0.1452719877986782</v>
+        <v>0.1375855947248288</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -57800,14 +57795,14 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>水曜</t>
+          <t>火曜</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4176</v>
+        <v>2287</v>
       </c>
       <c r="C33" s="8" t="n">
-        <v>0.2653787493645145</v>
+        <v>0.1450038042099924</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -57818,14 +57813,14 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>木曜</t>
+          <t>水曜</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3620</v>
+        <v>4176</v>
       </c>
       <c r="C34" s="8" t="n">
-        <v>0.230045754956787</v>
+        <v>0.264773015470454</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -57836,14 +57831,14 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>金曜</t>
+          <t>木曜</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3355</v>
+        <v>3620</v>
       </c>
       <c r="C35" s="8" t="n">
-        <v>0.2132053889171327</v>
+        <v>0.2295206695409586</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -57854,178 +57849,183 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>土曜</t>
+          <t>金曜</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>78</v>
+        <v>3355</v>
       </c>
       <c r="C36" s="8" t="n">
-        <v>0.004956786985256736</v>
+        <v>0.2127187420745625</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>休日</t>
+          <t>平日</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>土曜</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>78</v>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>0.004945472990109054</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>休日</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>日曜</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="B38" t="n">
         <v>86</v>
       </c>
-      <c r="C37" s="8" t="n">
-        <v>0.005465175394001017</v>
-      </c>
-      <c r="D37" t="inlineStr">
+      <c r="C38" s="8" t="n">
+        <v>0.005452700989094598</v>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>休日</t>
         </is>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>▼ 日別推移（プロンプト数・利用者数）</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>プロンプト数</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>利用者数</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>1720</v>
-      </c>
-      <c r="C41" t="n">
-        <v>222</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1316</v>
+        <v>1720</v>
       </c>
       <c r="C42" t="n">
-        <v>183</v>
+        <v>222</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1033</v>
+        <v>1316</v>
       </c>
       <c r="C43" t="n">
-        <v>163</v>
+        <v>183</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>14</v>
+        <v>1033</v>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>土曜</t>
-        </is>
+        <v>163</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="C45" t="n">
         <v>4</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>日曜</t>
+          <t>土曜</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1072</v>
+        <v>42</v>
       </c>
       <c r="C46" t="n">
-        <v>165</v>
+        <v>4</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>日曜</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1215</v>
+        <v>1072</v>
       </c>
       <c r="C47" t="n">
-        <v>173</v>
+        <v>165</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1268</v>
+        <v>1215</v>
       </c>
       <c r="C48" t="n">
         <v>173</v>
@@ -58034,164 +58034,203 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1185</v>
+        <v>1268</v>
       </c>
       <c r="C49" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1323</v>
+        <v>1185</v>
       </c>
       <c r="C50" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>39</v>
+        <v>1323</v>
       </c>
       <c r="C51" t="n">
-        <v>8</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>土曜</t>
-        </is>
+        <v>173</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C52" t="n">
         <v>8</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>日曜</t>
+          <t>土曜</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1063</v>
+        <v>31</v>
       </c>
       <c r="C53" t="n">
-        <v>160</v>
+        <v>8</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>日曜</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1071</v>
+        <v>1063</v>
       </c>
       <c r="C54" t="n">
-        <v>168</v>
+        <v>160</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1188</v>
+        <v>1071</v>
       </c>
       <c r="C55" t="n">
-        <v>183</v>
+        <v>168</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1119</v>
+        <v>1188</v>
       </c>
       <c r="C56" t="n">
-        <v>162</v>
+        <v>183</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>999</v>
+        <v>1119</v>
       </c>
       <c r="C57" t="n">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>25</v>
+        <v>999</v>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>土曜</t>
-        </is>
+        <v>167</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C59" t="n">
         <v>4</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t>土曜</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>13</v>
+      </c>
+      <c r="C60" t="n">
+        <v>4</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
           <t>日曜</t>
         </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>35</v>
+      </c>
+      <c r="C61" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -58223,7 +58262,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>集計期間: 2026-07-01 〜 2026-07-19  ※キーワードは機械的な頻度集計。プレフィックス・テンプレ文も含む。</t>
+          <t>集計期間: 2026-07-01 〜 2026-07-21  ※キーワードは機械的な頻度集計。プレフィックス・テンプレ文も含む。</t>
         </is>
       </c>
     </row>
@@ -58263,10 +58302,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10160</v>
+        <v>10189</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>0.6456532791052364</v>
+        <v>0.6460182602079635</v>
       </c>
     </row>
     <row r="8">
@@ -58276,10 +58315,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2209</v>
+        <v>2212</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>0.1403787493645145</v>
+        <v>0.1402485417195029</v>
       </c>
     </row>
     <row r="9">
@@ -58292,7 +58331,7 @@
         <v>1238</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>0.07867310625317743</v>
+        <v>0.07849353284301293</v>
       </c>
     </row>
     <row r="10">
@@ -58302,10 +58341,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>0.0557956278596848</v>
+        <v>0.05579507988840984</v>
       </c>
     </row>
     <row r="11">
@@ -58315,10 +58354,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>0.03615912557193696</v>
+        <v>0.0362033984275932</v>
       </c>
     </row>
     <row r="12">
@@ -58331,7 +58370,7 @@
         <v>354</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>0.02249618708693442</v>
+        <v>0.02244483895511032</v>
       </c>
     </row>
     <row r="13">
@@ -58344,7 +58383,7 @@
         <v>328</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>0.02084392475851551</v>
+        <v>0.0207963479584073</v>
       </c>
     </row>
     <row r="14">
@@ -58367,7 +58406,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15736</v>
+        <v>15772</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
@@ -58405,10 +58444,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>0.05001270971021861</v>
+        <v>0.05021557189956886</v>
       </c>
     </row>
     <row r="20">
@@ -58418,10 +58457,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14949</v>
+        <v>14980</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>0.9499872902897813</v>
+        <v>0.9497844281004312</v>
       </c>
     </row>
     <row r="21"/>
@@ -58495,9 +58534,9 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>157.4</v>
-      </c>
-      <c r="C27" t="n">
+        <v>157.1</v>
+      </c>
+      <c r="C27" s="8" t="n">
         <v>28</v>
       </c>
     </row>
@@ -58508,9 +58547,9 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>147.4</v>
-      </c>
-      <c r="C28" s="8" t="n">
+        <v>147.3</v>
+      </c>
+      <c r="C28" t="n">
         <v>34</v>
       </c>
     </row>
@@ -58521,7 +58560,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>74.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="C29" t="n">
         <v>28</v>
@@ -58567,7 +58606,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3745</v>
+        <v>3747</v>
       </c>
     </row>
     <row r="35">
@@ -58577,7 +58616,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3493</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="36">
@@ -58587,7 +58626,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3483</v>
+        <v>3488</v>
       </c>
     </row>
     <row r="37">
@@ -58597,7 +58636,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3399</v>
+        <v>3403</v>
       </c>
     </row>
     <row r="38">
@@ -58607,7 +58646,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3346</v>
+        <v>3350</v>
       </c>
     </row>
     <row r="39">
@@ -58617,7 +58656,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3344</v>
+        <v>3348</v>
       </c>
     </row>
     <row r="40">
@@ -58627,7 +58666,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3325</v>
+        <v>3331</v>
       </c>
     </row>
     <row r="41">
@@ -58637,7 +58676,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3125</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="42">
@@ -58647,7 +58686,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3124</v>
+        <v>3129</v>
       </c>
     </row>
     <row r="43">
@@ -58657,7 +58696,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3120</v>
+        <v>3125</v>
       </c>
     </row>
     <row r="44">
@@ -58667,7 +58706,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3031</v>
+        <v>3035</v>
       </c>
     </row>
     <row r="45">
@@ -58677,7 +58716,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2952</v>
+        <v>2956</v>
       </c>
     </row>
     <row r="46">
@@ -58687,7 +58726,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2636</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="47">
@@ -58697,7 +58736,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2478</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="48">
@@ -58707,7 +58746,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2379</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="49">
@@ -58717,7 +58756,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2245</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="50">
@@ -58727,7 +58766,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2230</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="51">
@@ -58737,7 +58776,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2192</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="52">
@@ -58747,7 +58786,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2191</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="53">
@@ -58757,7 +58796,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2191</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="54">
@@ -58767,7 +58806,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2120</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="55">
@@ -58777,7 +58816,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1944</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="56">
@@ -58787,7 +58826,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1834</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="57">
@@ -58797,7 +58836,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1739</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="58">
@@ -58817,7 +58856,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1396</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="60">
@@ -58837,7 +58876,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1382</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="62">
@@ -58847,7 +58886,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="63">
@@ -58857,7 +58896,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1343</v>
+        <v>1344</v>
       </c>
     </row>
   </sheetData>
@@ -58871,7 +58910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -58893,7 +58932,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>集計期間: 2026-07-01 〜 2026-07-19</t>
+          <t>集計期間: 2026-07-01 〜 2026-07-21</t>
         </is>
       </c>
     </row>
@@ -59445,6 +59484,60 @@
       </c>
       <c r="G23" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>7</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>7</v>
+      </c>
+      <c r="F24" t="n">
+        <v>491</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>491</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -59497,11 +59590,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15736</v>
+        <v>15772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ログ実数(2026-07-01〜2026-07-19)</t>
+          <t>ログ実数(2026-07-01〜2026-07-21)</t>
         </is>
       </c>
     </row>
@@ -59512,7 +59605,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -59697,7 +59790,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【年換算】実利用19日の実績を年間業務日数で単純外挿した粗い参考値。導入初期データのため過大/過小の双方に振れます。</t>
+          <t>【年換算】実利用21日の実績を年間業務日数で単純外挿した粗い参考値。導入初期データのため過大/過小の双方に振れます。</t>
         </is>
       </c>
     </row>
@@ -59771,7 +59864,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2418510</v>
+        <v>2421731</v>
       </c>
       <c r="C27">
         <f>ROUND(B27/B23/60,0)</f>
@@ -59790,7 +59883,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>20799311</v>
+        <v>20863969</v>
       </c>
       <c r="C28">
         <f>ROUND(B28/B24/60,0)</f>
@@ -59809,7 +59902,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.104</v>
+        <v>4.098</v>
       </c>
       <c r="C29">
         <f>ROUND(C28/B29,0)</f>
@@ -59866,7 +59959,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>【前提】入出力文字数はログ集計値（プレフィックス除く）。質問数C=総プロンプト数÷セッション数(ユーザーごとに発言間隔が60分を超えたら新セッション、として自動算出。今回のセッション数=3834)</t>
+          <t>【前提】入出力文字数はログ集計値（プレフィックス除く）。質問数C=総プロンプト数÷セッション数(ユーザーごとに発言間隔が60分を超えたら新セッション、として自動算出。今回のセッション数=3849)</t>
         </is>
       </c>
     </row>

--- a/reports/QommonsAI利用集計_2026-07.xlsx
+++ b/reports/QommonsAI利用集計_2026-07.xlsx
@@ -457,18 +457,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I140"/>
+  <dimension ref="A1:J140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,7 +482,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>集計期間: 2026-07-01 〜 2026-07-21  ／ 利用回数=プロンプト(質問)数  ／ 使用文字数=入力+出力(プレフィックス除く)</t>
+          <t>集計期間: 2026-07-01 〜 2026-07-21  ／ 利用回数=プロンプト(質問)数  ／ 使用文字数=入力+出力(プレフィックス除く)  ／ 利用率=利用者数÷登録者数(利用開始済み)</t>
         </is>
       </c>
     </row>
@@ -493,40 +494,47 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>登録者数</t>
+          <t>登録者数
+(全体)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>登録者数
+(利用開始済み)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>利用者数</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>利用率</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>プロンプト数</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>応答数</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>合計レコード</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>使用文字数</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>1人あたり
 プロンプト数(利用者)</t>
@@ -543,24 +551,27 @@
         <v>10</v>
       </c>
       <c r="C5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" t="n">
         <v>11</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="E5" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>1001</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>980</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>1981</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>1779787</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>91</v>
       </c>
     </row>
@@ -576,22 +587,25 @@
       <c r="C6" t="n">
         <v>11</v>
       </c>
-      <c r="D6" s="4" t="n">
-        <v>0.8461538461538461</v>
-      </c>
-      <c r="E6" t="n">
+      <c r="D6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
         <v>982</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>971</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>1953</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>1170131</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>89</v>
       </c>
     </row>
@@ -605,24 +619,27 @@
         <v>8</v>
       </c>
       <c r="C7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" t="n">
         <v>6</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="E7" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>782</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>771</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>1553</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>1234438</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>130</v>
       </c>
     </row>
@@ -638,22 +655,25 @@
       <c r="C8" t="n">
         <v>10</v>
       </c>
-      <c r="D8" s="4" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
         <v>699</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>693</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>1392</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>1054378</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>70</v>
       </c>
     </row>
@@ -667,24 +687,27 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
+        <v>16</v>
+      </c>
+      <c r="D9" t="n">
         <v>12</v>
       </c>
-      <c r="D9" s="4" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="E9" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F9" t="n">
         <v>583</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>580</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>1163</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>898619</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>49</v>
       </c>
     </row>
@@ -698,24 +721,27 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
+        <v>21</v>
+      </c>
+      <c r="D10" t="n">
         <v>17</v>
       </c>
-      <c r="D10" s="4" t="n">
-        <v>0.5666666666666667</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="E10" s="4" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="F10" t="n">
         <v>536</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>532</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>1068</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>842215</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>32</v>
       </c>
     </row>
@@ -731,22 +757,25 @@
       <c r="C11" t="n">
         <v>7</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>492</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>487</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>979</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>748956</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>70</v>
       </c>
     </row>
@@ -762,22 +791,25 @@
       <c r="C12" t="n">
         <v>5</v>
       </c>
-      <c r="D12" s="4" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
         <v>433</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>430</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>863</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>760047</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>87</v>
       </c>
     </row>
@@ -791,24 +823,27 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
+        <v>15</v>
+      </c>
+      <c r="D13" t="n">
         <v>13</v>
       </c>
-      <c r="D13" s="4" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="E13" t="n">
+      <c r="E13" s="4" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="F13" t="n">
         <v>426</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>425</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>851</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>657292</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>33</v>
       </c>
     </row>
@@ -824,22 +859,25 @@
       <c r="C14" t="n">
         <v>3</v>
       </c>
-      <c r="D14" s="4" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="E14" t="n">
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
         <v>416</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>407</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>823</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>563572</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>139</v>
       </c>
     </row>
@@ -855,22 +893,25 @@
       <c r="C15" t="n">
         <v>6</v>
       </c>
-      <c r="D15" s="4" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="E15" t="n">
+      <c r="D15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
         <v>371</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>368</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>739</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>481829</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>62</v>
       </c>
     </row>
@@ -884,24 +925,27 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
+        <v>9</v>
+      </c>
+      <c r="D16" t="n">
         <v>8</v>
       </c>
-      <c r="D16" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="E16" t="n">
+      <c r="E16" s="4" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="F16" t="n">
         <v>343</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>336</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>679</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>516173</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>43</v>
       </c>
     </row>
@@ -917,22 +961,25 @@
       <c r="C17" t="n">
         <v>8</v>
       </c>
-      <c r="D17" s="4" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="E17" t="n">
+      <c r="D17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
         <v>331</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>330</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>661</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>525196</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>41</v>
       </c>
     </row>
@@ -948,22 +995,25 @@
       <c r="C18" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E18" t="n">
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
         <v>314</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>312</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>626</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>404145</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>314</v>
       </c>
     </row>
@@ -977,24 +1027,27 @@
         <v>13</v>
       </c>
       <c r="C19" t="n">
+        <v>11</v>
+      </c>
+      <c r="D19" t="n">
         <v>9</v>
       </c>
-      <c r="D19" s="4" t="n">
-        <v>0.6923076923076923</v>
-      </c>
-      <c r="E19" t="n">
+      <c r="E19" s="4" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="F19" t="n">
         <v>308</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>305</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>613</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>295382</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>34</v>
       </c>
     </row>
@@ -1010,22 +1063,25 @@
       <c r="C20" t="n">
         <v>7</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E20" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>303</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>299</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>602</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>449750</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>43</v>
       </c>
     </row>
@@ -1039,24 +1095,27 @@
         <v>11</v>
       </c>
       <c r="C21" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" t="n">
         <v>8</v>
       </c>
-      <c r="D21" s="4" t="n">
-        <v>0.7272727272727273</v>
-      </c>
-      <c r="E21" t="n">
+      <c r="E21" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F21" t="n">
         <v>288</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>285</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>573</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>417501</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>36</v>
       </c>
     </row>
@@ -1070,24 +1129,27 @@
         <v>25</v>
       </c>
       <c r="C22" t="n">
+        <v>16</v>
+      </c>
+      <c r="D22" t="n">
         <v>9</v>
       </c>
-      <c r="D22" s="4" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E22" t="n">
+      <c r="E22" s="4" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="F22" t="n">
         <v>253</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>251</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>504</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>347196</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>28</v>
       </c>
     </row>
@@ -1101,24 +1163,27 @@
         <v>7</v>
       </c>
       <c r="C23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" t="n">
         <v>4</v>
       </c>
-      <c r="D23" s="4" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="E23" t="n">
+      <c r="E23" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F23" t="n">
         <v>245</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>242</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>487</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>334187</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>61</v>
       </c>
     </row>
@@ -1132,24 +1197,27 @@
         <v>8</v>
       </c>
       <c r="C24" t="n">
+        <v>6</v>
+      </c>
+      <c r="D24" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E24" t="n">
+      <c r="E24" s="4" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="F24" t="n">
         <v>232</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>231</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>463</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>370708</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>46</v>
       </c>
     </row>
@@ -1165,22 +1233,25 @@
       <c r="C25" t="n">
         <v>4</v>
       </c>
-      <c r="D25" s="4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E25" t="n">
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
         <v>229</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>225</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>454</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>307643</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>57</v>
       </c>
     </row>
@@ -1194,24 +1265,27 @@
         <v>21</v>
       </c>
       <c r="C26" t="n">
+        <v>16</v>
+      </c>
+      <c r="D26" t="n">
         <v>12</v>
       </c>
-      <c r="D26" s="4" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="E26" t="n">
+      <c r="E26" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F26" t="n">
         <v>224</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>221</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>445</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>307184</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1225,24 +1299,27 @@
         <v>18</v>
       </c>
       <c r="C27" t="n">
+        <v>11</v>
+      </c>
+      <c r="D27" t="n">
         <v>9</v>
       </c>
-      <c r="D27" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E27" t="n">
+      <c r="E27" s="4" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="F27" t="n">
         <v>212</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>210</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>422</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>236511</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>24</v>
       </c>
     </row>
@@ -1256,24 +1333,27 @@
         <v>10</v>
       </c>
       <c r="C28" t="n">
+        <v>8</v>
+      </c>
+      <c r="D28" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E28" t="n">
+      <c r="E28" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="F28" t="n">
         <v>192</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>189</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>381</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>280997</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>38</v>
       </c>
     </row>
@@ -1287,24 +1367,27 @@
         <v>6</v>
       </c>
       <c r="C29" t="n">
+        <v>6</v>
+      </c>
+      <c r="D29" t="n">
         <v>5</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="E29" s="4" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>185</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>181</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>366</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>341325</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>37</v>
       </c>
     </row>
@@ -1318,24 +1401,27 @@
         <v>7</v>
       </c>
       <c r="C30" t="n">
+        <v>6</v>
+      </c>
+      <c r="D30" t="n">
         <v>5</v>
       </c>
-      <c r="D30" s="4" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="E30" t="n">
+      <c r="E30" s="4" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="F30" t="n">
         <v>154</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>151</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>305</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>254351</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>31</v>
       </c>
     </row>
@@ -1351,22 +1437,25 @@
       <c r="C31" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="E31" t="n">
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
         <v>145</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>142</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>287</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>249255</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>72</v>
       </c>
     </row>
@@ -1382,22 +1471,25 @@
       <c r="C32" t="n">
         <v>6</v>
       </c>
-      <c r="D32" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="E32" t="n">
+      <c r="D32" t="n">
+        <v>6</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
         <v>134</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>133</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>267</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>179880</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>22</v>
       </c>
     </row>
@@ -1411,24 +1503,27 @@
         <v>4</v>
       </c>
       <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E33" t="n">
+      <c r="E33" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F33" t="n">
         <v>130</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>127</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>257</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>236039</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>130</v>
       </c>
     </row>
@@ -1444,22 +1539,25 @@
       <c r="C34" t="n">
         <v>3</v>
       </c>
-      <c r="D34" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E34" t="n">
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
         <v>117</v>
       </c>
-      <c r="F34" t="n">
+      <c r="G34" t="n">
         <v>118</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>235</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>146522</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>39</v>
       </c>
     </row>
@@ -1473,24 +1571,27 @@
         <v>6</v>
       </c>
       <c r="C35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" t="n">
         <v>4</v>
       </c>
-      <c r="D35" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="E35" t="n">
-        <v>116</v>
+      <c r="E35" s="4" t="n">
+        <v>0.8</v>
       </c>
       <c r="F35" t="n">
         <v>116</v>
       </c>
       <c r="G35" t="n">
+        <v>116</v>
+      </c>
+      <c r="H35" t="n">
         <v>232</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>159650</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>29</v>
       </c>
     </row>
@@ -1506,22 +1607,25 @@
       <c r="C36" t="n">
         <v>7</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" t="n">
+        <v>7</v>
+      </c>
+      <c r="E36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>113</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>112</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>225</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>181464</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1535,24 +1639,27 @@
         <v>9</v>
       </c>
       <c r="C37" t="n">
+        <v>6</v>
+      </c>
+      <c r="D37" t="n">
         <v>4</v>
       </c>
-      <c r="D37" s="4" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="E37" t="n">
+      <c r="E37" s="4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F37" t="n">
         <v>108</v>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>107</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>215</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>178315</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>27</v>
       </c>
     </row>
@@ -1568,22 +1675,25 @@
       <c r="C38" t="n">
         <v>6</v>
       </c>
-      <c r="D38" s="4" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="E38" t="n">
+      <c r="D38" t="n">
+        <v>6</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
         <v>107</v>
       </c>
-      <c r="F38" t="n">
+      <c r="G38" t="n">
         <v>106</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>213</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>166891</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>18</v>
       </c>
     </row>
@@ -1599,22 +1709,25 @@
       <c r="C39" t="n">
         <v>5</v>
       </c>
-      <c r="D39" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E39" t="n">
+      <c r="D39" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
         <v>106</v>
       </c>
-      <c r="F39" t="n">
+      <c r="G39" t="n">
         <v>104</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>210</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>149726</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>21</v>
       </c>
     </row>
@@ -1628,24 +1741,27 @@
         <v>10</v>
       </c>
       <c r="C40" t="n">
+        <v>5</v>
+      </c>
+      <c r="D40" t="n">
         <v>4</v>
       </c>
-      <c r="D40" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E40" t="n">
+      <c r="E40" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F40" t="n">
         <v>106</v>
       </c>
-      <c r="F40" t="n">
+      <c r="G40" t="n">
         <v>104</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>210</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>144597</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>26</v>
       </c>
     </row>
@@ -1661,22 +1777,25 @@
       <c r="C41" t="n">
         <v>3</v>
       </c>
-      <c r="D41" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E41" t="n">
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
         <v>102</v>
       </c>
-      <c r="F41" t="n">
+      <c r="G41" t="n">
         <v>101</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>203</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>170155</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>34</v>
       </c>
     </row>
@@ -1690,24 +1809,27 @@
         <v>7</v>
       </c>
       <c r="C42" t="n">
+        <v>6</v>
+      </c>
+      <c r="D42" t="n">
         <v>5</v>
       </c>
-      <c r="D42" s="4" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="E42" t="n">
-        <v>102</v>
+      <c r="E42" s="4" t="n">
+        <v>0.8333333333333334</v>
       </c>
       <c r="F42" t="n">
         <v>102</v>
       </c>
       <c r="G42" t="n">
+        <v>102</v>
+      </c>
+      <c r="H42" t="n">
         <v>204</v>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>119985</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1723,22 +1845,25 @@
       <c r="C43" t="n">
         <v>3</v>
       </c>
-      <c r="D43" s="4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E43" t="n">
+      <c r="D43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
         <v>102</v>
       </c>
-      <c r="F43" t="n">
+      <c r="G43" t="n">
         <v>97</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>199</v>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>146989</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>34</v>
       </c>
     </row>
@@ -1754,22 +1879,25 @@
       <c r="C44" t="n">
         <v>5</v>
       </c>
-      <c r="D44" s="4" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="E44" t="n">
+      <c r="D44" t="n">
+        <v>5</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
         <v>99</v>
       </c>
-      <c r="F44" t="n">
+      <c r="G44" t="n">
         <v>97</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>196</v>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>134932</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1783,24 +1911,27 @@
         <v>2</v>
       </c>
       <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="n">
         <v>1</v>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="E45" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>99</v>
       </c>
-      <c r="F45" t="n">
+      <c r="G45" t="n">
         <v>98</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>197</v>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>178741</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>99</v>
       </c>
     </row>
@@ -1816,22 +1947,25 @@
       <c r="C46" t="n">
         <v>4</v>
       </c>
-      <c r="D46" s="4" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="E46" t="n">
+      <c r="D46" t="n">
+        <v>4</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
         <v>96</v>
       </c>
-      <c r="F46" t="n">
+      <c r="G46" t="n">
         <v>95</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>191</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>151027</v>
       </c>
-      <c r="I46" t="n">
+      <c r="J46" t="n">
         <v>24</v>
       </c>
     </row>
@@ -1845,24 +1979,27 @@
         <v>8</v>
       </c>
       <c r="C47" t="n">
+        <v>6</v>
+      </c>
+      <c r="D47" t="n">
         <v>4</v>
       </c>
-      <c r="D47" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E47" t="n">
+      <c r="E47" s="4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F47" t="n">
         <v>95</v>
       </c>
-      <c r="F47" t="n">
+      <c r="G47" t="n">
         <v>93</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>188</v>
       </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>129166</v>
       </c>
-      <c r="I47" t="n">
+      <c r="J47" t="n">
         <v>24</v>
       </c>
     </row>
@@ -1876,24 +2013,27 @@
         <v>12</v>
       </c>
       <c r="C48" t="n">
+        <v>7</v>
+      </c>
+      <c r="D48" t="n">
         <v>6</v>
       </c>
-      <c r="D48" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E48" t="n">
+      <c r="E48" s="4" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="F48" t="n">
         <v>93</v>
       </c>
-      <c r="F48" t="n">
+      <c r="G48" t="n">
         <v>90</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>183</v>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>130292</v>
       </c>
-      <c r="I48" t="n">
+      <c r="J48" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1907,24 +2047,27 @@
         <v>11</v>
       </c>
       <c r="C49" t="n">
+        <v>8</v>
+      </c>
+      <c r="D49" t="n">
         <v>7</v>
       </c>
-      <c r="D49" s="4" t="n">
-        <v>0.6363636363636364</v>
-      </c>
-      <c r="E49" t="n">
-        <v>92</v>
+      <c r="E49" s="4" t="n">
+        <v>0.875</v>
       </c>
       <c r="F49" t="n">
         <v>92</v>
       </c>
       <c r="G49" t="n">
+        <v>92</v>
+      </c>
+      <c r="H49" t="n">
         <v>184</v>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>133496</v>
       </c>
-      <c r="I49" t="n">
+      <c r="J49" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1940,22 +2083,25 @@
       <c r="C50" t="n">
         <v>6</v>
       </c>
-      <c r="D50" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E50" t="n">
+      <c r="D50" t="n">
+        <v>6</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="n">
         <v>91</v>
       </c>
-      <c r="F50" t="n">
+      <c r="G50" t="n">
         <v>89</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>180</v>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>134223</v>
       </c>
-      <c r="I50" t="n">
+      <c r="J50" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1969,24 +2115,27 @@
         <v>6</v>
       </c>
       <c r="C51" t="n">
+        <v>6</v>
+      </c>
+      <c r="D51" t="n">
         <v>5</v>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="E51" s="4" t="n">
         <v>0.8333333333333334</v>
-      </c>
-      <c r="E51" t="n">
-        <v>86</v>
       </c>
       <c r="F51" t="n">
         <v>86</v>
       </c>
       <c r="G51" t="n">
+        <v>86</v>
+      </c>
+      <c r="H51" t="n">
         <v>172</v>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>126152</v>
       </c>
-      <c r="I51" t="n">
+      <c r="J51" t="n">
         <v>17</v>
       </c>
     </row>
@@ -2000,24 +2149,27 @@
         <v>3</v>
       </c>
       <c r="C52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" t="n">
         <v>2</v>
       </c>
-      <c r="D52" s="4" t="n">
+      <c r="E52" s="4" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>85</v>
       </c>
-      <c r="F52" t="n">
+      <c r="G52" t="n">
         <v>84</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>169</v>
       </c>
-      <c r="H52" t="n">
+      <c r="I52" t="n">
         <v>94654</v>
       </c>
-      <c r="I52" t="n">
+      <c r="J52" t="n">
         <v>42</v>
       </c>
     </row>
@@ -2033,22 +2185,25 @@
       <c r="C53" t="n">
         <v>6</v>
       </c>
-      <c r="D53" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="E53" t="n">
+      <c r="D53" t="n">
+        <v>6</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="n">
         <v>82</v>
       </c>
-      <c r="F53" t="n">
+      <c r="G53" t="n">
         <v>79</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>161</v>
       </c>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
         <v>119272</v>
       </c>
-      <c r="I53" t="n">
+      <c r="J53" t="n">
         <v>14</v>
       </c>
     </row>
@@ -2064,22 +2219,25 @@
       <c r="C54" t="n">
         <v>2</v>
       </c>
-      <c r="D54" s="4" t="n">
+      <c r="D54" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E54" t="n">
+      <c r="F54" t="n">
         <v>82</v>
       </c>
-      <c r="F54" t="n">
+      <c r="G54" t="n">
         <v>80</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>162</v>
       </c>
-      <c r="H54" t="n">
+      <c r="I54" t="n">
         <v>140602</v>
       </c>
-      <c r="I54" t="n">
+      <c r="J54" t="n">
         <v>41</v>
       </c>
     </row>
@@ -2095,22 +2253,25 @@
       <c r="C55" t="n">
         <v>4</v>
       </c>
-      <c r="D55" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="E55" t="n">
+      <c r="D55" t="n">
+        <v>4</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="n">
         <v>80</v>
       </c>
-      <c r="F55" t="n">
+      <c r="G55" t="n">
         <v>81</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>161</v>
       </c>
-      <c r="H55" t="n">
+      <c r="I55" t="n">
         <v>118914</v>
       </c>
-      <c r="I55" t="n">
+      <c r="J55" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2126,22 +2287,25 @@
       <c r="C56" t="n">
         <v>3</v>
       </c>
-      <c r="D56" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E56" t="n">
+      <c r="D56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" t="n">
         <v>79</v>
       </c>
-      <c r="F56" t="n">
+      <c r="G56" t="n">
         <v>77</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>156</v>
       </c>
-      <c r="H56" t="n">
+      <c r="I56" t="n">
         <v>102286</v>
       </c>
-      <c r="I56" t="n">
+      <c r="J56" t="n">
         <v>26</v>
       </c>
     </row>
@@ -2155,24 +2319,27 @@
         <v>8</v>
       </c>
       <c r="C57" t="n">
+        <v>6</v>
+      </c>
+      <c r="D57" t="n">
         <v>5</v>
       </c>
-      <c r="D57" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E57" t="n">
-        <v>79</v>
+      <c r="E57" s="4" t="n">
+        <v>0.8333333333333334</v>
       </c>
       <c r="F57" t="n">
         <v>79</v>
       </c>
       <c r="G57" t="n">
+        <v>79</v>
+      </c>
+      <c r="H57" t="n">
         <v>158</v>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>125691</v>
       </c>
-      <c r="I57" t="n">
+      <c r="J57" t="n">
         <v>16</v>
       </c>
     </row>
@@ -2186,24 +2353,27 @@
         <v>9</v>
       </c>
       <c r="C58" t="n">
+        <v>8</v>
+      </c>
+      <c r="D58" t="n">
         <v>4</v>
       </c>
-      <c r="D58" s="4" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="E58" t="n">
-        <v>74</v>
+      <c r="E58" s="4" t="n">
+        <v>0.5</v>
       </c>
       <c r="F58" t="n">
         <v>74</v>
       </c>
       <c r="G58" t="n">
+        <v>74</v>
+      </c>
+      <c r="H58" t="n">
         <v>148</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>108160</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>18</v>
       </c>
     </row>
@@ -2219,22 +2389,25 @@
       <c r="C59" t="n">
         <v>2</v>
       </c>
-      <c r="D59" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E59" t="n">
+      <c r="D59" t="n">
+        <v>2</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="n">
         <v>73</v>
       </c>
-      <c r="F59" t="n">
+      <c r="G59" t="n">
         <v>72</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>145</v>
       </c>
-      <c r="H59" t="n">
+      <c r="I59" t="n">
         <v>98484</v>
       </c>
-      <c r="I59" t="n">
+      <c r="J59" t="n">
         <v>36</v>
       </c>
     </row>
@@ -2248,24 +2421,27 @@
         <v>8</v>
       </c>
       <c r="C60" t="n">
+        <v>4</v>
+      </c>
+      <c r="D60" t="n">
         <v>2</v>
       </c>
-      <c r="D60" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E60" t="n">
+      <c r="E60" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F60" t="n">
         <v>70</v>
       </c>
-      <c r="F60" t="n">
+      <c r="G60" t="n">
         <v>69</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>139</v>
       </c>
-      <c r="H60" t="n">
+      <c r="I60" t="n">
         <v>88769</v>
       </c>
-      <c r="I60" t="n">
+      <c r="J60" t="n">
         <v>35</v>
       </c>
     </row>
@@ -2281,22 +2457,25 @@
       <c r="C61" t="n">
         <v>3</v>
       </c>
-      <c r="D61" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E61" t="n">
-        <v>67</v>
+      <c r="D61" t="n">
+        <v>3</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F61" t="n">
         <v>67</v>
       </c>
       <c r="G61" t="n">
+        <v>67</v>
+      </c>
+      <c r="H61" t="n">
         <v>134</v>
       </c>
-      <c r="H61" t="n">
+      <c r="I61" t="n">
         <v>93382</v>
       </c>
-      <c r="I61" t="n">
+      <c r="J61" t="n">
         <v>22</v>
       </c>
     </row>
@@ -2310,24 +2489,27 @@
         <v>8</v>
       </c>
       <c r="C62" t="n">
+        <v>6</v>
+      </c>
+      <c r="D62" t="n">
         <v>5</v>
       </c>
-      <c r="D62" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E62" t="n">
-        <v>64</v>
+      <c r="E62" s="4" t="n">
+        <v>0.8333333333333334</v>
       </c>
       <c r="F62" t="n">
         <v>64</v>
       </c>
       <c r="G62" t="n">
+        <v>64</v>
+      </c>
+      <c r="H62" t="n">
         <v>128</v>
       </c>
-      <c r="H62" t="n">
+      <c r="I62" t="n">
         <v>89894</v>
       </c>
-      <c r="I62" t="n">
+      <c r="J62" t="n">
         <v>13</v>
       </c>
     </row>
@@ -2341,24 +2523,27 @@
         <v>7</v>
       </c>
       <c r="C63" t="n">
+        <v>4</v>
+      </c>
+      <c r="D63" t="n">
         <v>3</v>
       </c>
-      <c r="D63" s="4" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="E63" t="n">
-        <v>63</v>
+      <c r="E63" s="4" t="n">
+        <v>0.75</v>
       </c>
       <c r="F63" t="n">
         <v>63</v>
       </c>
       <c r="G63" t="n">
+        <v>63</v>
+      </c>
+      <c r="H63" t="n">
         <v>126</v>
       </c>
-      <c r="H63" t="n">
+      <c r="I63" t="n">
         <v>108299</v>
       </c>
-      <c r="I63" t="n">
+      <c r="J63" t="n">
         <v>21</v>
       </c>
     </row>
@@ -2374,22 +2559,25 @@
       <c r="C64" t="n">
         <v>1</v>
       </c>
-      <c r="D64" s="4" t="n">
+      <c r="D64" t="n">
         <v>1</v>
       </c>
-      <c r="E64" t="n">
-        <v>62</v>
+      <c r="E64" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>62</v>
       </c>
       <c r="G64" t="n">
+        <v>62</v>
+      </c>
+      <c r="H64" t="n">
         <v>124</v>
       </c>
-      <c r="H64" t="n">
+      <c r="I64" t="n">
         <v>138594</v>
       </c>
-      <c r="I64" t="n">
+      <c r="J64" t="n">
         <v>62</v>
       </c>
     </row>
@@ -2403,24 +2591,27 @@
         <v>14</v>
       </c>
       <c r="C65" t="n">
+        <v>6</v>
+      </c>
+      <c r="D65" t="n">
         <v>5</v>
       </c>
-      <c r="D65" s="4" t="n">
-        <v>0.3571428571428572</v>
-      </c>
-      <c r="E65" t="n">
+      <c r="E65" s="4" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="F65" t="n">
         <v>61</v>
       </c>
-      <c r="F65" t="n">
+      <c r="G65" t="n">
         <v>62</v>
       </c>
-      <c r="G65" t="n">
+      <c r="H65" t="n">
         <v>123</v>
       </c>
-      <c r="H65" t="n">
+      <c r="I65" t="n">
         <v>92974</v>
       </c>
-      <c r="I65" t="n">
+      <c r="J65" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2436,22 +2627,25 @@
       <c r="C66" t="n">
         <v>2</v>
       </c>
-      <c r="D66" s="4" t="n">
+      <c r="D66" t="n">
+        <v>2</v>
+      </c>
+      <c r="E66" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E66" t="n">
+      <c r="F66" t="n">
         <v>60</v>
       </c>
-      <c r="F66" t="n">
+      <c r="G66" t="n">
         <v>59</v>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>119</v>
       </c>
-      <c r="H66" t="n">
+      <c r="I66" t="n">
         <v>103077</v>
       </c>
-      <c r="I66" t="n">
+      <c r="J66" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2467,22 +2661,25 @@
       <c r="C67" t="n">
         <v>2</v>
       </c>
-      <c r="D67" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="E67" t="n">
+      <c r="D67" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" t="n">
         <v>60</v>
       </c>
-      <c r="F67" t="n">
+      <c r="G67" t="n">
         <v>59</v>
       </c>
-      <c r="G67" t="n">
+      <c r="H67" t="n">
         <v>119</v>
       </c>
-      <c r="H67" t="n">
+      <c r="I67" t="n">
         <v>96131</v>
       </c>
-      <c r="I67" t="n">
+      <c r="J67" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2498,22 +2695,25 @@
       <c r="C68" t="n">
         <v>3</v>
       </c>
-      <c r="D68" s="4" t="n">
+      <c r="D68" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="E68" t="n">
-        <v>59</v>
       </c>
       <c r="F68" t="n">
         <v>59</v>
       </c>
       <c r="G68" t="n">
+        <v>59</v>
+      </c>
+      <c r="H68" t="n">
         <v>118</v>
       </c>
-      <c r="H68" t="n">
+      <c r="I68" t="n">
         <v>99106</v>
       </c>
-      <c r="I68" t="n">
+      <c r="J68" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2529,22 +2729,25 @@
       <c r="C69" t="n">
         <v>5</v>
       </c>
-      <c r="D69" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E69" t="n">
-        <v>58</v>
+      <c r="D69" t="n">
+        <v>5</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F69" t="n">
         <v>58</v>
       </c>
       <c r="G69" t="n">
+        <v>58</v>
+      </c>
+      <c r="H69" t="n">
         <v>116</v>
       </c>
-      <c r="H69" t="n">
+      <c r="I69" t="n">
         <v>78484</v>
       </c>
-      <c r="I69" t="n">
+      <c r="J69" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2560,22 +2763,25 @@
       <c r="C70" t="n">
         <v>1</v>
       </c>
-      <c r="D70" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E70" t="n">
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" t="n">
         <v>57</v>
       </c>
-      <c r="F70" t="n">
+      <c r="G70" t="n">
         <v>56</v>
       </c>
-      <c r="G70" t="n">
+      <c r="H70" t="n">
         <v>113</v>
       </c>
-      <c r="H70" t="n">
+      <c r="I70" t="n">
         <v>76180</v>
       </c>
-      <c r="I70" t="n">
+      <c r="J70" t="n">
         <v>57</v>
       </c>
     </row>
@@ -2589,24 +2795,27 @@
         <v>3</v>
       </c>
       <c r="C71" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" t="n">
         <v>1</v>
       </c>
-      <c r="D71" s="4" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="E71" t="n">
+      <c r="E71" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F71" t="n">
         <v>56</v>
       </c>
-      <c r="F71" t="n">
+      <c r="G71" t="n">
         <v>55</v>
       </c>
-      <c r="G71" t="n">
+      <c r="H71" t="n">
         <v>111</v>
       </c>
-      <c r="H71" t="n">
+      <c r="I71" t="n">
         <v>94572</v>
       </c>
-      <c r="I71" t="n">
+      <c r="J71" t="n">
         <v>56</v>
       </c>
     </row>
@@ -2620,24 +2829,27 @@
         <v>10</v>
       </c>
       <c r="C72" t="n">
+        <v>6</v>
+      </c>
+      <c r="D72" t="n">
         <v>4</v>
       </c>
-      <c r="D72" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E72" t="n">
-        <v>56</v>
+      <c r="E72" s="4" t="n">
+        <v>0.6666666666666666</v>
       </c>
       <c r="F72" t="n">
         <v>56</v>
       </c>
       <c r="G72" t="n">
+        <v>56</v>
+      </c>
+      <c r="H72" t="n">
         <v>112</v>
       </c>
-      <c r="H72" t="n">
+      <c r="I72" t="n">
         <v>72581</v>
       </c>
-      <c r="I72" t="n">
+      <c r="J72" t="n">
         <v>14</v>
       </c>
     </row>
@@ -2651,24 +2863,27 @@
         <v>8</v>
       </c>
       <c r="C73" t="n">
+        <v>6</v>
+      </c>
+      <c r="D73" t="n">
         <v>3</v>
       </c>
-      <c r="D73" s="4" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E73" t="n">
-        <v>55</v>
+      <c r="E73" s="4" t="n">
+        <v>0.5</v>
       </c>
       <c r="F73" t="n">
         <v>55</v>
       </c>
       <c r="G73" t="n">
+        <v>55</v>
+      </c>
+      <c r="H73" t="n">
         <v>110</v>
       </c>
-      <c r="H73" t="n">
+      <c r="I73" t="n">
         <v>81861</v>
       </c>
-      <c r="I73" t="n">
+      <c r="J73" t="n">
         <v>18</v>
       </c>
     </row>
@@ -2682,24 +2897,27 @@
         <v>12</v>
       </c>
       <c r="C74" t="n">
+        <v>10</v>
+      </c>
+      <c r="D74" t="n">
         <v>8</v>
       </c>
-      <c r="D74" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="E74" t="n">
+      <c r="E74" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F74" t="n">
         <v>55</v>
       </c>
-      <c r="F74" t="n">
+      <c r="G74" t="n">
         <v>53</v>
       </c>
-      <c r="G74" t="n">
+      <c r="H74" t="n">
         <v>108</v>
       </c>
-      <c r="H74" t="n">
+      <c r="I74" t="n">
         <v>54378</v>
       </c>
-      <c r="I74" t="n">
+      <c r="J74" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2715,22 +2933,25 @@
       <c r="C75" t="n">
         <v>1</v>
       </c>
-      <c r="D75" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E75" t="n">
-        <v>55</v>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F75" t="n">
         <v>55</v>
       </c>
       <c r="G75" t="n">
+        <v>55</v>
+      </c>
+      <c r="H75" t="n">
         <v>110</v>
       </c>
-      <c r="H75" t="n">
+      <c r="I75" t="n">
         <v>105930</v>
       </c>
-      <c r="I75" t="n">
+      <c r="J75" t="n">
         <v>55</v>
       </c>
     </row>
@@ -2746,22 +2967,25 @@
       <c r="C76" t="n">
         <v>5</v>
       </c>
-      <c r="D76" s="4" t="n">
-        <v>0.2631578947368421</v>
-      </c>
-      <c r="E76" t="n">
+      <c r="D76" t="n">
+        <v>5</v>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" t="n">
         <v>53</v>
       </c>
-      <c r="F76" t="n">
+      <c r="G76" t="n">
         <v>52</v>
       </c>
-      <c r="G76" t="n">
+      <c r="H76" t="n">
         <v>105</v>
       </c>
-      <c r="H76" t="n">
+      <c r="I76" t="n">
         <v>66548</v>
       </c>
-      <c r="I76" t="n">
+      <c r="J76" t="n">
         <v>11</v>
       </c>
     </row>
@@ -2777,22 +3001,25 @@
       <c r="C77" t="n">
         <v>3</v>
       </c>
-      <c r="D77" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E77" t="n">
-        <v>51</v>
+      <c r="D77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F77" t="n">
         <v>51</v>
       </c>
       <c r="G77" t="n">
+        <v>51</v>
+      </c>
+      <c r="H77" t="n">
         <v>102</v>
       </c>
-      <c r="H77" t="n">
+      <c r="I77" t="n">
         <v>69866</v>
       </c>
-      <c r="I77" t="n">
+      <c r="J77" t="n">
         <v>17</v>
       </c>
     </row>
@@ -2806,24 +3033,27 @@
         <v>2</v>
       </c>
       <c r="C78" t="n">
+        <v>2</v>
+      </c>
+      <c r="D78" t="n">
         <v>1</v>
       </c>
-      <c r="D78" s="4" t="n">
+      <c r="E78" s="4" t="n">
         <v>0.5</v>
-      </c>
-      <c r="E78" t="n">
-        <v>49</v>
       </c>
       <c r="F78" t="n">
         <v>49</v>
       </c>
       <c r="G78" t="n">
+        <v>49</v>
+      </c>
+      <c r="H78" t="n">
         <v>98</v>
       </c>
-      <c r="H78" t="n">
+      <c r="I78" t="n">
         <v>81259</v>
       </c>
-      <c r="I78" t="n">
+      <c r="J78" t="n">
         <v>49</v>
       </c>
     </row>
@@ -2839,22 +3069,25 @@
       <c r="C79" t="n">
         <v>2</v>
       </c>
-      <c r="D79" s="4" t="n">
+      <c r="D79" t="n">
+        <v>2</v>
+      </c>
+      <c r="E79" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E79" t="n">
+      <c r="F79" t="n">
         <v>47</v>
       </c>
-      <c r="F79" t="n">
+      <c r="G79" t="n">
         <v>46</v>
       </c>
-      <c r="G79" t="n">
+      <c r="H79" t="n">
         <v>93</v>
       </c>
-      <c r="H79" t="n">
+      <c r="I79" t="n">
         <v>62930</v>
       </c>
-      <c r="I79" t="n">
+      <c r="J79" t="n">
         <v>24</v>
       </c>
     </row>
@@ -2868,24 +3101,27 @@
         <v>11</v>
       </c>
       <c r="C80" t="n">
+        <v>7</v>
+      </c>
+      <c r="D80" t="n">
         <v>5</v>
       </c>
-      <c r="D80" s="4" t="n">
-        <v>0.4545454545454545</v>
-      </c>
-      <c r="E80" t="n">
+      <c r="E80" s="4" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="F80" t="n">
         <v>45</v>
       </c>
-      <c r="F80" t="n">
+      <c r="G80" t="n">
         <v>43</v>
       </c>
-      <c r="G80" t="n">
+      <c r="H80" t="n">
         <v>88</v>
       </c>
-      <c r="H80" t="n">
+      <c r="I80" t="n">
         <v>58040</v>
       </c>
-      <c r="I80" t="n">
+      <c r="J80" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2901,22 +3137,25 @@
       <c r="C81" t="n">
         <v>2</v>
       </c>
-      <c r="D81" s="4" t="n">
+      <c r="D81" t="n">
+        <v>2</v>
+      </c>
+      <c r="E81" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="E81" t="n">
-        <v>45</v>
       </c>
       <c r="F81" t="n">
         <v>45</v>
       </c>
       <c r="G81" t="n">
+        <v>45</v>
+      </c>
+      <c r="H81" t="n">
         <v>90</v>
       </c>
-      <c r="H81" t="n">
+      <c r="I81" t="n">
         <v>65340</v>
       </c>
-      <c r="I81" t="n">
+      <c r="J81" t="n">
         <v>22</v>
       </c>
     </row>
@@ -2932,22 +3171,25 @@
       <c r="C82" t="n">
         <v>1</v>
       </c>
-      <c r="D82" s="4" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="E82" t="n">
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" t="n">
         <v>44</v>
       </c>
-      <c r="F82" t="n">
+      <c r="G82" t="n">
         <v>43</v>
       </c>
-      <c r="G82" t="n">
+      <c r="H82" t="n">
         <v>87</v>
       </c>
-      <c r="H82" t="n">
+      <c r="I82" t="n">
         <v>60697</v>
       </c>
-      <c r="I82" t="n">
+      <c r="J82" t="n">
         <v>44</v>
       </c>
     </row>
@@ -2963,22 +3205,25 @@
       <c r="C83" t="n">
         <v>3</v>
       </c>
-      <c r="D83" s="4" t="n">
+      <c r="D83" t="n">
+        <v>3</v>
+      </c>
+      <c r="E83" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="E83" t="n">
-        <v>43</v>
       </c>
       <c r="F83" t="n">
         <v>43</v>
       </c>
       <c r="G83" t="n">
+        <v>43</v>
+      </c>
+      <c r="H83" t="n">
         <v>86</v>
       </c>
-      <c r="H83" t="n">
+      <c r="I83" t="n">
         <v>54824</v>
       </c>
-      <c r="I83" t="n">
+      <c r="J83" t="n">
         <v>14</v>
       </c>
     </row>
@@ -2992,24 +3237,27 @@
         <v>3</v>
       </c>
       <c r="C84" t="n">
+        <v>2</v>
+      </c>
+      <c r="D84" t="n">
         <v>1</v>
       </c>
-      <c r="D84" s="4" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="E84" t="n">
-        <v>42</v>
+      <c r="E84" s="4" t="n">
+        <v>0.5</v>
       </c>
       <c r="F84" t="n">
         <v>42</v>
       </c>
       <c r="G84" t="n">
+        <v>42</v>
+      </c>
+      <c r="H84" t="n">
         <v>84</v>
       </c>
-      <c r="H84" t="n">
+      <c r="I84" t="n">
         <v>60833</v>
       </c>
-      <c r="I84" t="n">
+      <c r="J84" t="n">
         <v>42</v>
       </c>
     </row>
@@ -3025,22 +3273,25 @@
       <c r="C85" t="n">
         <v>3</v>
       </c>
-      <c r="D85" s="4" t="n">
+      <c r="D85" t="n">
+        <v>3</v>
+      </c>
+      <c r="E85" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="E85" t="n">
-        <v>39</v>
       </c>
       <c r="F85" t="n">
         <v>39</v>
       </c>
       <c r="G85" t="n">
+        <v>39</v>
+      </c>
+      <c r="H85" t="n">
         <v>78</v>
       </c>
-      <c r="H85" t="n">
+      <c r="I85" t="n">
         <v>54875</v>
       </c>
-      <c r="I85" t="n">
+      <c r="J85" t="n">
         <v>13</v>
       </c>
     </row>
@@ -3056,22 +3307,25 @@
       <c r="C86" t="n">
         <v>2</v>
       </c>
-      <c r="D86" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E86" t="n">
-        <v>37</v>
+      <c r="D86" t="n">
+        <v>2</v>
+      </c>
+      <c r="E86" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F86" t="n">
         <v>37</v>
       </c>
       <c r="G86" t="n">
+        <v>37</v>
+      </c>
+      <c r="H86" t="n">
         <v>74</v>
       </c>
-      <c r="H86" t="n">
+      <c r="I86" t="n">
         <v>45424</v>
       </c>
-      <c r="I86" t="n">
+      <c r="J86" t="n">
         <v>18</v>
       </c>
     </row>
@@ -3087,22 +3341,25 @@
       <c r="C87" t="n">
         <v>1</v>
       </c>
-      <c r="D87" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E87" t="n">
+      <c r="D87" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" t="n">
         <v>37</v>
       </c>
-      <c r="F87" t="n">
+      <c r="G87" t="n">
         <v>36</v>
       </c>
-      <c r="G87" t="n">
+      <c r="H87" t="n">
         <v>73</v>
       </c>
-      <c r="H87" t="n">
+      <c r="I87" t="n">
         <v>41549</v>
       </c>
-      <c r="I87" t="n">
+      <c r="J87" t="n">
         <v>37</v>
       </c>
     </row>
@@ -3118,22 +3375,25 @@
       <c r="C88" t="n">
         <v>2</v>
       </c>
-      <c r="D88" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="E88" t="n">
-        <v>36</v>
+      <c r="D88" t="n">
+        <v>2</v>
+      </c>
+      <c r="E88" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F88" t="n">
         <v>36</v>
       </c>
       <c r="G88" t="n">
+        <v>36</v>
+      </c>
+      <c r="H88" t="n">
         <v>72</v>
       </c>
-      <c r="H88" t="n">
+      <c r="I88" t="n">
         <v>36412</v>
       </c>
-      <c r="I88" t="n">
+      <c r="J88" t="n">
         <v>18</v>
       </c>
     </row>
@@ -3149,22 +3409,25 @@
       <c r="C89" t="n">
         <v>1</v>
       </c>
-      <c r="D89" s="4" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="E89" t="n">
-        <v>34</v>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F89" t="n">
         <v>34</v>
       </c>
       <c r="G89" t="n">
+        <v>34</v>
+      </c>
+      <c r="H89" t="n">
         <v>68</v>
       </c>
-      <c r="H89" t="n">
+      <c r="I89" t="n">
         <v>58216</v>
       </c>
-      <c r="I89" t="n">
+      <c r="J89" t="n">
         <v>34</v>
       </c>
     </row>
@@ -3180,22 +3443,25 @@
       <c r="C90" t="n">
         <v>2</v>
       </c>
-      <c r="D90" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E90" t="n">
-        <v>33</v>
+      <c r="D90" t="n">
+        <v>2</v>
+      </c>
+      <c r="E90" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F90" t="n">
         <v>33</v>
       </c>
       <c r="G90" t="n">
+        <v>33</v>
+      </c>
+      <c r="H90" t="n">
         <v>66</v>
       </c>
-      <c r="H90" t="n">
+      <c r="I90" t="n">
         <v>39823</v>
       </c>
-      <c r="I90" t="n">
+      <c r="J90" t="n">
         <v>16</v>
       </c>
     </row>
@@ -3211,22 +3477,25 @@
       <c r="C91" t="n">
         <v>4</v>
       </c>
-      <c r="D91" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="E91" t="n">
-        <v>33</v>
+      <c r="D91" t="n">
+        <v>4</v>
+      </c>
+      <c r="E91" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F91" t="n">
         <v>33</v>
       </c>
       <c r="G91" t="n">
+        <v>33</v>
+      </c>
+      <c r="H91" t="n">
         <v>66</v>
       </c>
-      <c r="H91" t="n">
+      <c r="I91" t="n">
         <v>51998</v>
       </c>
-      <c r="I91" t="n">
+      <c r="J91" t="n">
         <v>8</v>
       </c>
     </row>
@@ -3242,22 +3511,25 @@
       <c r="C92" t="n">
         <v>3</v>
       </c>
-      <c r="D92" s="4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E92" t="n">
+      <c r="D92" t="n">
+        <v>3</v>
+      </c>
+      <c r="E92" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" t="n">
         <v>33</v>
       </c>
-      <c r="F92" t="n">
+      <c r="G92" t="n">
         <v>32</v>
       </c>
-      <c r="G92" t="n">
+      <c r="H92" t="n">
         <v>65</v>
       </c>
-      <c r="H92" t="n">
+      <c r="I92" t="n">
         <v>41309</v>
       </c>
-      <c r="I92" t="n">
+      <c r="J92" t="n">
         <v>11</v>
       </c>
     </row>
@@ -3273,22 +3545,25 @@
       <c r="C93" t="n">
         <v>3</v>
       </c>
-      <c r="D93" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E93" t="n">
+      <c r="D93" t="n">
+        <v>3</v>
+      </c>
+      <c r="E93" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" t="n">
         <v>32</v>
       </c>
-      <c r="F93" t="n">
+      <c r="G93" t="n">
         <v>31</v>
       </c>
-      <c r="G93" t="n">
+      <c r="H93" t="n">
         <v>63</v>
       </c>
-      <c r="H93" t="n">
+      <c r="I93" t="n">
         <v>38430</v>
       </c>
-      <c r="I93" t="n">
+      <c r="J93" t="n">
         <v>11</v>
       </c>
     </row>
@@ -3304,22 +3579,25 @@
       <c r="C94" t="n">
         <v>1</v>
       </c>
-      <c r="D94" s="4" t="n">
+      <c r="D94" t="n">
         <v>1</v>
       </c>
-      <c r="E94" t="n">
-        <v>31</v>
+      <c r="E94" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F94" t="n">
         <v>31</v>
       </c>
       <c r="G94" t="n">
+        <v>31</v>
+      </c>
+      <c r="H94" t="n">
         <v>62</v>
       </c>
-      <c r="H94" t="n">
+      <c r="I94" t="n">
         <v>35848</v>
       </c>
-      <c r="I94" t="n">
+      <c r="J94" t="n">
         <v>31</v>
       </c>
     </row>
@@ -3335,22 +3613,25 @@
       <c r="C95" t="n">
         <v>2</v>
       </c>
-      <c r="D95" s="4" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="E95" t="n">
-        <v>31</v>
+      <c r="D95" t="n">
+        <v>2</v>
+      </c>
+      <c r="E95" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F95" t="n">
         <v>31</v>
       </c>
       <c r="G95" t="n">
+        <v>31</v>
+      </c>
+      <c r="H95" t="n">
         <v>62</v>
       </c>
-      <c r="H95" t="n">
+      <c r="I95" t="n">
         <v>55802</v>
       </c>
-      <c r="I95" t="n">
+      <c r="J95" t="n">
         <v>16</v>
       </c>
     </row>
@@ -3364,24 +3645,27 @@
         <v>7</v>
       </c>
       <c r="C96" t="n">
+        <v>5</v>
+      </c>
+      <c r="D96" t="n">
         <v>3</v>
       </c>
-      <c r="D96" s="4" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="E96" t="n">
+      <c r="E96" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F96" t="n">
         <v>30</v>
       </c>
-      <c r="F96" t="n">
+      <c r="G96" t="n">
         <v>29</v>
       </c>
-      <c r="G96" t="n">
+      <c r="H96" t="n">
         <v>59</v>
       </c>
-      <c r="H96" t="n">
+      <c r="I96" t="n">
         <v>44999</v>
       </c>
-      <c r="I96" t="n">
+      <c r="J96" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3397,22 +3681,25 @@
       <c r="C97" t="n">
         <v>3</v>
       </c>
-      <c r="D97" s="4" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="E97" t="n">
-        <v>29</v>
+      <c r="D97" t="n">
+        <v>3</v>
+      </c>
+      <c r="E97" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F97" t="n">
         <v>29</v>
       </c>
       <c r="G97" t="n">
+        <v>29</v>
+      </c>
+      <c r="H97" t="n">
         <v>58</v>
       </c>
-      <c r="H97" t="n">
+      <c r="I97" t="n">
         <v>45435</v>
       </c>
-      <c r="I97" t="n">
+      <c r="J97" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3428,22 +3715,25 @@
       <c r="C98" t="n">
         <v>2</v>
       </c>
-      <c r="D98" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E98" t="n">
+      <c r="D98" t="n">
+        <v>2</v>
+      </c>
+      <c r="E98" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" t="n">
         <v>27</v>
       </c>
-      <c r="F98" t="n">
+      <c r="G98" t="n">
         <v>26</v>
       </c>
-      <c r="G98" t="n">
+      <c r="H98" t="n">
         <v>53</v>
       </c>
-      <c r="H98" t="n">
+      <c r="I98" t="n">
         <v>40774</v>
       </c>
-      <c r="I98" t="n">
+      <c r="J98" t="n">
         <v>14</v>
       </c>
     </row>
@@ -3457,24 +3747,27 @@
         <v>5</v>
       </c>
       <c r="C99" t="n">
+        <v>4</v>
+      </c>
+      <c r="D99" t="n">
         <v>3</v>
       </c>
-      <c r="D99" s="4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E99" t="n">
-        <v>27</v>
+      <c r="E99" s="4" t="n">
+        <v>0.75</v>
       </c>
       <c r="F99" t="n">
         <v>27</v>
       </c>
       <c r="G99" t="n">
+        <v>27</v>
+      </c>
+      <c r="H99" t="n">
         <v>54</v>
       </c>
-      <c r="H99" t="n">
+      <c r="I99" t="n">
         <v>46920</v>
       </c>
-      <c r="I99" t="n">
+      <c r="J99" t="n">
         <v>9</v>
       </c>
     </row>
@@ -3490,22 +3783,25 @@
       <c r="C100" t="n">
         <v>1</v>
       </c>
-      <c r="D100" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E100" t="n">
-        <v>27</v>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F100" t="n">
         <v>27</v>
       </c>
       <c r="G100" t="n">
+        <v>27</v>
+      </c>
+      <c r="H100" t="n">
         <v>54</v>
       </c>
-      <c r="H100" t="n">
+      <c r="I100" t="n">
         <v>45399</v>
       </c>
-      <c r="I100" t="n">
+      <c r="J100" t="n">
         <v>27</v>
       </c>
     </row>
@@ -3519,24 +3815,27 @@
         <v>6</v>
       </c>
       <c r="C101" t="n">
+        <v>3</v>
+      </c>
+      <c r="D101" t="n">
         <v>2</v>
       </c>
-      <c r="D101" s="4" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="E101" t="n">
+      <c r="E101" s="4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F101" t="n">
         <v>25</v>
       </c>
-      <c r="F101" t="n">
+      <c r="G101" t="n">
         <v>24</v>
       </c>
-      <c r="G101" t="n">
+      <c r="H101" t="n">
         <v>49</v>
       </c>
-      <c r="H101" t="n">
+      <c r="I101" t="n">
         <v>27843</v>
       </c>
-      <c r="I101" t="n">
+      <c r="J101" t="n">
         <v>12</v>
       </c>
     </row>
@@ -3552,22 +3851,25 @@
       <c r="C102" t="n">
         <v>1</v>
       </c>
-      <c r="D102" s="4" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="E102" t="n">
-        <v>25</v>
+      <c r="D102" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F102" t="n">
         <v>25</v>
       </c>
       <c r="G102" t="n">
+        <v>25</v>
+      </c>
+      <c r="H102" t="n">
         <v>50</v>
       </c>
-      <c r="H102" t="n">
+      <c r="I102" t="n">
         <v>37538</v>
       </c>
-      <c r="I102" t="n">
+      <c r="J102" t="n">
         <v>25</v>
       </c>
     </row>
@@ -3583,22 +3885,25 @@
       <c r="C103" t="n">
         <v>4</v>
       </c>
-      <c r="D103" s="4" t="n">
-        <v>0.1904761904761905</v>
-      </c>
-      <c r="E103" t="n">
-        <v>24</v>
+      <c r="D103" t="n">
+        <v>4</v>
+      </c>
+      <c r="E103" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F103" t="n">
         <v>24</v>
       </c>
       <c r="G103" t="n">
+        <v>24</v>
+      </c>
+      <c r="H103" t="n">
         <v>48</v>
       </c>
-      <c r="H103" t="n">
+      <c r="I103" t="n">
         <v>35052</v>
       </c>
-      <c r="I103" t="n">
+      <c r="J103" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3614,22 +3919,25 @@
       <c r="C104" t="n">
         <v>4</v>
       </c>
-      <c r="D104" s="4" t="n">
+      <c r="D104" t="n">
+        <v>4</v>
+      </c>
+      <c r="E104" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="E104" t="n">
-        <v>24</v>
       </c>
       <c r="F104" t="n">
         <v>24</v>
       </c>
       <c r="G104" t="n">
+        <v>24</v>
+      </c>
+      <c r="H104" t="n">
         <v>48</v>
       </c>
-      <c r="H104" t="n">
+      <c r="I104" t="n">
         <v>34110</v>
       </c>
-      <c r="I104" t="n">
+      <c r="J104" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3643,24 +3951,27 @@
         <v>8</v>
       </c>
       <c r="C105" t="n">
+        <v>3</v>
+      </c>
+      <c r="D105" t="n">
         <v>1</v>
       </c>
-      <c r="D105" s="4" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E105" t="n">
-        <v>24</v>
+      <c r="E105" s="4" t="n">
+        <v>0.3333333333333333</v>
       </c>
       <c r="F105" t="n">
         <v>24</v>
       </c>
       <c r="G105" t="n">
+        <v>24</v>
+      </c>
+      <c r="H105" t="n">
         <v>48</v>
       </c>
-      <c r="H105" t="n">
+      <c r="I105" t="n">
         <v>27495</v>
       </c>
-      <c r="I105" t="n">
+      <c r="J105" t="n">
         <v>24</v>
       </c>
     </row>
@@ -3676,22 +3987,25 @@
       <c r="C106" t="n">
         <v>2</v>
       </c>
-      <c r="D106" s="4" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="E106" t="n">
-        <v>22</v>
+      <c r="D106" t="n">
+        <v>2</v>
+      </c>
+      <c r="E106" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F106" t="n">
         <v>22</v>
       </c>
       <c r="G106" t="n">
+        <v>22</v>
+      </c>
+      <c r="H106" t="n">
         <v>44</v>
       </c>
-      <c r="H106" t="n">
+      <c r="I106" t="n">
         <v>26374</v>
       </c>
-      <c r="I106" t="n">
+      <c r="J106" t="n">
         <v>11</v>
       </c>
     </row>
@@ -3705,24 +4019,27 @@
         <v>3</v>
       </c>
       <c r="C107" t="n">
+        <v>3</v>
+      </c>
+      <c r="D107" t="n">
         <v>2</v>
       </c>
-      <c r="D107" s="4" t="n">
+      <c r="E107" s="4" t="n">
         <v>0.6666666666666666</v>
-      </c>
-      <c r="E107" t="n">
-        <v>21</v>
       </c>
       <c r="F107" t="n">
         <v>21</v>
       </c>
       <c r="G107" t="n">
+        <v>21</v>
+      </c>
+      <c r="H107" t="n">
         <v>42</v>
       </c>
-      <c r="H107" t="n">
+      <c r="I107" t="n">
         <v>23682</v>
       </c>
-      <c r="I107" t="n">
+      <c r="J107" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3738,22 +4055,25 @@
       <c r="C108" t="n">
         <v>1</v>
       </c>
-      <c r="D108" s="4" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="E108" t="n">
-        <v>20</v>
+      <c r="D108" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F108" t="n">
         <v>20</v>
       </c>
       <c r="G108" t="n">
+        <v>20</v>
+      </c>
+      <c r="H108" t="n">
         <v>40</v>
       </c>
-      <c r="H108" t="n">
+      <c r="I108" t="n">
         <v>38328</v>
       </c>
-      <c r="I108" t="n">
+      <c r="J108" t="n">
         <v>20</v>
       </c>
     </row>
@@ -3769,22 +4089,25 @@
       <c r="C109" t="n">
         <v>1</v>
       </c>
-      <c r="D109" s="4" t="n">
+      <c r="D109" t="n">
         <v>1</v>
       </c>
-      <c r="E109" t="n">
-        <v>19</v>
+      <c r="E109" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F109" t="n">
         <v>19</v>
       </c>
       <c r="G109" t="n">
+        <v>19</v>
+      </c>
+      <c r="H109" t="n">
         <v>38</v>
       </c>
-      <c r="H109" t="n">
+      <c r="I109" t="n">
         <v>31988</v>
       </c>
-      <c r="I109" t="n">
+      <c r="J109" t="n">
         <v>19</v>
       </c>
     </row>
@@ -3798,24 +4121,27 @@
         <v>5</v>
       </c>
       <c r="C110" t="n">
+        <v>4</v>
+      </c>
+      <c r="D110" t="n">
         <v>3</v>
       </c>
-      <c r="D110" s="4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E110" t="n">
-        <v>19</v>
+      <c r="E110" s="4" t="n">
+        <v>0.75</v>
       </c>
       <c r="F110" t="n">
         <v>19</v>
       </c>
       <c r="G110" t="n">
+        <v>19</v>
+      </c>
+      <c r="H110" t="n">
         <v>38</v>
       </c>
-      <c r="H110" t="n">
+      <c r="I110" t="n">
         <v>32831</v>
       </c>
-      <c r="I110" t="n">
+      <c r="J110" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3831,22 +4157,25 @@
       <c r="C111" t="n">
         <v>4</v>
       </c>
-      <c r="D111" s="4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E111" t="n">
-        <v>18</v>
+      <c r="D111" t="n">
+        <v>4</v>
+      </c>
+      <c r="E111" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F111" t="n">
         <v>18</v>
       </c>
       <c r="G111" t="n">
+        <v>18</v>
+      </c>
+      <c r="H111" t="n">
         <v>36</v>
       </c>
-      <c r="H111" t="n">
+      <c r="I111" t="n">
         <v>32734</v>
       </c>
-      <c r="I111" t="n">
+      <c r="J111" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3862,22 +4191,25 @@
       <c r="C112" t="n">
         <v>1</v>
       </c>
-      <c r="D112" s="4" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="E112" t="n">
-        <v>18</v>
+      <c r="D112" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F112" t="n">
         <v>18</v>
       </c>
       <c r="G112" t="n">
+        <v>18</v>
+      </c>
+      <c r="H112" t="n">
         <v>36</v>
       </c>
-      <c r="H112" t="n">
+      <c r="I112" t="n">
         <v>25971</v>
       </c>
-      <c r="I112" t="n">
+      <c r="J112" t="n">
         <v>18</v>
       </c>
     </row>
@@ -3891,24 +4223,27 @@
         <v>6</v>
       </c>
       <c r="C113" t="n">
+        <v>2</v>
+      </c>
+      <c r="D113" t="n">
         <v>1</v>
       </c>
-      <c r="D113" s="4" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="E113" t="n">
-        <v>15</v>
+      <c r="E113" s="4" t="n">
+        <v>0.5</v>
       </c>
       <c r="F113" t="n">
         <v>15</v>
       </c>
       <c r="G113" t="n">
+        <v>15</v>
+      </c>
+      <c r="H113" t="n">
         <v>30</v>
       </c>
-      <c r="H113" t="n">
+      <c r="I113" t="n">
         <v>20108</v>
       </c>
-      <c r="I113" t="n">
+      <c r="J113" t="n">
         <v>15</v>
       </c>
     </row>
@@ -3924,22 +4259,25 @@
       <c r="C114" t="n">
         <v>1</v>
       </c>
-      <c r="D114" s="4" t="n">
+      <c r="D114" t="n">
         <v>1</v>
       </c>
-      <c r="E114" t="n">
-        <v>14</v>
+      <c r="E114" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F114" t="n">
         <v>14</v>
       </c>
       <c r="G114" t="n">
+        <v>14</v>
+      </c>
+      <c r="H114" t="n">
         <v>28</v>
       </c>
-      <c r="H114" t="n">
+      <c r="I114" t="n">
         <v>14820</v>
       </c>
-      <c r="I114" t="n">
+      <c r="J114" t="n">
         <v>14</v>
       </c>
     </row>
@@ -3955,22 +4293,25 @@
       <c r="C115" t="n">
         <v>1</v>
       </c>
-      <c r="D115" s="4" t="n">
+      <c r="D115" t="n">
         <v>1</v>
       </c>
-      <c r="E115" t="n">
-        <v>13</v>
+      <c r="E115" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F115" t="n">
         <v>13</v>
       </c>
       <c r="G115" t="n">
+        <v>13</v>
+      </c>
+      <c r="H115" t="n">
         <v>26</v>
       </c>
-      <c r="H115" t="n">
+      <c r="I115" t="n">
         <v>11996</v>
       </c>
-      <c r="I115" t="n">
+      <c r="J115" t="n">
         <v>13</v>
       </c>
     </row>
@@ -3986,22 +4327,25 @@
       <c r="C116" t="n">
         <v>1</v>
       </c>
-      <c r="D116" s="4" t="n">
+      <c r="D116" t="n">
         <v>1</v>
       </c>
-      <c r="E116" t="n">
-        <v>13</v>
+      <c r="E116" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F116" t="n">
         <v>13</v>
       </c>
       <c r="G116" t="n">
+        <v>13</v>
+      </c>
+      <c r="H116" t="n">
         <v>26</v>
       </c>
-      <c r="H116" t="n">
+      <c r="I116" t="n">
         <v>19895</v>
       </c>
-      <c r="I116" t="n">
+      <c r="J116" t="n">
         <v>13</v>
       </c>
     </row>
@@ -4017,22 +4361,25 @@
       <c r="C117" t="n">
         <v>1</v>
       </c>
-      <c r="D117" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E117" t="n">
-        <v>13</v>
+      <c r="D117" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F117" t="n">
         <v>13</v>
       </c>
       <c r="G117" t="n">
+        <v>13</v>
+      </c>
+      <c r="H117" t="n">
         <v>26</v>
       </c>
-      <c r="H117" t="n">
+      <c r="I117" t="n">
         <v>15588</v>
       </c>
-      <c r="I117" t="n">
+      <c r="J117" t="n">
         <v>13</v>
       </c>
     </row>
@@ -4048,22 +4395,25 @@
       <c r="C118" t="n">
         <v>4</v>
       </c>
-      <c r="D118" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="E118" t="n">
-        <v>12</v>
+      <c r="D118" t="n">
+        <v>4</v>
+      </c>
+      <c r="E118" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F118" t="n">
         <v>12</v>
       </c>
       <c r="G118" t="n">
+        <v>12</v>
+      </c>
+      <c r="H118" t="n">
         <v>24</v>
       </c>
-      <c r="H118" t="n">
+      <c r="I118" t="n">
         <v>20290</v>
       </c>
-      <c r="I118" t="n">
+      <c r="J118" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4079,22 +4429,25 @@
       <c r="C119" t="n">
         <v>1</v>
       </c>
-      <c r="D119" s="4" t="n">
+      <c r="D119" t="n">
         <v>1</v>
       </c>
-      <c r="E119" t="n">
-        <v>12</v>
+      <c r="E119" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F119" t="n">
         <v>12</v>
       </c>
       <c r="G119" t="n">
+        <v>12</v>
+      </c>
+      <c r="H119" t="n">
         <v>24</v>
       </c>
-      <c r="H119" t="n">
+      <c r="I119" t="n">
         <v>18146</v>
       </c>
-      <c r="I119" t="n">
+      <c r="J119" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4108,24 +4461,27 @@
         <v>6</v>
       </c>
       <c r="C120" t="n">
+        <v>2</v>
+      </c>
+      <c r="D120" t="n">
         <v>1</v>
       </c>
-      <c r="D120" s="4" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="E120" t="n">
+      <c r="E120" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F120" t="n">
         <v>11</v>
       </c>
-      <c r="F120" t="n">
+      <c r="G120" t="n">
         <v>10</v>
       </c>
-      <c r="G120" t="n">
+      <c r="H120" t="n">
         <v>21</v>
       </c>
-      <c r="H120" t="n">
+      <c r="I120" t="n">
         <v>11363</v>
       </c>
-      <c r="I120" t="n">
+      <c r="J120" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4141,22 +4497,25 @@
       <c r="C121" t="n">
         <v>1</v>
       </c>
-      <c r="D121" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E121" t="n">
+      <c r="D121" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" t="n">
         <v>10</v>
       </c>
-      <c r="F121" t="n">
+      <c r="G121" t="n">
         <v>9</v>
       </c>
-      <c r="G121" t="n">
+      <c r="H121" t="n">
         <v>19</v>
       </c>
-      <c r="H121" t="n">
+      <c r="I121" t="n">
         <v>12111</v>
       </c>
-      <c r="I121" t="n">
+      <c r="J121" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4172,22 +4531,25 @@
       <c r="C122" t="n">
         <v>2</v>
       </c>
-      <c r="D122" s="4" t="n">
-        <v>0.1052631578947368</v>
-      </c>
-      <c r="E122" t="n">
-        <v>9</v>
+      <c r="D122" t="n">
+        <v>2</v>
+      </c>
+      <c r="E122" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F122" t="n">
         <v>9</v>
       </c>
       <c r="G122" t="n">
+        <v>9</v>
+      </c>
+      <c r="H122" t="n">
         <v>18</v>
       </c>
-      <c r="H122" t="n">
+      <c r="I122" t="n">
         <v>13220</v>
       </c>
-      <c r="I122" t="n">
+      <c r="J122" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4203,22 +4565,25 @@
       <c r="C123" t="n">
         <v>1</v>
       </c>
-      <c r="D123" s="4" t="n">
+      <c r="D123" t="n">
         <v>1</v>
       </c>
-      <c r="E123" t="n">
-        <v>9</v>
+      <c r="E123" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F123" t="n">
         <v>9</v>
       </c>
       <c r="G123" t="n">
+        <v>9</v>
+      </c>
+      <c r="H123" t="n">
         <v>18</v>
       </c>
-      <c r="H123" t="n">
+      <c r="I123" t="n">
         <v>15941</v>
       </c>
-      <c r="I123" t="n">
+      <c r="J123" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4234,22 +4599,25 @@
       <c r="C124" t="n">
         <v>1</v>
       </c>
-      <c r="D124" s="4" t="n">
+      <c r="D124" t="n">
         <v>1</v>
       </c>
-      <c r="E124" t="n">
-        <v>9</v>
+      <c r="E124" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F124" t="n">
         <v>9</v>
       </c>
       <c r="G124" t="n">
+        <v>9</v>
+      </c>
+      <c r="H124" t="n">
         <v>18</v>
       </c>
-      <c r="H124" t="n">
+      <c r="I124" t="n">
         <v>13727</v>
       </c>
-      <c r="I124" t="n">
+      <c r="J124" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4265,22 +4633,25 @@
       <c r="C125" t="n">
         <v>1</v>
       </c>
-      <c r="D125" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E125" t="n">
-        <v>8</v>
+      <c r="D125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F125" t="n">
         <v>8</v>
       </c>
       <c r="G125" t="n">
+        <v>8</v>
+      </c>
+      <c r="H125" t="n">
         <v>16</v>
       </c>
-      <c r="H125" t="n">
+      <c r="I125" t="n">
         <v>18271</v>
       </c>
-      <c r="I125" t="n">
+      <c r="J125" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4294,24 +4665,27 @@
         <v>6</v>
       </c>
       <c r="C126" t="n">
+        <v>6</v>
+      </c>
+      <c r="D126" t="n">
         <v>3</v>
       </c>
-      <c r="D126" s="4" t="n">
+      <c r="E126" s="4" t="n">
         <v>0.5</v>
-      </c>
-      <c r="E126" t="n">
-        <v>7</v>
       </c>
       <c r="F126" t="n">
         <v>7</v>
       </c>
       <c r="G126" t="n">
+        <v>7</v>
+      </c>
+      <c r="H126" t="n">
         <v>14</v>
       </c>
-      <c r="H126" t="n">
+      <c r="I126" t="n">
         <v>6662</v>
       </c>
-      <c r="I126" t="n">
+      <c r="J126" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4327,22 +4701,25 @@
       <c r="C127" t="n">
         <v>1</v>
       </c>
-      <c r="D127" s="4" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="E127" t="n">
-        <v>7</v>
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F127" t="n">
         <v>7</v>
       </c>
       <c r="G127" t="n">
+        <v>7</v>
+      </c>
+      <c r="H127" t="n">
         <v>14</v>
       </c>
-      <c r="H127" t="n">
+      <c r="I127" t="n">
         <v>9215</v>
       </c>
-      <c r="I127" t="n">
+      <c r="J127" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4358,22 +4735,25 @@
       <c r="C128" t="n">
         <v>1</v>
       </c>
-      <c r="D128" s="4" t="n">
+      <c r="D128" t="n">
         <v>1</v>
       </c>
-      <c r="E128" t="n">
-        <v>6</v>
+      <c r="E128" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F128" t="n">
         <v>6</v>
       </c>
       <c r="G128" t="n">
+        <v>6</v>
+      </c>
+      <c r="H128" t="n">
         <v>12</v>
       </c>
-      <c r="H128" t="n">
+      <c r="I128" t="n">
         <v>7289</v>
       </c>
-      <c r="I128" t="n">
+      <c r="J128" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4387,24 +4767,27 @@
         <v>9</v>
       </c>
       <c r="C129" t="n">
+        <v>4</v>
+      </c>
+      <c r="D129" t="n">
         <v>2</v>
       </c>
-      <c r="D129" s="4" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="E129" t="n">
-        <v>6</v>
+      <c r="E129" s="4" t="n">
+        <v>0.5</v>
       </c>
       <c r="F129" t="n">
         <v>6</v>
       </c>
       <c r="G129" t="n">
+        <v>6</v>
+      </c>
+      <c r="H129" t="n">
         <v>12</v>
       </c>
-      <c r="H129" t="n">
+      <c r="I129" t="n">
         <v>9240</v>
       </c>
-      <c r="I129" t="n">
+      <c r="J129" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4418,24 +4801,27 @@
         <v>4</v>
       </c>
       <c r="C130" t="n">
+        <v>3</v>
+      </c>
+      <c r="D130" t="n">
         <v>2</v>
       </c>
-      <c r="D130" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E130" t="n">
-        <v>6</v>
+      <c r="E130" s="4" t="n">
+        <v>0.6666666666666666</v>
       </c>
       <c r="F130" t="n">
         <v>6</v>
       </c>
       <c r="G130" t="n">
+        <v>6</v>
+      </c>
+      <c r="H130" t="n">
         <v>12</v>
       </c>
-      <c r="H130" t="n">
+      <c r="I130" t="n">
         <v>9099</v>
       </c>
-      <c r="I130" t="n">
+      <c r="J130" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4451,22 +4837,25 @@
       <c r="C131" t="n">
         <v>2</v>
       </c>
-      <c r="D131" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E131" t="n">
-        <v>5</v>
+      <c r="D131" t="n">
+        <v>2</v>
+      </c>
+      <c r="E131" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F131" t="n">
         <v>5</v>
       </c>
       <c r="G131" t="n">
+        <v>5</v>
+      </c>
+      <c r="H131" t="n">
         <v>10</v>
       </c>
-      <c r="H131" t="n">
+      <c r="I131" t="n">
         <v>7956</v>
       </c>
-      <c r="I131" t="n">
+      <c r="J131" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4482,22 +4871,25 @@
       <c r="C132" t="n">
         <v>1</v>
       </c>
-      <c r="D132" s="4" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="E132" t="n">
-        <v>5</v>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F132" t="n">
         <v>5</v>
       </c>
       <c r="G132" t="n">
+        <v>5</v>
+      </c>
+      <c r="H132" t="n">
         <v>10</v>
       </c>
-      <c r="H132" t="n">
+      <c r="I132" t="n">
         <v>6256</v>
       </c>
-      <c r="I132" t="n">
+      <c r="J132" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4513,22 +4905,25 @@
       <c r="C133" t="n">
         <v>1</v>
       </c>
-      <c r="D133" s="4" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="E133" t="n">
-        <v>5</v>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F133" t="n">
         <v>5</v>
       </c>
       <c r="G133" t="n">
+        <v>5</v>
+      </c>
+      <c r="H133" t="n">
         <v>10</v>
       </c>
-      <c r="H133" t="n">
+      <c r="I133" t="n">
         <v>8632</v>
       </c>
-      <c r="I133" t="n">
+      <c r="J133" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4542,24 +4937,27 @@
         <v>8</v>
       </c>
       <c r="C134" t="n">
+        <v>2</v>
+      </c>
+      <c r="D134" t="n">
         <v>1</v>
       </c>
-      <c r="D134" s="4" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E134" t="n">
-        <v>4</v>
+      <c r="E134" s="4" t="n">
+        <v>0.5</v>
       </c>
       <c r="F134" t="n">
         <v>4</v>
       </c>
       <c r="G134" t="n">
+        <v>4</v>
+      </c>
+      <c r="H134" t="n">
         <v>8</v>
       </c>
-      <c r="H134" t="n">
+      <c r="I134" t="n">
         <v>6316</v>
       </c>
-      <c r="I134" t="n">
+      <c r="J134" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4575,22 +4973,25 @@
       <c r="C135" t="n">
         <v>1</v>
       </c>
-      <c r="D135" s="4" t="n">
+      <c r="D135" t="n">
         <v>1</v>
       </c>
-      <c r="E135" t="n">
-        <v>3</v>
+      <c r="E135" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F135" t="n">
         <v>3</v>
       </c>
       <c r="G135" t="n">
+        <v>3</v>
+      </c>
+      <c r="H135" t="n">
         <v>6</v>
       </c>
-      <c r="H135" t="n">
+      <c r="I135" t="n">
         <v>3415</v>
       </c>
-      <c r="I135" t="n">
+      <c r="J135" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4606,22 +5007,25 @@
       <c r="C136" t="n">
         <v>2</v>
       </c>
-      <c r="D136" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="E136" t="n">
-        <v>3</v>
+      <c r="D136" t="n">
+        <v>2</v>
+      </c>
+      <c r="E136" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F136" t="n">
         <v>3</v>
       </c>
       <c r="G136" t="n">
+        <v>3</v>
+      </c>
+      <c r="H136" t="n">
         <v>6</v>
       </c>
-      <c r="H136" t="n">
+      <c r="I136" t="n">
         <v>5725</v>
       </c>
-      <c r="I136" t="n">
+      <c r="J136" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4637,22 +5041,25 @@
       <c r="C137" t="n">
         <v>1</v>
       </c>
-      <c r="D137" s="4" t="n">
+      <c r="D137" t="n">
         <v>1</v>
       </c>
-      <c r="E137" t="n">
-        <v>3</v>
+      <c r="E137" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F137" t="n">
         <v>3</v>
       </c>
       <c r="G137" t="n">
+        <v>3</v>
+      </c>
+      <c r="H137" t="n">
         <v>6</v>
       </c>
-      <c r="H137" t="n">
+      <c r="I137" t="n">
         <v>6067</v>
       </c>
-      <c r="I137" t="n">
+      <c r="J137" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4668,22 +5075,25 @@
       <c r="C138" t="n">
         <v>1</v>
       </c>
-      <c r="D138" s="4" t="n">
+      <c r="D138" t="n">
         <v>1</v>
       </c>
-      <c r="E138" t="n">
-        <v>2</v>
+      <c r="E138" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F138" t="n">
         <v>2</v>
       </c>
       <c r="G138" t="n">
+        <v>2</v>
+      </c>
+      <c r="H138" t="n">
         <v>4</v>
       </c>
-      <c r="H138" t="n">
+      <c r="I138" t="n">
         <v>3262</v>
       </c>
-      <c r="I138" t="n">
+      <c r="J138" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4699,22 +5109,25 @@
       <c r="C139" t="n">
         <v>1</v>
       </c>
-      <c r="D139" s="4" t="n">
+      <c r="D139" t="n">
         <v>1</v>
       </c>
-      <c r="E139" t="n">
-        <v>2</v>
+      <c r="E139" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F139" t="n">
         <v>2</v>
       </c>
       <c r="G139" t="n">
+        <v>2</v>
+      </c>
+      <c r="H139" t="n">
         <v>4</v>
       </c>
-      <c r="H139" t="n">
+      <c r="I139" t="n">
         <v>3400</v>
       </c>
-      <c r="I139" t="n">
+      <c r="J139" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4730,22 +5143,25 @@
       <c r="C140" t="n">
         <v>1</v>
       </c>
-      <c r="D140" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E140" t="n">
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F140" t="n">
         <v>1</v>
       </c>
       <c r="G140" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" t="n">
         <v>2</v>
       </c>
-      <c r="H140" t="n">
+      <c r="I140" t="n">
         <v>909</v>
       </c>
-      <c r="I140" t="n">
+      <c r="J140" t="n">
         <v>1</v>
       </c>
     </row>

--- a/reports/QommonsAI利用集計_2026-07.xlsx
+++ b/reports/QommonsAI利用集計_2026-07.xlsx
@@ -482,7 +482,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>集計期間: 2026-07-01 〜 2026-07-22  ／ 利用回数=プロンプト(質問)数  ／ 使用文字数=入力+出力(プレフィックス除く)  ／ 利用率=利用者数÷登録者数(利用開始済み)</t>
+          <t>集計期間: 2026-07-01 〜 2026-07-22  ／ 利用回数=プロンプト(質問)数  ／ 使用文字数=入力+出力(プレフィックス除く)  ／ 利用率=利用者数÷登録者数(全体)</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         <v>11</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="F6" t="n">
         <v>1132</v>
@@ -659,7 +659,7 @@
         <v>10</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F8" t="n">
         <v>816</v>
@@ -693,7 +693,7 @@
         <v>13</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.8125</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="F9" t="n">
         <v>688</v>
@@ -727,7 +727,7 @@
         <v>17</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F10" t="n">
         <v>674</v>
@@ -795,7 +795,7 @@
         <v>5</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="F12" t="n">
         <v>527</v>
@@ -829,7 +829,7 @@
         <v>13</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8125</v>
       </c>
       <c r="F13" t="n">
         <v>504</v>
@@ -863,7 +863,7 @@
         <v>6</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="F14" t="n">
         <v>500</v>
@@ -897,7 +897,7 @@
         <v>3</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="F15" t="n">
         <v>495</v>
@@ -931,7 +931,7 @@
         <v>8</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F16" t="n">
         <v>391</v>
@@ -965,7 +965,7 @@
         <v>8</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="F17" t="n">
         <v>368</v>
@@ -1033,7 +1033,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F19" t="n">
         <v>348</v>
@@ -1067,7 +1067,7 @@
         <v>8</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.8</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="F20" t="n">
         <v>334</v>
@@ -1101,7 +1101,7 @@
         <v>9</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="F21" t="n">
         <v>318</v>
@@ -1135,7 +1135,7 @@
         <v>9</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.5625</v>
+        <v>0.36</v>
       </c>
       <c r="F22" t="n">
         <v>308</v>
@@ -1169,7 +1169,7 @@
         <v>4</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.8</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="F23" t="n">
         <v>293</v>
@@ -1203,7 +1203,7 @@
         <v>6</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F24" t="n">
         <v>258</v>
@@ -1237,7 +1237,7 @@
         <v>12</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.75</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="F25" t="n">
         <v>247</v>
@@ -1271,7 +1271,7 @@
         <v>4</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F26" t="n">
         <v>245</v>
@@ -1305,7 +1305,7 @@
         <v>5</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="F27" t="n">
         <v>222</v>
@@ -1339,7 +1339,7 @@
         <v>9</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.5</v>
       </c>
       <c r="F28" t="n">
         <v>219</v>
@@ -1407,7 +1407,7 @@
         <v>5</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="F30" t="n">
         <v>171</v>
@@ -1441,7 +1441,7 @@
         <v>2</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F31" t="n">
         <v>163</v>
@@ -1475,7 +1475,7 @@
         <v>5</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F32" t="n">
         <v>155</v>
@@ -1509,7 +1509,7 @@
         <v>3</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F33" t="n">
         <v>154</v>
@@ -1577,7 +1577,7 @@
         <v>8</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="F35" t="n">
         <v>143</v>
@@ -1611,7 +1611,7 @@
         <v>2</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="F36" t="n">
         <v>136</v>
@@ -1645,7 +1645,7 @@
         <v>3</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F37" t="n">
         <v>130</v>
@@ -1713,7 +1713,7 @@
         <v>6</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="F39" t="n">
         <v>125</v>
@@ -1747,7 +1747,7 @@
         <v>4</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="F40" t="n">
         <v>124</v>
@@ -1781,7 +1781,7 @@
         <v>4</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F41" t="n">
         <v>120</v>
@@ -1815,7 +1815,7 @@
         <v>5</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F42" t="n">
         <v>118</v>
@@ -1849,7 +1849,7 @@
         <v>6</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="F43" t="n">
         <v>116</v>
@@ -1883,7 +1883,7 @@
         <v>5</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="F44" t="n">
         <v>115</v>
@@ -1917,7 +1917,7 @@
         <v>4</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="F45" t="n">
         <v>108</v>
@@ -1951,7 +1951,7 @@
         <v>6</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F46" t="n">
         <v>106</v>
@@ -2019,7 +2019,7 @@
         <v>3</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="F48" t="n">
         <v>102</v>
@@ -2053,7 +2053,7 @@
         <v>6</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F49" t="n">
         <v>101</v>
@@ -2087,7 +2087,7 @@
         <v>3</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F50" t="n">
         <v>101</v>
@@ -2121,7 +2121,7 @@
         <v>5</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="F51" t="n">
         <v>100</v>
@@ -2155,7 +2155,7 @@
         <v>4</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>1</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="F52" t="n">
         <v>98</v>
@@ -2223,7 +2223,7 @@
         <v>7</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.875</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="F54" t="n">
         <v>94</v>
@@ -2257,7 +2257,7 @@
         <v>6</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.5</v>
       </c>
       <c r="F55" t="n">
         <v>93</v>
@@ -2325,7 +2325,7 @@
         <v>6</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F57" t="n">
         <v>89</v>
@@ -2359,7 +2359,7 @@
         <v>4</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F58" t="n">
         <v>81</v>
@@ -2393,7 +2393,7 @@
         <v>5</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="F59" t="n">
         <v>77</v>
@@ -2427,7 +2427,7 @@
         <v>4</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>0.5</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="F60" t="n">
         <v>74</v>
@@ -2461,7 +2461,7 @@
         <v>2</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F61" t="n">
         <v>73</v>
@@ -2495,7 +2495,7 @@
         <v>3</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F62" t="n">
         <v>71</v>
@@ -2529,7 +2529,7 @@
         <v>2</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F63" t="n">
         <v>70</v>
@@ -2597,7 +2597,7 @@
         <v>5</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="F65" t="n">
         <v>66</v>
@@ -2631,7 +2631,7 @@
         <v>1</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F66" t="n">
         <v>66</v>
@@ -2665,7 +2665,7 @@
         <v>2</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F67" t="n">
         <v>66</v>
@@ -2699,7 +2699,7 @@
         <v>4</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4</v>
       </c>
       <c r="F68" t="n">
         <v>65</v>
@@ -2767,7 +2767,7 @@
         <v>3</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>0.75</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="F70" t="n">
         <v>64</v>
@@ -2801,7 +2801,7 @@
         <v>5</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>1</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="F71" t="n">
         <v>64</v>
@@ -2937,7 +2937,7 @@
         <v>2</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F75" t="n">
         <v>59</v>
@@ -2971,7 +2971,7 @@
         <v>1</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F76" t="n">
         <v>59</v>
@@ -3005,7 +3005,7 @@
         <v>3</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F77" t="n">
         <v>57</v>
@@ -3039,7 +3039,7 @@
         <v>8</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F78" t="n">
         <v>56</v>
@@ -3073,7 +3073,7 @@
         <v>1</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F79" t="n">
         <v>56</v>
@@ -3141,7 +3141,7 @@
         <v>3</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="F81" t="n">
         <v>55</v>
@@ -3175,7 +3175,7 @@
         <v>1</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F82" t="n">
         <v>55</v>
@@ -3209,7 +3209,7 @@
         <v>5</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="F83" t="n">
         <v>51</v>
@@ -3243,7 +3243,7 @@
         <v>1</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F84" t="n">
         <v>45</v>
@@ -3311,7 +3311,7 @@
         <v>1</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F86" t="n">
         <v>42</v>
@@ -3379,7 +3379,7 @@
         <v>2</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F88" t="n">
         <v>38</v>
@@ -3413,7 +3413,7 @@
         <v>4</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F89" t="n">
         <v>38</v>
@@ -3447,7 +3447,7 @@
         <v>1</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="F90" t="n">
         <v>37</v>
@@ -3481,7 +3481,7 @@
         <v>2</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F91" t="n">
         <v>36</v>
@@ -3515,7 +3515,7 @@
         <v>3</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F92" t="n">
         <v>36</v>
@@ -3549,7 +3549,7 @@
         <v>3</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="F93" t="n">
         <v>36</v>
@@ -3583,7 +3583,7 @@
         <v>3</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>0.6</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="F94" t="n">
         <v>32</v>
@@ -3617,7 +3617,7 @@
         <v>1</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F95" t="n">
         <v>32</v>
@@ -3685,7 +3685,7 @@
         <v>3</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F97" t="n">
         <v>31</v>
@@ -3719,7 +3719,7 @@
         <v>2</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F98" t="n">
         <v>31</v>
@@ -3753,7 +3753,7 @@
         <v>2</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F99" t="n">
         <v>28</v>
@@ -3787,7 +3787,7 @@
         <v>3</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="F100" t="n">
         <v>28</v>
@@ -3855,7 +3855,7 @@
         <v>2</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F102" t="n">
         <v>26</v>
@@ -3889,7 +3889,7 @@
         <v>1</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>1</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="F103" t="n">
         <v>26</v>
@@ -3923,7 +3923,7 @@
         <v>1</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.125</v>
       </c>
       <c r="F104" t="n">
         <v>25</v>
@@ -3957,7 +3957,7 @@
         <v>2</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F105" t="n">
         <v>25</v>
@@ -3991,7 +3991,7 @@
         <v>4</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>1</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="F106" t="n">
         <v>24</v>
@@ -4093,7 +4093,7 @@
         <v>1</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F109" t="n">
         <v>20</v>
@@ -4127,7 +4127,7 @@
         <v>3</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="F110" t="n">
         <v>19</v>
@@ -4161,7 +4161,7 @@
         <v>4</v>
       </c>
       <c r="E111" s="4" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F111" t="n">
         <v>18</v>
@@ -4195,7 +4195,7 @@
         <v>1</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F112" t="n">
         <v>18</v>
@@ -4229,7 +4229,7 @@
         <v>2</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F113" t="n">
         <v>15</v>
@@ -4263,7 +4263,7 @@
         <v>1</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>0.5</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="F114" t="n">
         <v>15</v>
@@ -4331,7 +4331,7 @@
         <v>4</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F116" t="n">
         <v>13</v>
@@ -4433,7 +4433,7 @@
         <v>1</v>
       </c>
       <c r="E119" s="4" t="n">
-        <v>0.5</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="F119" t="n">
         <v>13</v>
@@ -4467,7 +4467,7 @@
         <v>1</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F120" t="n">
         <v>13</v>
@@ -4501,7 +4501,7 @@
         <v>1</v>
       </c>
       <c r="E121" s="4" t="n">
-        <v>1</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="F121" t="n">
         <v>13</v>
@@ -4569,7 +4569,7 @@
         <v>2</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F123" t="n">
         <v>12</v>
@@ -4637,7 +4637,7 @@
         <v>2</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>0.5</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="F125" t="n">
         <v>10</v>
@@ -4671,7 +4671,7 @@
         <v>2</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>1</v>
+        <v>0.1052631578947368</v>
       </c>
       <c r="F126" t="n">
         <v>9</v>
@@ -4773,7 +4773,7 @@
         <v>1</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F129" t="n">
         <v>8</v>
@@ -4807,7 +4807,7 @@
         <v>2</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F130" t="n">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F131" t="n">
         <v>7</v>
@@ -4909,7 +4909,7 @@
         <v>2</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="F133" t="n">
         <v>6</v>
@@ -4943,7 +4943,7 @@
         <v>1</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>0.5</v>
+        <v>0.125</v>
       </c>
       <c r="F134" t="n">
         <v>6</v>
@@ -4977,7 +4977,7 @@
         <v>1</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>1</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="F135" t="n">
         <v>5</v>
@@ -5079,7 +5079,7 @@
         <v>2</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F138" t="n">
         <v>3</v>
@@ -5113,7 +5113,7 @@
         <v>1</v>
       </c>
       <c r="E139" s="4" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F139" t="n">
         <v>3</v>
@@ -5215,7 +5215,7 @@
         <v>1</v>
       </c>
       <c r="E142" s="4" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F142" t="n">
         <v>1</v>
